--- a/lrcx/dist/20261025_科林研發模型_v0.2.1.xlsx
+++ b/lrcx/dist/20261025_科林研發模型_v0.2.1.xlsx
@@ -38192,7 +38192,7 @@
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="str">
         <f aca="false">"重點觀察 1：目標價 US$"&amp;TEXT(Val!$B$128,"0.00")&amp;"（DCF "&amp;TEXT(Val!$B$114,"0.00")&amp;"、Comparable（相對倍數調整後）"&amp;TEXT(tp_comp_adj,"0.00")&amp;"；DCF 權重 "&amp;TEXT(tp_w_dcf,"0%")&amp;"），比現價 "&amp;TEXT(px,"0.00")&amp;"（2026-10-23）"&amp;IF(Val!$B$131&gt;=0,"高 "&amp;TEXT(Val!$B$131,"0.0%"),"低 "&amp;TEXT(-Val!$B$131,"0.0%"))&amp;"，級距 "&amp;Val!$B$138&amp;"、投資建議 "&amp;Val!$B$139&amp;"。相對倍數調整係數 "&amp;TEXT(rm_factor,"0.00")&amp;"（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 "&amp;TEXT((tp_w_dcf*Val!$B$114+(1-tp_w_dcf)*Val!$B$124)/px-1,"+0.0%;−0.0%")&amp;"；Comparable 單獨（市場主流同業法、未調整）為 "&amp;TEXT(Val!$B$132,"+0.0%;−0.0%")&amp;"。"&amp;"以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：DCF 比現價低 36.2%，因情境 B、C 的 EPS 在 FY2029 後依收斂法下滑（C 的 FY2032 EPS 5.25 只有 FY2027 9.42 的 56%），不是 ROE（近三年 56.3%）。"</f>
-        <v>重點觀察 1：目標價 US$195.13（DCF 146.89、Comparable（相對倍數調整後）243.38；DCF 權重 50%），比現價 230.10（2026-10-23）低 15.2%，級距 0%～−25%、投資建議 中立。相對倍數調整係數 0.94（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 −11.8%；Comparable 單獨（市場主流同業法、未調整）為 +12.5%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：DCF 比現價低 36.2%，因情境 B、C 的 EPS 在 FY2029 後依收斂法下滑（C 的 FY2032 EPS 5.25 只有 FY2027 9.42 的 56%），不是 ROE（近三年 56.3%）。</v>
+        <v>重點觀察 1：目標價 US$190.79（DCF 143.84、Comparable（相對倍數調整後）237.73；DCF 權重 50%），比現價 230.10（2026-10-23）低 17.1%，級距 0%～−25%、投資建議 中立。相對倍數調整係數 0.94（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 −13.8%；Comparable 單獨（市場主流同業法、未調整）為 +9.9%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：DCF 比現價低 36.2%，因情境 B、C 的 EPS 在 FY2029 後依收斂法下滑（C 的 FY2032 EPS 5.25 只有 FY2027 9.42 的 56%），不是 ROE（近三年 56.3%）。</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38524,7 +38524,7 @@
         <v>31</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>39.3659468014757</v>
+        <v>41.8742847275048</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>32</v>
@@ -38627,7 +38627,7 @@
         <v>31</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>17.5039054704765</v>
+        <v>18.4595763045422</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>32</v>
@@ -38730,7 +38730,7 @@
         <v>31</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>32</v>
@@ -39039,7 +39039,7 @@
         <v>31</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>39.3659468014757</v>
+        <v>41.8742847275048</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>32</v>
@@ -39142,7 +39142,7 @@
         <v>31</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>17.5039054704765</v>
+        <v>18.4595763045422</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>32</v>
@@ -39245,7 +39245,7 @@
         <v>31</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="G51" s="8" t="s">
         <v>32</v>
@@ -39554,7 +39554,7 @@
         <v>31</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>39.3659468014757</v>
+        <v>41.8742847275048</v>
       </c>
       <c r="G66" s="8" t="s">
         <v>32</v>
@@ -39657,7 +39657,7 @@
         <v>31</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>17.5039054704765</v>
+        <v>18.4595763045422</v>
       </c>
       <c r="G71" s="8" t="s">
         <v>32</v>
@@ -39760,7 +39760,7 @@
         <v>31</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="G76" s="8" t="s">
         <v>32</v>
@@ -42665,11 +42665,11 @@
       </c>
       <c r="D22" s="13" t="n">
         <f aca="false">dramA_26</f>
-        <v>39.3659468014757</v>
+        <v>41.8742847275048</v>
       </c>
       <c r="E22" s="10" t="n">
         <f aca="false">C22/D22</f>
-        <v>0.110603242999779</v>
+        <v>0.10397792841916</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>478</v>
@@ -42688,11 +42688,11 @@
       </c>
       <c r="D23" s="13" t="n">
         <f aca="false">nandA_26</f>
-        <v>17.5039054704765</v>
+        <v>18.4595763045422</v>
       </c>
       <c r="E23" s="10" t="n">
         <f aca="false">C23/D23</f>
-        <v>0.257382436599582</v>
+        <v>0.244057488951761</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>478</v>
@@ -42708,11 +42708,11 @@
       </c>
       <c r="D24" s="8" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E24" s="10" t="n">
         <f aca="false">C24/D24</f>
-        <v>0.12696721619429</v>
+        <v>0.123882809341932</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42815,15 +42815,15 @@
       </c>
       <c r="E5" s="22" t="n">
         <f aca="false">E52</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F5" s="22" t="n">
         <f aca="false">F52</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G5" s="22" t="n">
         <f aca="false">G52</f>
-        <v>41.4707470424977</v>
+        <v>40.709804555138</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42843,15 +42843,15 @@
       </c>
       <c r="E6" s="22" t="n">
         <f aca="false">E50</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F6" s="22" t="n">
         <f aca="false">F50</f>
-        <v>26.1018954419896</v>
+        <v>25.3988409204097</v>
       </c>
       <c r="G6" s="22" t="n">
         <f aca="false">G50</f>
-        <v>28.4236972034577</v>
+        <v>27.662754716098</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42899,15 +42899,15 @@
       </c>
       <c r="E8" s="10" t="n">
         <f aca="false">E53</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F8" s="10" t="n">
         <f aca="false">F53</f>
-        <v>0.530054366629259</v>
+        <v>0.52907214052116</v>
       </c>
       <c r="G8" s="10" t="n">
         <f aca="false">G53</f>
-        <v>0.534964444590398</v>
+        <v>0.533996833374025</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42927,15 +42927,15 @@
       </c>
       <c r="E9" s="22" t="n">
         <f aca="false">E56</f>
-        <v>14.0367292073729</v>
+        <v>13.8635007864222</v>
       </c>
       <c r="F9" s="22" t="n">
         <f aca="false">F56</f>
-        <v>15.6911059757308</v>
+        <v>15.3204841939707</v>
       </c>
       <c r="G9" s="22" t="n">
         <f aca="false">G56</f>
-        <v>17.6630767659088</v>
+        <v>17.2581969874251</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42955,15 +42955,15 @@
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">E57</f>
-        <v>0.405658936660381</v>
+        <v>0.404526007234486</v>
       </c>
       <c r="F10" s="10" t="n">
         <f aca="false">F57</f>
-        <v>0.415646907510161</v>
+        <v>0.413530751178012</v>
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">G57</f>
-        <v>0.425916532147547</v>
+        <v>0.423932199528257</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42983,15 +42983,15 @@
       </c>
       <c r="E11" s="22" t="n">
         <f aca="false">E58</f>
-        <v>11.8041688881564</v>
+        <v>11.6595231566625</v>
       </c>
       <c r="F11" s="22" t="n">
         <f aca="false">F58</f>
-        <v>13.1855734897352</v>
+        <v>12.8761043019655</v>
       </c>
       <c r="G11" s="22" t="n">
         <f aca="false">G58</f>
-        <v>14.8321690995338</v>
+        <v>14.4940944845</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43011,15 +43011,15 @@
       </c>
       <c r="E12" s="13" t="n">
         <f aca="false">E60</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F12" s="13" t="n">
         <f aca="false">F60</f>
-        <v>10.6834549282617</v>
+        <v>10.4327111800435</v>
       </c>
       <c r="G12" s="13" t="n">
         <f aca="false">G60</f>
-        <v>12.2005985188508</v>
+        <v>11.9225061764723</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43044,15 +43044,15 @@
       </c>
       <c r="E15" s="22" t="n">
         <f aca="false">E76</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F15" s="22" t="n">
         <f aca="false">F76</f>
-        <v>35.8954420982568</v>
+        <v>35.2328074932868</v>
       </c>
       <c r="G15" s="22" t="n">
         <f aca="false">G76</f>
-        <v>35.9602100328354</v>
+        <v>35.3141412929896</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43072,15 +43072,15 @@
       </c>
       <c r="E16" s="22" t="n">
         <f aca="false">E74</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F16" s="22" t="n">
         <f aca="false">F74</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="G16" s="22" t="n">
         <f aca="false">G74</f>
-        <v>23.9615838415754</v>
+        <v>23.3155151017296</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43128,15 +43128,15 @@
       </c>
       <c r="E18" s="10" t="n">
         <f aca="false">E77</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F18" s="10" t="n">
         <f aca="false">F77</f>
-        <v>0.527420880041177</v>
+        <v>0.526447347986323</v>
       </c>
       <c r="G18" s="10" t="n">
         <f aca="false">G77</f>
-        <v>0.527515070070121</v>
+        <v>0.526567823481368</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43156,15 +43156,15 @@
       </c>
       <c r="E19" s="22" t="n">
         <f aca="false">E80</f>
-        <v>14.0367292073729</v>
+        <v>13.8635007864222</v>
       </c>
       <c r="F19" s="22" t="n">
         <f aca="false">F80</f>
-        <v>14.7144207867113</v>
+        <v>14.3668489197291</v>
       </c>
       <c r="G19" s="22" t="n">
         <f aca="false">G80</f>
-        <v>14.7484280049782</v>
+        <v>14.409476142353</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43184,15 +43184,15 @@
       </c>
       <c r="E20" s="10" t="n">
         <f aca="false">E81</f>
-        <v>0.405658936660381</v>
+        <v>0.404526007234486</v>
       </c>
       <c r="F20" s="10" t="n">
         <f aca="false">F81</f>
-        <v>0.409924489756483</v>
+        <v>0.407769063605463</v>
       </c>
       <c r="G20" s="10" t="n">
         <f aca="false">G81</f>
-        <v>0.410131864956056</v>
+        <v>0.40803699636365</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43212,15 +43212,15 @@
       </c>
       <c r="E21" s="22" t="n">
         <f aca="false">E82</f>
-        <v>11.8041688881564</v>
+        <v>11.6595231566625</v>
       </c>
       <c r="F21" s="22" t="n">
         <f aca="false">F82</f>
-        <v>12.3700413569039</v>
+        <v>12.0798188479738</v>
       </c>
       <c r="G21" s="22" t="n">
         <f aca="false">G82</f>
-        <v>12.3984373841568</v>
+        <v>12.1154125788648</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43240,15 +43240,15 @@
       </c>
       <c r="E22" s="13" t="n">
         <f aca="false">E84</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F22" s="13" t="n">
         <f aca="false">F84</f>
-        <v>10.0226796657799</v>
+        <v>9.7875303113938</v>
       </c>
       <c r="G22" s="13" t="n">
         <f aca="false">G84</f>
-        <v>10.1986672192108</v>
+        <v>9.96585757437253</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43273,15 +43273,15 @@
       </c>
       <c r="E25" s="22" t="n">
         <f aca="false">E100</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F25" s="22" t="n">
         <f aca="false">F100</f>
-        <v>32.2748375498097</v>
+        <v>31.6964900665919</v>
       </c>
       <c r="G25" s="22" t="n">
         <f aca="false">G100</f>
-        <v>28.8240248814277</v>
+        <v>28.329964519962</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43301,15 +43301,15 @@
       </c>
       <c r="E26" s="22" t="n">
         <f aca="false">E98</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F26" s="22" t="n">
         <f aca="false">F98</f>
-        <v>21.4499183353097</v>
+        <v>20.8715708520919</v>
       </c>
       <c r="G26" s="22" t="n">
         <f aca="false">G98</f>
-        <v>18.3238532433627</v>
+        <v>17.829792881897</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43357,15 +43357,15 @@
       </c>
       <c r="E28" s="10" t="n">
         <f aca="false">E101</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F28" s="10" t="n">
         <f aca="false">F101</f>
-        <v>0.521865668906637</v>
+        <v>0.520920909947459</v>
       </c>
       <c r="G28" s="10" t="n">
         <f aca="false">G101</f>
-        <v>0.515957452643486</v>
+        <v>0.515054115267156</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43385,15 +43385,15 @@
       </c>
       <c r="E29" s="22" t="n">
         <f aca="false">E104</f>
-        <v>14.0367292073729</v>
+        <v>13.8635007864222</v>
       </c>
       <c r="F29" s="22" t="n">
         <f aca="false">F104</f>
-        <v>12.8234258542389</v>
+        <v>12.5232697016044</v>
       </c>
       <c r="G29" s="22" t="n">
         <f aca="false">G104</f>
-        <v>11.0408678320501</v>
+        <v>10.7873646367219</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43413,15 +43413,15 @@
       </c>
       <c r="E30" s="10" t="n">
         <f aca="false">E105</f>
-        <v>0.405658936660381</v>
+        <v>0.404526007234486</v>
       </c>
       <c r="F30" s="10" t="n">
         <f aca="false">F105</f>
-        <v>0.397319609570413</v>
+        <v>0.395099573337426</v>
       </c>
       <c r="G30" s="10" t="n">
         <f aca="false">G105</f>
-        <v>0.38304393218742</v>
+        <v>0.380775790563411</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43441,15 +43441,15 @@
       </c>
       <c r="E31" s="22" t="n">
         <f aca="false">E106</f>
-        <v>11.8041688881564</v>
+        <v>11.6595231566625</v>
       </c>
       <c r="F31" s="22" t="n">
         <f aca="false">F106</f>
-        <v>10.7910605882895</v>
+        <v>10.5404302008397</v>
       </c>
       <c r="G31" s="22" t="n">
         <f aca="false">G106</f>
-        <v>9.30262463976181</v>
+        <v>9.09094947166281</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43469,15 +43469,15 @@
       </c>
       <c r="E32" s="13" t="n">
         <f aca="false">E108</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F32" s="13" t="n">
         <f aca="false">F108</f>
-        <v>8.74332917812638</v>
+        <v>8.54025887177551</v>
       </c>
       <c r="G32" s="13" t="n">
         <f aca="false">G108</f>
-        <v>7.6521234109224</v>
+        <v>7.4780043238856</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43567,15 +43567,15 @@
       </c>
       <c r="E44" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F44" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G44" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H44" s="8" t="s">
         <v>506</v>
@@ -43594,15 +43594,15 @@
       </c>
       <c r="E45" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F45" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G45" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H45" s="8" t="s">
         <v>506</v>
@@ -43644,15 +43644,15 @@
       </c>
       <c r="E47" s="17" t="n">
         <f aca="false">SUM(E43:E46)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F47" s="17" t="n">
         <f aca="false">SUM(F43:F46)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G47" s="17" t="n">
         <f aca="false">SUM(G43:G46)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43704,15 +43704,15 @@
       </c>
       <c r="E50" s="17" t="n">
         <f aca="false">h2s26+h1s*E47</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F50" s="17" t="n">
         <f aca="false">(1-h1s)*E47+h1s*F47</f>
-        <v>26.1018954419896</v>
+        <v>25.3988409204097</v>
       </c>
       <c r="G50" s="17" t="n">
         <f aca="false">(1-h1s)*F47+h1s*G47</f>
-        <v>28.4236972034577</v>
+        <v>27.662754716098</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>515</v>
@@ -43763,15 +43763,15 @@
       </c>
       <c r="E52" s="17" t="n">
         <f aca="false">E50+E51</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F52" s="17" t="n">
         <f aca="false">F50+F51</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G52" s="17" t="n">
         <f aca="false">G50+G51</f>
-        <v>41.4707470424977</v>
+        <v>40.709804555138</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43791,15 +43791,15 @@
       </c>
       <c r="E53" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E52)</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F53" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F52)</f>
-        <v>0.530054366629259</v>
+        <v>0.52907214052116</v>
       </c>
       <c r="G53" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G52)</f>
-        <v>0.534964444590398</v>
+        <v>0.533996833374025</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>516</v>
@@ -43822,15 +43822,15 @@
       </c>
       <c r="E54" s="17" t="n">
         <f aca="false">E52*E53</f>
-        <v>18.1836381009569</v>
+        <v>17.9923018165092</v>
       </c>
       <c r="F54" s="17" t="n">
         <f aca="false">F52*F53</f>
-        <v>20.0101073516955</v>
+        <v>19.6010607270061</v>
       </c>
       <c r="G54" s="17" t="n">
         <f aca="false">G52*G53</f>
-        <v>22.1853751583387</v>
+        <v>21.7389067197192</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43850,15 +43850,15 @@
       </c>
       <c r="E55" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E52</f>
-        <v>4.14690889358399</v>
+        <v>4.12880103008697</v>
       </c>
       <c r="F55" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F52</f>
-        <v>4.31900137596466</v>
+        <v>4.28057653303542</v>
       </c>
       <c r="G55" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G52</f>
-        <v>4.52229839242993</v>
+        <v>4.48070973229404</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>517</v>
@@ -43881,15 +43881,15 @@
       </c>
       <c r="E56" s="17" t="n">
         <f aca="false">E54-E55</f>
-        <v>14.0367292073729</v>
+        <v>13.8635007864222</v>
       </c>
       <c r="F56" s="17" t="n">
         <f aca="false">F54-F55</f>
-        <v>15.6911059757308</v>
+        <v>15.3204841939707</v>
       </c>
       <c r="G56" s="17" t="n">
         <f aca="false">G54-G55</f>
-        <v>17.6630767659088</v>
+        <v>17.2581969874251</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43909,15 +43909,15 @@
       </c>
       <c r="E57" s="10" t="n">
         <f aca="false">E56/E52</f>
-        <v>0.405658936660381</v>
+        <v>0.404526007234486</v>
       </c>
       <c r="F57" s="10" t="n">
         <f aca="false">F56/F52</f>
-        <v>0.415646907510161</v>
+        <v>0.413530751178012</v>
       </c>
       <c r="G57" s="10" t="n">
         <f aca="false">G56/G52</f>
-        <v>0.425916532147547</v>
+        <v>0.423932199528257</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43937,15 +43937,15 @@
       </c>
       <c r="E58" s="17" t="n">
         <f aca="false">(E56+oth_inc)*(1-tax)</f>
-        <v>11.8041688881564</v>
+        <v>11.6595231566625</v>
       </c>
       <c r="F58" s="17" t="n">
         <f aca="false">(F56+oth_inc)*(1-tax)</f>
-        <v>13.1855734897352</v>
+        <v>12.8761043019655</v>
       </c>
       <c r="G58" s="17" t="n">
         <f aca="false">(G56+oth_inc)*(1-tax)</f>
-        <v>14.8321690995338</v>
+        <v>14.4940944845</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43993,15 +43993,15 @@
       </c>
       <c r="E60" s="13" t="n">
         <f aca="false">E58/E59</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F60" s="13" t="n">
         <f aca="false">F58/F59</f>
-        <v>10.6834549282617</v>
+        <v>10.4327111800435</v>
       </c>
       <c r="G60" s="13" t="n">
         <f aca="false">G58/G59</f>
-        <v>12.2005985188508</v>
+        <v>11.9225061764723</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44021,15 +44021,15 @@
       </c>
       <c r="E61" s="10" t="n">
         <f aca="false">E50/E52</f>
-        <v>0.697479442127972</v>
+        <v>0.694554801249891</v>
       </c>
       <c r="F61" s="10" t="n">
         <f aca="false">F50/F52</f>
-        <v>0.691421760671098</v>
+        <v>0.685565915012096</v>
       </c>
       <c r="G61" s="10" t="n">
         <f aca="false">G50/G52</f>
-        <v>0.685391492329042</v>
+        <v>0.679510870130343</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44108,15 +44108,15 @@
       </c>
       <c r="E68" s="17" t="n">
         <f aca="false">k_dram*dramB_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F68" s="17" t="n">
         <f aca="false">k_dram*dramB_28*(1+drift)^2</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="G68" s="17" t="n">
         <f aca="false">k_dram*dramB_29*(1+drift)^3</f>
-        <v>5.59605913906334</v>
+        <v>5.2608460729499</v>
       </c>
       <c r="H68" s="8" t="s">
         <v>506</v>
@@ -44135,15 +44135,15 @@
       </c>
       <c r="E69" s="17" t="n">
         <f aca="false">k_nand*nandB_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F69" s="17" t="n">
         <f aca="false">k_nand*nandB_28*(1+drift)^2</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="G69" s="17" t="n">
         <f aca="false">k_nand*nandB_29*(1+drift)^3</f>
-        <v>5.68445220258324</v>
+        <v>5.3901623939752</v>
       </c>
       <c r="H69" s="8" t="s">
         <v>506</v>
@@ -44185,15 +44185,15 @@
       </c>
       <c r="E71" s="17" t="n">
         <f aca="false">SUM(E67:E70)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F71" s="17" t="n">
         <f aca="false">SUM(F67:F70)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="G71" s="17" t="n">
         <f aca="false">SUM(G67:G70)</f>
-        <v>23.3471842558939</v>
+        <v>22.7176813811724</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44245,15 +44245,15 @@
       </c>
       <c r="E74" s="17" t="n">
         <f aca="false">h2s26+h1s*E71</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F74" s="17" t="n">
         <f aca="false">(1-h1s)*E71+h1s*F71</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="G74" s="17" t="n">
         <f aca="false">(1-h1s)*F71+h1s*G71</f>
-        <v>23.9615838415754</v>
+        <v>23.3155151017296</v>
       </c>
       <c r="H74" s="8" t="s">
         <v>515</v>
@@ -44304,15 +44304,15 @@
       </c>
       <c r="E76" s="17" t="n">
         <f aca="false">E74+E75</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F76" s="17" t="n">
         <f aca="false">F74+F75</f>
-        <v>35.8954420982568</v>
+        <v>35.2328074932868</v>
       </c>
       <c r="G76" s="17" t="n">
         <f aca="false">G74+G75</f>
-        <v>35.9602100328354</v>
+        <v>35.3141412929896</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44332,15 +44332,15 @@
       </c>
       <c r="E77" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E76)</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F77" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F76)</f>
-        <v>0.527420880041177</v>
+        <v>0.526447347986323</v>
       </c>
       <c r="G77" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G76)</f>
-        <v>0.527515070070121</v>
+        <v>0.526567823481368</v>
       </c>
       <c r="H77" s="5" t="s">
         <v>516</v>
@@ -44363,15 +44363,15 @@
       </c>
       <c r="E78" s="17" t="n">
         <f aca="false">E76*E77</f>
-        <v>18.1836381009569</v>
+        <v>17.9923018165092</v>
       </c>
       <c r="F78" s="17" t="n">
         <f aca="false">F76*F77</f>
-        <v>18.9320056609297</v>
+        <v>18.5482180669535</v>
       </c>
       <c r="G78" s="17" t="n">
         <f aca="false">G76*G77</f>
-        <v>18.9695527152074</v>
+        <v>18.595290518763</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44391,15 +44391,15 @@
       </c>
       <c r="E79" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E76</f>
-        <v>4.14690889358399</v>
+        <v>4.12880103008697</v>
       </c>
       <c r="F79" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F76</f>
-        <v>4.21758487421841</v>
+        <v>4.18136914722438</v>
       </c>
       <c r="G79" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G76</f>
-        <v>4.2211247102292</v>
+        <v>4.18581437641002</v>
       </c>
       <c r="H79" s="5" t="s">
         <v>517</v>
@@ -44422,15 +44422,15 @@
       </c>
       <c r="E80" s="17" t="n">
         <f aca="false">E78-E79</f>
-        <v>14.0367292073729</v>
+        <v>13.8635007864222</v>
       </c>
       <c r="F80" s="17" t="n">
         <f aca="false">F78-F79</f>
-        <v>14.7144207867113</v>
+        <v>14.3668489197291</v>
       </c>
       <c r="G80" s="17" t="n">
         <f aca="false">G78-G79</f>
-        <v>14.7484280049782</v>
+        <v>14.409476142353</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44450,15 +44450,15 @@
       </c>
       <c r="E81" s="10" t="n">
         <f aca="false">E80/E76</f>
-        <v>0.405658936660381</v>
+        <v>0.404526007234486</v>
       </c>
       <c r="F81" s="10" t="n">
         <f aca="false">F80/F76</f>
-        <v>0.409924489756483</v>
+        <v>0.407769063605463</v>
       </c>
       <c r="G81" s="10" t="n">
         <f aca="false">G80/G76</f>
-        <v>0.410131864956056</v>
+        <v>0.40803699636365</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44478,15 +44478,15 @@
       </c>
       <c r="E82" s="17" t="n">
         <f aca="false">(E80+oth_inc)*(1-tax)</f>
-        <v>11.8041688881564</v>
+        <v>11.6595231566625</v>
       </c>
       <c r="F82" s="17" t="n">
         <f aca="false">(F80+oth_inc)*(1-tax)</f>
-        <v>12.3700413569039</v>
+        <v>12.0798188479738</v>
       </c>
       <c r="G82" s="17" t="n">
         <f aca="false">(G80+oth_inc)*(1-tax)</f>
-        <v>12.3984373841568</v>
+        <v>12.1154125788648</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44534,15 +44534,15 @@
       </c>
       <c r="E84" s="13" t="n">
         <f aca="false">E82/E83</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F84" s="13" t="n">
         <f aca="false">F82/F83</f>
-        <v>10.0226796657799</v>
+        <v>9.7875303113938</v>
       </c>
       <c r="G84" s="13" t="n">
         <f aca="false">G82/G83</f>
-        <v>10.1986672192108</v>
+        <v>9.96585757437253</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44562,15 +44562,15 @@
       </c>
       <c r="E85" s="10" t="n">
         <f aca="false">E74/E76</f>
-        <v>0.697479442127972</v>
+        <v>0.694554801249891</v>
       </c>
       <c r="F85" s="10" t="n">
         <f aca="false">F74/F76</f>
-        <v>0.684654707970578</v>
+        <v>0.678723908869403</v>
       </c>
       <c r="G85" s="10" t="n">
         <f aca="false">G74/G76</f>
-        <v>0.666336036961296</v>
+        <v>0.660231687591908</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44649,15 +44649,15 @@
       </c>
       <c r="E92" s="17" t="n">
         <f aca="false">k_dram*dramC_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F92" s="17" t="n">
         <f aca="false">k_dram*dramC_28*(1+drift)^2</f>
-        <v>4.71247085394807</v>
+        <v>4.43018616669465</v>
       </c>
       <c r="G92" s="17" t="n">
         <f aca="false">k_dram*dramC_29*(1+drift)^3</f>
-        <v>4.71247085394807</v>
+        <v>4.43018616669465</v>
       </c>
       <c r="H92" s="8" t="s">
         <v>506</v>
@@ -44676,15 +44676,15 @@
       </c>
       <c r="E93" s="17" t="n">
         <f aca="false">k_nand*nandC_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F93" s="17" t="n">
         <f aca="false">k_nand*nandC_28*(1+drift)^2</f>
-        <v>4.78690711796484</v>
+        <v>4.53908412124228</v>
       </c>
       <c r="G93" s="17" t="n">
         <f aca="false">k_nand*nandC_29*(1+drift)^3</f>
-        <v>4.78690711796484</v>
+        <v>4.53908412124228</v>
       </c>
       <c r="H93" s="8" t="s">
         <v>506</v>
@@ -44703,11 +44703,11 @@
       </c>
       <c r="F94" s="17" t="n">
         <f aca="false">-cn_sh*cutC*(F91+F92+F93)</f>
-        <v>-1.33693349844277</v>
+        <v>-1.3008861759324</v>
       </c>
       <c r="G94" s="17" t="n">
         <f aca="false">-cn_sh*cutC*(G91+G92+G93)</f>
-        <v>-1.33693349844277</v>
+        <v>-1.3008861759324</v>
       </c>
       <c r="H94" s="5" t="s">
         <v>510</v>
@@ -44726,15 +44726,15 @@
       </c>
       <c r="E95" s="17" t="n">
         <f aca="false">SUM(E91:E94)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F95" s="17" t="n">
         <f aca="false">SUM(F91:F94)</f>
-        <v>18.3238532433627</v>
+        <v>17.829792881897</v>
       </c>
       <c r="G95" s="17" t="n">
         <f aca="false">SUM(G91:G94)</f>
-        <v>18.3238532433627</v>
+        <v>17.829792881897</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44786,15 +44786,15 @@
       </c>
       <c r="E98" s="17" t="n">
         <f aca="false">h2s26+h1s*E95</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F98" s="17" t="n">
         <f aca="false">(1-h1s)*E95+h1s*F95</f>
-        <v>21.4499183353097</v>
+        <v>20.8715708520919</v>
       </c>
       <c r="G98" s="17" t="n">
         <f aca="false">(1-h1s)*F95+h1s*G95</f>
-        <v>18.3238532433627</v>
+        <v>17.829792881897</v>
       </c>
       <c r="H98" s="8" t="s">
         <v>515</v>
@@ -44845,15 +44845,15 @@
       </c>
       <c r="E100" s="17" t="n">
         <f aca="false">E98+E99</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F100" s="17" t="n">
         <f aca="false">F98+F99</f>
-        <v>32.2748375498097</v>
+        <v>31.6964900665919</v>
       </c>
       <c r="G100" s="17" t="n">
         <f aca="false">G98+G99</f>
-        <v>28.8240248814277</v>
+        <v>28.329964519962</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44873,15 +44873,15 @@
       </c>
       <c r="E101" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E100)</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F101" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F100)</f>
-        <v>0.521865668906637</v>
+        <v>0.520920909947459</v>
       </c>
       <c r="G101" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G100)</f>
-        <v>0.515957452643486</v>
+        <v>0.515054115267156</v>
       </c>
       <c r="H101" s="5" t="s">
         <v>516</v>
@@ -44904,15 +44904,15 @@
       </c>
       <c r="E102" s="17" t="n">
         <f aca="false">E100*E101</f>
-        <v>18.1836381009569</v>
+        <v>17.9923018165092</v>
       </c>
       <c r="F102" s="17" t="n">
         <f aca="false">F100*F101</f>
-        <v>16.8431296867845</v>
+        <v>16.5113644476296</v>
       </c>
       <c r="G102" s="17" t="n">
         <f aca="false">G100*G101</f>
-        <v>14.8719704527539</v>
+        <v>14.591464811379</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44932,15 +44932,15 @@
       </c>
       <c r="E103" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E100</f>
-        <v>4.14690889358399</v>
+        <v>4.12880103008697</v>
       </c>
       <c r="F103" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F100</f>
-        <v>4.01970383254562</v>
+        <v>3.98809474602523</v>
       </c>
       <c r="G103" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G100</f>
-        <v>3.83110262070379</v>
+        <v>3.80410017465704</v>
       </c>
       <c r="H103" s="5" t="s">
         <v>517</v>
@@ -44963,15 +44963,15 @@
       </c>
       <c r="E104" s="17" t="n">
         <f aca="false">E102-E103</f>
-        <v>14.0367292073729</v>
+        <v>13.8635007864222</v>
       </c>
       <c r="F104" s="17" t="n">
         <f aca="false">F102-F103</f>
-        <v>12.8234258542389</v>
+        <v>12.5232697016044</v>
       </c>
       <c r="G104" s="17" t="n">
         <f aca="false">G102-G103</f>
-        <v>11.0408678320501</v>
+        <v>10.7873646367219</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44991,15 +44991,15 @@
       </c>
       <c r="E105" s="10" t="n">
         <f aca="false">E104/E100</f>
-        <v>0.405658936660381</v>
+        <v>0.404526007234486</v>
       </c>
       <c r="F105" s="10" t="n">
         <f aca="false">F104/F100</f>
-        <v>0.397319609570413</v>
+        <v>0.395099573337426</v>
       </c>
       <c r="G105" s="10" t="n">
         <f aca="false">G104/G100</f>
-        <v>0.38304393218742</v>
+        <v>0.380775790563411</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45019,15 +45019,15 @@
       </c>
       <c r="E106" s="17" t="n">
         <f aca="false">(E104+oth_inc)*(1-tax)</f>
-        <v>11.8041688881564</v>
+        <v>11.6595231566625</v>
       </c>
       <c r="F106" s="17" t="n">
         <f aca="false">(F104+oth_inc)*(1-tax)</f>
-        <v>10.7910605882895</v>
+        <v>10.5404302008397</v>
       </c>
       <c r="G106" s="17" t="n">
         <f aca="false">(G104+oth_inc)*(1-tax)</f>
-        <v>9.30262463976181</v>
+        <v>9.09094947166281</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45075,15 +45075,15 @@
       </c>
       <c r="E108" s="13" t="n">
         <f aca="false">E106/E107</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F108" s="13" t="n">
         <f aca="false">F106/F107</f>
-        <v>8.74332917812638</v>
+        <v>8.54025887177551</v>
       </c>
       <c r="G108" s="13" t="n">
         <f aca="false">G106/G107</f>
-        <v>7.6521234109224</v>
+        <v>7.4780043238856</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45103,15 +45103,15 @@
       </c>
       <c r="E109" s="10" t="n">
         <f aca="false">E98/E100</f>
-        <v>0.697479442127972</v>
+        <v>0.694554801249891</v>
       </c>
       <c r="F109" s="10" t="n">
         <f aca="false">F98/F100</f>
-        <v>0.664601899303322</v>
+        <v>0.658482084553915</v>
       </c>
       <c r="G109" s="10" t="n">
         <f aca="false">G98/G100</f>
-        <v>0.635714592904385</v>
+        <v>0.629361638251742</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45181,27 +45181,27 @@
       </c>
       <c r="E116" s="22" t="n">
         <f aca="false">E5</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F116" s="22" t="n">
         <f aca="false">F5</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G116" s="22" t="n">
         <f aca="false">G5</f>
-        <v>41.4707470424977</v>
+        <v>40.709804555138</v>
       </c>
       <c r="H116" s="23" t="n">
         <f aca="false">G116*(1+H117)</f>
-        <v>45.0243025122197</v>
+        <v>44.2064968757915</v>
       </c>
       <c r="I116" s="23" t="n">
         <f aca="false">H116*(1+I117)</f>
-        <v>48.3040582855953</v>
+        <v>47.4312088572235</v>
       </c>
       <c r="J116" s="23" t="n">
         <f aca="false">I116*(1+J117)</f>
-        <v>51.2023017827311</v>
+        <v>50.2770813886569</v>
       </c>
       <c r="K116" s="8" t="s">
         <v>529</v>
@@ -45220,23 +45220,23 @@
       </c>
       <c r="E117" s="10" t="n">
         <f aca="false">E116/D116-1</f>
-        <v>0.48937951496914</v>
+        <v>0.475118690997185</v>
       </c>
       <c r="F117" s="10" t="n">
         <f aca="false">F116/E116-1</f>
-        <v>0.0909984364351344</v>
+        <v>0.0810311722997552</v>
       </c>
       <c r="G117" s="10" t="n">
         <f aca="false">G116/F116-1</f>
-        <v>0.0985323652144636</v>
+        <v>0.0988396871047665</v>
       </c>
       <c r="H117" s="24" t="n">
         <f aca="false">$G117+((tp_g+0.02)-$G117)*1/3</f>
-        <v>0.0856882434763091</v>
+        <v>0.085893124736511</v>
       </c>
       <c r="I117" s="24" t="n">
         <f aca="false">$G117+((tp_g+0.02)-$G117)*2/3</f>
-        <v>0.0728441217381545</v>
+        <v>0.0729465623682555</v>
       </c>
       <c r="J117" s="24" t="n">
         <f aca="false">$G117+((tp_g+0.02)-$G117)*3/3</f>
@@ -45260,27 +45260,27 @@
       </c>
       <c r="E118" s="10" t="n">
         <f aca="false">E119/E116</f>
-        <v>0.341138347017045</v>
+        <v>0.340215680114658</v>
       </c>
       <c r="F118" s="10" t="n">
         <f aca="false">F119/F116</f>
-        <v>0.349277026949731</v>
+        <v>0.347552010551582</v>
       </c>
       <c r="G118" s="10" t="n">
         <f aca="false">G119/G116</f>
-        <v>0.357653771810147</v>
+        <v>0.356034489550765</v>
       </c>
       <c r="H118" s="24" t="n">
         <f aca="false">$G118+($G118-$G118)*1/3</f>
-        <v>0.357653771810147</v>
+        <v>0.356034489550765</v>
       </c>
       <c r="I118" s="24" t="n">
         <f aca="false">$G118+($G118-$G118)*2/3</f>
-        <v>0.357653771810147</v>
+        <v>0.356034489550765</v>
       </c>
       <c r="J118" s="24" t="n">
         <f aca="false">$G118+($G118-$G118)*3/3</f>
-        <v>0.357653771810147</v>
+        <v>0.356034489550765</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45300,27 +45300,27 @@
       </c>
       <c r="E119" s="22" t="n">
         <f aca="false">E11</f>
-        <v>11.8041688881564</v>
+        <v>11.6595231566625</v>
       </c>
       <c r="F119" s="22" t="n">
         <f aca="false">F11</f>
-        <v>13.1855734897352</v>
+        <v>12.8761043019655</v>
       </c>
       <c r="G119" s="22" t="n">
         <f aca="false">G11</f>
-        <v>14.8321690995338</v>
+        <v>14.4940944845</v>
       </c>
       <c r="H119" s="23" t="n">
         <f aca="false">H116*H118</f>
-        <v>16.1031116166165</v>
+        <v>15.7390375499999</v>
       </c>
       <c r="I119" s="23" t="n">
         <f aca="false">I116*I118</f>
-        <v>17.2761286395804</v>
+        <v>16.8871462342573</v>
       </c>
       <c r="J119" s="23" t="n">
         <f aca="false">J116*J118</f>
-        <v>18.3126963579552</v>
+        <v>17.9003750083127</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45340,27 +45340,27 @@
       </c>
       <c r="E120" s="13" t="n">
         <f aca="false">E12</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F120" s="13" t="n">
         <f aca="false">F12</f>
-        <v>10.6834549282617</v>
+        <v>10.4327111800435</v>
       </c>
       <c r="G120" s="13" t="n">
         <f aca="false">G12</f>
-        <v>12.2005985188508</v>
+        <v>11.9225061764723</v>
       </c>
       <c r="H120" s="25" t="n">
         <f aca="false">$G120*H119/$G119</f>
-        <v>13.2460463752907</v>
+        <v>12.9465674866598</v>
       </c>
       <c r="I120" s="25" t="n">
         <f aca="false">$G120*I119/$G119</f>
-        <v>14.2109429900017</v>
+        <v>13.8909750792803</v>
       </c>
       <c r="J120" s="25" t="n">
         <f aca="false">$G120*J119/$G119</f>
-        <v>15.0635995694018</v>
+        <v>14.7244335840371</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45385,27 +45385,27 @@
       </c>
       <c r="E123" s="22" t="n">
         <f aca="false">E15</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F123" s="22" t="n">
         <f aca="false">F15</f>
-        <v>35.8954420982568</v>
+        <v>35.2328074932868</v>
       </c>
       <c r="G123" s="22" t="n">
         <f aca="false">G15</f>
-        <v>35.9602100328354</v>
+        <v>35.3141412929896</v>
       </c>
       <c r="H123" s="23" t="n">
         <f aca="false">G123*(1+H124)</f>
-        <v>36.4829360323331</v>
+        <v>35.8393442143336</v>
       </c>
       <c r="I123" s="23" t="n">
         <f aca="false">H123*(1+I124)</f>
-        <v>37.4777569862467</v>
+        <v>36.8226380501025</v>
       </c>
       <c r="J123" s="23" t="n">
         <f aca="false">I123*(1+J124)</f>
-        <v>38.9768672656966</v>
+        <v>38.2955435721066</v>
       </c>
       <c r="K123" s="8" t="s">
         <v>529</v>
@@ -45424,23 +45424,23 @@
       </c>
       <c r="E124" s="10" t="n">
         <f aca="false">E123/D123-1</f>
-        <v>0.48937951496914</v>
+        <v>0.475118690997185</v>
       </c>
       <c r="F124" s="10" t="n">
         <f aca="false">F123/E123-1</f>
-        <v>0.0373717877869069</v>
+        <v>0.0280655051341336</v>
       </c>
       <c r="G124" s="10" t="n">
         <f aca="false">G123/F123-1</f>
-        <v>0.00180434982250111</v>
+        <v>0.00230846774610094</v>
       </c>
       <c r="H124" s="24" t="n">
         <f aca="false">$G124+((tp_g)-$G124)*1/3</f>
-        <v>0.0145362332150007</v>
+        <v>0.014872311830734</v>
       </c>
       <c r="I124" s="24" t="n">
         <f aca="false">$G124+((tp_g)-$G124)*2/3</f>
-        <v>0.0272681166075004</v>
+        <v>0.027436155915367</v>
       </c>
       <c r="J124" s="24" t="n">
         <f aca="false">$G124+((tp_g)-$G124)*3/3</f>
@@ -45464,27 +45464,27 @@
       </c>
       <c r="E125" s="10" t="n">
         <f aca="false">E126/E123</f>
-        <v>0.341138347017045</v>
+        <v>0.340215680114658</v>
       </c>
       <c r="F125" s="10" t="n">
         <f aca="false">F126/F123</f>
-        <v>0.34461314957602</v>
+        <v>0.342857118334253</v>
       </c>
       <c r="G125" s="10" t="n">
         <f aca="false">G126/G123</f>
-        <v>0.344782118147691</v>
+        <v>0.34307538383412</v>
       </c>
       <c r="H125" s="24" t="n">
         <f aca="false">$G125+(($G125+nim10)/2-$G125)*1/3</f>
-        <v>0.326891456083938</v>
+        <v>0.325469177489296</v>
       </c>
       <c r="I125" s="24" t="n">
         <f aca="false">$G125+(($G125+nim10)/2-$G125)*2/3</f>
-        <v>0.309000794020186</v>
+        <v>0.307862971144472</v>
       </c>
       <c r="J125" s="24" t="n">
         <f aca="false">$G125+(($G125+nim10)/2-$G125)*3/3</f>
-        <v>0.291110131956433</v>
+        <v>0.290256764799648</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45504,27 +45504,27 @@
       </c>
       <c r="E126" s="22" t="n">
         <f aca="false">E21</f>
-        <v>11.8041688881564</v>
+        <v>11.6595231566625</v>
       </c>
       <c r="F126" s="22" t="n">
         <f aca="false">F21</f>
-        <v>12.3700413569039</v>
+        <v>12.0798188479738</v>
       </c>
       <c r="G126" s="22" t="n">
         <f aca="false">G21</f>
-        <v>12.3984373841568</v>
+        <v>12.1154125788648</v>
       </c>
       <c r="H126" s="23" t="n">
         <f aca="false">H123*H125</f>
-        <v>11.9259600818265</v>
+        <v>11.6646018831949</v>
       </c>
       <c r="I126" s="23" t="n">
         <f aca="false">I123*I125</f>
-        <v>11.5806566668458</v>
+        <v>11.336326755482</v>
       </c>
       <c r="J126" s="23" t="n">
         <f aca="false">J123*J125</f>
-        <v>11.3465609729653</v>
+        <v>11.1155405834836</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45544,27 +45544,27 @@
       </c>
       <c r="E127" s="13" t="n">
         <f aca="false">E22</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F127" s="13" t="n">
         <f aca="false">F22</f>
-        <v>10.0226796657799</v>
+        <v>9.7875303113938</v>
       </c>
       <c r="G127" s="13" t="n">
         <f aca="false">G22</f>
-        <v>10.1986672192108</v>
+        <v>9.96585757437253</v>
       </c>
       <c r="H127" s="25" t="n">
         <f aca="false">$G127*H126/$G126</f>
-        <v>9.81001834146964</v>
+        <v>9.59503114507806</v>
       </c>
       <c r="I127" s="25" t="n">
         <f aca="false">$G127*I126/$G126</f>
-        <v>9.52597975580514</v>
+        <v>9.32499963383572</v>
       </c>
       <c r="J127" s="25" t="n">
         <f aca="false">$G127*J126/$G126</f>
-        <v>9.33341806392709</v>
+        <v>9.14338604616758</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45589,27 +45589,27 @@
       </c>
       <c r="E130" s="22" t="n">
         <f aca="false">E25</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F130" s="22" t="n">
         <f aca="false">F25</f>
-        <v>32.2748375498097</v>
+        <v>31.6964900665919</v>
       </c>
       <c r="G130" s="22" t="n">
         <f aca="false">G25</f>
-        <v>28.8240248814277</v>
+        <v>28.329964519962</v>
       </c>
       <c r="H130" s="23" t="n">
         <f aca="false">G130*(1+H131)</f>
-        <v>26.9616162714252</v>
+        <v>26.5128559648271</v>
       </c>
       <c r="I130" s="23" t="n">
         <f aca="false">H130*(1+I131)</f>
-        <v>26.3601960939676</v>
+        <v>25.9277057081923</v>
       </c>
       <c r="J130" s="23" t="n">
         <f aca="false">I130*(1+J131)</f>
-        <v>26.8874000158469</v>
+        <v>26.4462598223561</v>
       </c>
       <c r="K130" s="8" t="s">
         <v>529</v>
@@ -45628,23 +45628,23 @@
       </c>
       <c r="E131" s="10" t="n">
         <f aca="false">E130/D130-1</f>
-        <v>0.48937951496914</v>
+        <v>0.475118690997185</v>
       </c>
       <c r="F131" s="10" t="n">
         <f aca="false">F130/E130-1</f>
-        <v>-0.0672630291631352</v>
+        <v>-0.0751214453319178</v>
       </c>
       <c r="G131" s="10" t="n">
         <f aca="false">G130/F130-1</f>
-        <v>-0.10691959837308</v>
+        <v>-0.106211304139893</v>
       </c>
       <c r="H131" s="24" t="n">
         <f aca="false">$G131+((tp_g-0.02)-$G131)*1/3</f>
-        <v>-0.0646130655820535</v>
+        <v>-0.064140869426595</v>
       </c>
       <c r="I131" s="24" t="n">
         <f aca="false">$G131+((tp_g-0.02)-$G131)*2/3</f>
-        <v>-0.0223065327910267</v>
+        <v>-0.0220704347132975</v>
       </c>
       <c r="J131" s="24" t="n">
         <f aca="false">$G131+((tp_g-0.02)-$G131)*3/3</f>
@@ -45668,23 +45668,23 @@
       </c>
       <c r="E132" s="10" t="n">
         <f aca="false">E133/E130</f>
-        <v>0.341138347017045</v>
+        <v>0.340215680114658</v>
       </c>
       <c r="F132" s="10" t="n">
         <f aca="false">F133/F130</f>
-        <v>0.334349028763836</v>
+        <v>0.332542504822933</v>
       </c>
       <c r="G132" s="10" t="n">
         <f aca="false">G133/G130</f>
-        <v>0.322738572355168</v>
+        <v>0.320895194388863</v>
       </c>
       <c r="H132" s="24" t="n">
         <f aca="false">$G132+(nim10-$G132)*1/3</f>
-        <v>0.294305096825171</v>
+        <v>0.293076178180967</v>
       </c>
       <c r="I132" s="24" t="n">
         <f aca="false">$G132+(nim10-$G132)*2/3</f>
-        <v>0.265871621295173</v>
+        <v>0.265257161973071</v>
       </c>
       <c r="J132" s="24" t="n">
         <f aca="false">$G132+(nim10-$G132)*3/3</f>
@@ -45708,27 +45708,27 @@
       </c>
       <c r="E133" s="22" t="n">
         <f aca="false">E31</f>
-        <v>11.8041688881564</v>
+        <v>11.6595231566625</v>
       </c>
       <c r="F133" s="22" t="n">
         <f aca="false">F31</f>
-        <v>10.7910605882895</v>
+        <v>10.5404302008397</v>
       </c>
       <c r="G133" s="22" t="n">
         <f aca="false">G31</f>
-        <v>9.30262463976181</v>
+        <v>9.09094947166281</v>
       </c>
       <c r="H133" s="23" t="n">
         <f aca="false">H130*H132</f>
-        <v>7.9349410873249</v>
+        <v>7.77028649883397</v>
       </c>
       <c r="I133" s="23" t="n">
         <f aca="false">I130*I132</f>
-        <v>7.00842807316184</v>
+        <v>6.87750963262808</v>
       </c>
       <c r="J133" s="23" t="n">
         <f aca="false">J130*J132</f>
-        <v>6.38409440420923</v>
+        <v>6.27935089464428</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45748,27 +45748,27 @@
       </c>
       <c r="E134" s="13" t="n">
         <f aca="false">E32</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F134" s="13" t="n">
         <f aca="false">F32</f>
-        <v>8.74332917812638</v>
+        <v>8.54025887177551</v>
       </c>
       <c r="G134" s="13" t="n">
         <f aca="false">G32</f>
-        <v>7.6521234109224</v>
+        <v>7.4780043238856</v>
       </c>
       <c r="H134" s="25" t="n">
         <f aca="false">$G134*H133/$G133</f>
-        <v>6.52709862107943</v>
+        <v>6.39165757297761</v>
       </c>
       <c r="I134" s="25" t="n">
         <f aca="false">$G134*I133/$G133</f>
-        <v>5.76497049049811</v>
+        <v>5.65728001576393</v>
       </c>
       <c r="J134" s="25" t="n">
         <f aca="false">$G134*J133/$G133</f>
-        <v>5.25140808532493</v>
+        <v>5.1652485021189</v>
       </c>
     </row>
   </sheetData>
@@ -45832,7 +45832,7 @@
       </c>
       <c r="B6" s="27" t="n">
         <f aca="false">tp_wA*B8+tp_wB*B9+tp_wC*B10</f>
-        <v>154.25592051976</v>
+        <v>152.365701845981</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>542</v>
@@ -45844,7 +45844,7 @@
       </c>
       <c r="B7" s="10" t="n">
         <f aca="false">B6/px-1</f>
-        <v>-0.329613557063189</v>
+        <v>-0.337828327483785</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>544</v>
@@ -45856,7 +45856,7 @@
       </c>
       <c r="B8" s="28" t="n">
         <f aca="false">F61</f>
-        <v>163.315119093162</v>
+        <v>161.313890960198</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>546</v>
@@ -45868,7 +45868,7 @@
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">F68</f>
-        <v>163.315119093162</v>
+        <v>161.313890960198</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>37</v>
@@ -45880,7 +45880,7 @@
       </c>
       <c r="B10" s="28" t="n">
         <f aca="false">F75</f>
-        <v>118.019126226154</v>
+        <v>116.572945389113</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>37</v>
@@ -46942,7 +46942,7 @@
       </c>
       <c r="C61" s="34" t="n">
         <f aca="false">PL!E12</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D61" s="33" t="str">
         <f aca="false">"規則值："&amp;D55</f>
@@ -46954,11 +46954,11 @@
       </c>
       <c r="F61" s="27" t="n">
         <f aca="false">C61*E61</f>
-        <v>163.315119093162</v>
+        <v>161.313890960198</v>
       </c>
       <c r="G61" s="36" t="n">
         <f aca="false">F61/px-1</f>
-        <v>-0.290242854875437</v>
+        <v>-0.298940065362025</v>
       </c>
       <c r="H61" s="33"/>
     </row>
@@ -46971,7 +46971,7 @@
       </c>
       <c r="C62" s="13" t="n">
         <f aca="false">PL!E12</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>630</v>
@@ -46982,11 +46982,11 @@
       </c>
       <c r="F62" s="28" t="n">
         <f aca="false">C62*E62</f>
-        <v>118.019126226154</v>
+        <v>116.572945389113</v>
       </c>
       <c r="G62" s="21" t="n">
         <f aca="false">F62/px-1</f>
-        <v>-0.487096365814195</v>
+        <v>-0.493381375970827</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46998,7 +46998,7 @@
       </c>
       <c r="C63" s="13" t="n">
         <f aca="false">PL!E12</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>631</v>
@@ -47009,11 +47009,11 @@
       </c>
       <c r="F63" s="28" t="n">
         <f aca="false">C63*E63</f>
-        <v>163.315119093162</v>
+        <v>161.313890960198</v>
       </c>
       <c r="G63" s="21" t="n">
         <f aca="false">F63/px-1</f>
-        <v>-0.290242854875437</v>
+        <v>-0.298940065362025</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47025,7 +47025,7 @@
       </c>
       <c r="C64" s="13" t="n">
         <f aca="false">PL!E12</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>632</v>
@@ -47036,11 +47036,11 @@
       </c>
       <c r="F64" s="28" t="n">
         <f aca="false">C64*E64</f>
-        <v>198.636010337613</v>
+        <v>196.201967645702</v>
       </c>
       <c r="G64" s="21" t="n">
         <f aca="false">F64/px-1</f>
-        <v>-0.136740502661395</v>
+        <v>-0.147318697758793</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47052,7 +47052,7 @@
       </c>
       <c r="C65" s="13" t="n">
         <f aca="false">PL!F12</f>
-        <v>10.6834549282617</v>
+        <v>10.4327111800435</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>630</v>
@@ -47063,11 +47063,11 @@
       </c>
       <c r="F65" s="28" t="n">
         <f aca="false">C65*E65</f>
-        <v>133.838103355983</v>
+        <v>130.696884722569</v>
       </c>
       <c r="G65" s="21" t="n">
         <f aca="false">F65/px-1</f>
-        <v>-0.418348094932711</v>
+        <v>-0.43199963180109</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47079,7 +47079,7 @@
       </c>
       <c r="C66" s="13" t="n">
         <f aca="false">PL!F12</f>
-        <v>10.6834549282617</v>
+        <v>10.4327111800435</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>631</v>
@@ -47090,11 +47090,11 @@
       </c>
       <c r="F66" s="28" t="n">
         <f aca="false">C66*E66</f>
-        <v>185.205453452523</v>
+        <v>180.858628394433</v>
       </c>
       <c r="G66" s="21" t="n">
         <f aca="false">F66/px-1</f>
-        <v>-0.195108850706116</v>
+        <v>-0.213999876599596</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47106,7 +47106,7 @@
       </c>
       <c r="C67" s="13" t="n">
         <f aca="false">PL!F12</f>
-        <v>10.6834549282617</v>
+        <v>10.4327111800435</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>632</v>
@@ -47117,11 +47117,11 @@
       </c>
       <c r="F67" s="28" t="n">
         <f aca="false">C67*E67</f>
-        <v>225.260665214908</v>
+        <v>219.97373286003</v>
       </c>
       <c r="G67" s="21" t="n">
         <f aca="false">F67/px-1</f>
-        <v>-0.0210314419169573</v>
+        <v>-0.0440081144718403</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47133,7 +47133,7 @@
       </c>
       <c r="C68" s="34" t="n">
         <f aca="false">PL!E22</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D68" s="33" t="str">
         <f aca="false">"規則值："&amp;D56</f>
@@ -47145,11 +47145,11 @@
       </c>
       <c r="F68" s="27" t="n">
         <f aca="false">C68*E68</f>
-        <v>163.315119093162</v>
+        <v>161.313890960198</v>
       </c>
       <c r="G68" s="36" t="n">
         <f aca="false">F68/px-1</f>
-        <v>-0.290242854875437</v>
+        <v>-0.298940065362025</v>
       </c>
       <c r="H68" s="33"/>
     </row>
@@ -47162,7 +47162,7 @@
       </c>
       <c r="C69" s="13" t="n">
         <f aca="false">PL!E22</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>630</v>
@@ -47173,11 +47173,11 @@
       </c>
       <c r="F69" s="28" t="n">
         <f aca="false">C69*E69</f>
-        <v>118.019126226154</v>
+        <v>116.572945389113</v>
       </c>
       <c r="G69" s="21" t="n">
         <f aca="false">F69/px-1</f>
-        <v>-0.487096365814195</v>
+        <v>-0.493381375970827</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47189,7 +47189,7 @@
       </c>
       <c r="C70" s="13" t="n">
         <f aca="false">PL!E22</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>631</v>
@@ -47200,11 +47200,11 @@
       </c>
       <c r="F70" s="28" t="n">
         <f aca="false">C70*E70</f>
-        <v>163.315119093162</v>
+        <v>161.313890960198</v>
       </c>
       <c r="G70" s="21" t="n">
         <f aca="false">F70/px-1</f>
-        <v>-0.290242854875437</v>
+        <v>-0.298940065362025</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47216,7 +47216,7 @@
       </c>
       <c r="C71" s="13" t="n">
         <f aca="false">PL!E22</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>632</v>
@@ -47227,11 +47227,11 @@
       </c>
       <c r="F71" s="28" t="n">
         <f aca="false">C71*E71</f>
-        <v>198.636010337613</v>
+        <v>196.201967645702</v>
       </c>
       <c r="G71" s="21" t="n">
         <f aca="false">F71/px-1</f>
-        <v>-0.136740502661395</v>
+        <v>-0.147318697758793</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47243,7 +47243,7 @@
       </c>
       <c r="C72" s="13" t="n">
         <f aca="false">PL!F22</f>
-        <v>10.0226796657799</v>
+        <v>9.7875303113938</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>630</v>
@@ -47254,11 +47254,11 @@
       </c>
       <c r="F72" s="28" t="n">
         <f aca="false">C72*E72</f>
-        <v>125.560171875114</v>
+        <v>122.614313647812</v>
       </c>
       <c r="G72" s="21" t="n">
         <f aca="false">F72/px-1</f>
-        <v>-0.454323459908242</v>
+        <v>-0.467125972847405</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47270,7 +47270,7 @@
       </c>
       <c r="C73" s="13" t="n">
         <f aca="false">PL!F22</f>
-        <v>10.0226796657799</v>
+        <v>9.7875303113938</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>631</v>
@@ -47281,11 +47281,11 @@
       </c>
       <c r="F73" s="28" t="n">
         <f aca="false">C73*E73</f>
-        <v>173.750434178336</v>
+        <v>169.673949267734</v>
       </c>
       <c r="G73" s="21" t="n">
         <f aca="false">F73/px-1</f>
-        <v>-0.244891637643042</v>
+        <v>-0.262607782408803</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47297,7 +47297,7 @@
       </c>
       <c r="C74" s="13" t="n">
         <f aca="false">PL!F22</f>
-        <v>10.0226796657799</v>
+        <v>9.7875303113938</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>632</v>
@@ -47308,11 +47308,11 @@
       </c>
       <c r="F74" s="28" t="n">
         <f aca="false">C74*E74</f>
-        <v>211.328217688927</v>
+        <v>206.370093154348</v>
       </c>
       <c r="G74" s="21" t="n">
         <f aca="false">F74/px-1</f>
-        <v>-0.0815809748416919</v>
+        <v>-0.103128669472628</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47324,7 +47324,7 @@
       </c>
       <c r="C75" s="34" t="n">
         <f aca="false">PL!E32</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D75" s="33" t="str">
         <f aca="false">"規則值："&amp;D57</f>
@@ -47336,11 +47336,11 @@
       </c>
       <c r="F75" s="27" t="n">
         <f aca="false">C75*E75</f>
-        <v>118.019126226154</v>
+        <v>116.572945389113</v>
       </c>
       <c r="G75" s="36" t="n">
         <f aca="false">F75/px-1</f>
-        <v>-0.487096365814195</v>
+        <v>-0.493381375970827</v>
       </c>
       <c r="H75" s="33"/>
     </row>
@@ -47353,7 +47353,7 @@
       </c>
       <c r="C76" s="13" t="n">
         <f aca="false">PL!E32</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>630</v>
@@ -47364,11 +47364,11 @@
       </c>
       <c r="F76" s="28" t="n">
         <f aca="false">C76*E76</f>
-        <v>118.019126226154</v>
+        <v>116.572945389113</v>
       </c>
       <c r="G76" s="21" t="n">
         <f aca="false">F76/px-1</f>
-        <v>-0.487096365814195</v>
+        <v>-0.493381375970827</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47380,7 +47380,7 @@
       </c>
       <c r="C77" s="13" t="n">
         <f aca="false">PL!E32</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>631</v>
@@ -47391,11 +47391,11 @@
       </c>
       <c r="F77" s="28" t="n">
         <f aca="false">C77*E77</f>
-        <v>163.315119093162</v>
+        <v>161.313890960198</v>
       </c>
       <c r="G77" s="21" t="n">
         <f aca="false">F77/px-1</f>
-        <v>-0.290242854875437</v>
+        <v>-0.298940065362025</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47407,7 +47407,7 @@
       </c>
       <c r="C78" s="13" t="n">
         <f aca="false">PL!E32</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>632</v>
@@ -47418,11 +47418,11 @@
       </c>
       <c r="F78" s="28" t="n">
         <f aca="false">C78*E78</f>
-        <v>198.636010337613</v>
+        <v>196.201967645702</v>
       </c>
       <c r="G78" s="21" t="n">
         <f aca="false">F78/px-1</f>
-        <v>-0.136740502661395</v>
+        <v>-0.147318697758793</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47434,7 +47434,7 @@
       </c>
       <c r="C79" s="13" t="n">
         <f aca="false">PL!F32</f>
-        <v>8.74332917812638</v>
+        <v>8.54025887177551</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>630</v>
@@ -47445,11 +47445,11 @@
       </c>
       <c r="F79" s="28" t="n">
         <f aca="false">C79*E79</f>
-        <v>109.532974311697</v>
+        <v>106.988989726896</v>
       </c>
       <c r="G79" s="21" t="n">
         <f aca="false">F79/px-1</f>
-        <v>-0.523976643582367</v>
+        <v>-0.535032639170379</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47461,7 +47461,7 @@
       </c>
       <c r="C80" s="13" t="n">
         <f aca="false">PL!F32</f>
-        <v>8.74332917812638</v>
+        <v>8.54025887177551</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>631</v>
@@ -47472,11 +47472,11 @@
       </c>
       <c r="F80" s="28" t="n">
         <f aca="false">C80*E80</f>
-        <v>151.571963937985</v>
+        <v>148.051592632728</v>
       </c>
       <c r="G80" s="21" t="n">
         <f aca="false">F80/px-1</f>
-        <v>-0.34127786206873</v>
+        <v>-0.356577172391446</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47488,7 +47488,7 @@
       </c>
       <c r="C81" s="13" t="n">
         <f aca="false">PL!F32</f>
-        <v>8.74332917812638</v>
+        <v>8.54025887177551</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>632</v>
@@ -47499,11 +47499,11 @@
       </c>
       <c r="F81" s="28" t="n">
         <f aca="false">C81*E81</f>
-        <v>184.353110494952</v>
+        <v>180.071372742403</v>
       </c>
       <c r="G81" s="21" t="n">
         <f aca="false">F81/px-1</f>
-        <v>-0.198813079117983</v>
+        <v>-0.217421239711417</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47576,15 +47576,15 @@
       </c>
       <c r="B89" s="30" t="n">
         <f aca="false">px/PL!E12</f>
-        <v>24.4248708004575</v>
+        <v>24.7278809026808</v>
       </c>
       <c r="C89" s="30" t="n">
         <f aca="false">px/PL!E22</f>
-        <v>24.4248708004575</v>
+        <v>24.7278809026808</v>
       </c>
       <c r="D89" s="30" t="n">
         <f aca="false">px/PL!E32</f>
-        <v>24.4248708004575</v>
+        <v>24.7278809026808</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>641</v>
@@ -47596,15 +47596,15 @@
       </c>
       <c r="B90" s="30" t="n">
         <f aca="false">px/PL!F12</f>
-        <v>21.5379763892016</v>
+        <v>22.0556283049562</v>
       </c>
       <c r="C90" s="30" t="n">
         <f aca="false">px/PL!F22</f>
-        <v>22.9579321771224</v>
+        <v>23.5095057363079</v>
       </c>
       <c r="D90" s="30" t="n">
         <f aca="false">px/PL!F32</f>
-        <v>26.3172065596767</v>
+        <v>26.9429771924657</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>641</v>
@@ -47616,7 +47616,7 @@
       </c>
       <c r="B91" s="13" t="n">
         <f aca="false">B89/E55</f>
-        <v>1.4089326283915</v>
+        <v>1.42641156710289</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>644</v>
@@ -47663,15 +47663,15 @@
       </c>
       <c r="B98" s="13" t="n">
         <f aca="false">PL!E120</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="C98" s="13" t="n">
         <f aca="false">PL!E127</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D98" s="13" t="n">
         <f aca="false">PL!E134</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47680,15 +47680,15 @@
       </c>
       <c r="B99" s="13" t="n">
         <f aca="false">PL!F120</f>
-        <v>10.6834549282617</v>
+        <v>10.4327111800435</v>
       </c>
       <c r="C99" s="13" t="n">
         <f aca="false">PL!F127</f>
-        <v>10.0226796657799</v>
+        <v>9.7875303113938</v>
       </c>
       <c r="D99" s="13" t="n">
         <f aca="false">PL!F134</f>
-        <v>8.74332917812638</v>
+        <v>8.54025887177551</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47697,15 +47697,15 @@
       </c>
       <c r="B100" s="13" t="n">
         <f aca="false">PL!G120</f>
-        <v>12.2005985188508</v>
+        <v>11.9225061764723</v>
       </c>
       <c r="C100" s="13" t="n">
         <f aca="false">PL!G127</f>
-        <v>10.1986672192108</v>
+        <v>9.96585757437253</v>
       </c>
       <c r="D100" s="13" t="n">
         <f aca="false">PL!G134</f>
-        <v>7.6521234109224</v>
+        <v>7.4780043238856</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47714,15 +47714,15 @@
       </c>
       <c r="B101" s="13" t="n">
         <f aca="false">PL!H120</f>
-        <v>13.2460463752907</v>
+        <v>12.9465674866598</v>
       </c>
       <c r="C101" s="13" t="n">
         <f aca="false">PL!H127</f>
-        <v>9.81001834146964</v>
+        <v>9.59503114507806</v>
       </c>
       <c r="D101" s="13" t="n">
         <f aca="false">PL!H134</f>
-        <v>6.52709862107943</v>
+        <v>6.39165757297761</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47731,15 +47731,15 @@
       </c>
       <c r="B102" s="13" t="n">
         <f aca="false">PL!I120</f>
-        <v>14.2109429900017</v>
+        <v>13.8909750792803</v>
       </c>
       <c r="C102" s="13" t="n">
         <f aca="false">PL!I127</f>
-        <v>9.52597975580514</v>
+        <v>9.32499963383572</v>
       </c>
       <c r="D102" s="13" t="n">
         <f aca="false">PL!I134</f>
-        <v>5.76497049049811</v>
+        <v>5.65728001576393</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47748,15 +47748,15 @@
       </c>
       <c r="B103" s="13" t="n">
         <f aca="false">PL!J120</f>
-        <v>15.0635995694018</v>
+        <v>14.7244335840371</v>
       </c>
       <c r="C103" s="13" t="n">
         <f aca="false">PL!J127</f>
-        <v>9.33341806392709</v>
+        <v>9.14338604616758</v>
       </c>
       <c r="D103" s="13" t="n">
         <f aca="false">PL!J134</f>
-        <v>5.25140808532493</v>
+        <v>5.1652485021189</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47785,15 +47785,15 @@
       </c>
       <c r="B106" s="13" t="n">
         <f aca="false">B98*(1-$B$105)</f>
-        <v>8.75187727807688</v>
+        <v>8.64463366755026</v>
       </c>
       <c r="C106" s="13" t="n">
         <f aca="false">C98*(1-$B$105)</f>
-        <v>8.75187727807688</v>
+        <v>8.64463366755026</v>
       </c>
       <c r="D106" s="13" t="n">
         <f aca="false">D98*(1-$B$105)</f>
-        <v>8.75187727807688</v>
+        <v>8.64463366755026</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47802,15 +47802,15 @@
       </c>
       <c r="B107" s="13" t="n">
         <f aca="false">B99*(1-$B$105)</f>
-        <v>9.92495617581144</v>
+        <v>9.69201461064031</v>
       </c>
       <c r="C107" s="13" t="n">
         <f aca="false">C99*(1-$B$105)</f>
-        <v>9.31109431499684</v>
+        <v>9.09263998044642</v>
       </c>
       <c r="D107" s="13" t="n">
         <f aca="false">D99*(1-$B$105)</f>
-        <v>8.12257453289199</v>
+        <v>7.93392171367998</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47819,15 +47819,15 @@
       </c>
       <c r="B108" s="13" t="n">
         <f aca="false">B100*(1-$B$105)</f>
-        <v>11.3343863414386</v>
+        <v>11.0760378643337</v>
       </c>
       <c r="C108" s="13" t="n">
         <f aca="false">C100*(1-$B$105)</f>
-        <v>9.47458718944791</v>
+        <v>9.2583064508814</v>
       </c>
       <c r="D108" s="13" t="n">
         <f aca="false">D100*(1-$B$105)</f>
-        <v>7.10884166360806</v>
+        <v>6.94708459908009</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47836,15 +47836,15 @@
       </c>
       <c r="B109" s="13" t="n">
         <f aca="false">B101*(1-$B$105)</f>
-        <v>12.3056099979183</v>
+        <v>12.0273933662012</v>
       </c>
       <c r="C109" s="13" t="n">
         <f aca="false">C101*(1-$B$105)</f>
-        <v>9.11353141626768</v>
+        <v>8.91380777659542</v>
       </c>
       <c r="D109" s="13" t="n">
         <f aca="false">D101*(1-$B$105)</f>
-        <v>6.06369083825519</v>
+        <v>5.93786576800937</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47853,15 +47853,15 @@
       </c>
       <c r="B110" s="13" t="n">
         <f aca="false">B102*(1-$B$105)</f>
-        <v>13.2020013506689</v>
+        <v>12.9047503665164</v>
       </c>
       <c r="C110" s="13" t="n">
         <f aca="false">C102*(1-$B$105)</f>
-        <v>8.84965886437418</v>
+        <v>8.66294783164646</v>
       </c>
       <c r="D110" s="13" t="n">
         <f aca="false">D102*(1-$B$105)</f>
-        <v>5.35567191112302</v>
+        <v>5.2556271924935</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47870,15 +47870,15 @@
       </c>
       <c r="B111" s="13" t="n">
         <f aca="false">B103*(1-$B$105)</f>
-        <v>13.9941214317091</v>
+        <v>13.6790353885073</v>
       </c>
       <c r="C111" s="13" t="n">
         <f aca="false">C103*(1-$B$105)</f>
-        <v>8.67076857412041</v>
+        <v>8.49422835740879</v>
       </c>
       <c r="D111" s="13" t="n">
         <f aca="false">D103*(1-$B$105)</f>
-        <v>4.87857116055923</v>
+        <v>4.79852869366175</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47887,15 +47887,15 @@
       </c>
       <c r="B112" s="13" t="n">
         <f aca="false">SUMPRODUCT(B106:B111,1/(1+tp_r)^{1;2;3;4;5;6})+B111*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
-        <v>186.097495333471</v>
+        <v>181.978063859518</v>
       </c>
       <c r="C112" s="13" t="n">
         <f aca="false">SUMPRODUCT(C106:C111,1/(1+tp_r)^{1;2;3;4;5;6})+C111*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
-        <v>124.220460317705</v>
+        <v>121.700623890309</v>
       </c>
       <c r="D112" s="13" t="n">
         <f aca="false">SUMPRODUCT(D106:D111,1/(1+tp_r)^{1;2;3;4;5;6})+D111*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
-        <v>77.9639491930723</v>
+        <v>76.6126184149461</v>
       </c>
       <c r="E112" s="8" t="s">
         <v>663</v>
@@ -47907,15 +47907,15 @@
       </c>
       <c r="B113" s="13" t="n">
         <f aca="false">B112*(1+tp_r)</f>
-        <v>204.707244866818</v>
+        <v>200.17587024547</v>
       </c>
       <c r="C113" s="13" t="n">
         <f aca="false">C112*(1+tp_r)</f>
-        <v>136.642506349476</v>
+        <v>133.87068627934</v>
       </c>
       <c r="D113" s="13" t="n">
         <f aca="false">D112*(1+tp_r)</f>
-        <v>85.7603441123795</v>
+        <v>84.2738802564408</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47924,7 +47924,7 @@
       </c>
       <c r="B114" s="34" t="n">
         <f aca="false">tp_wA*B113+tp_wB*C113+tp_wC*D113</f>
-        <v>146.885495457259</v>
+        <v>143.842880264599</v>
       </c>
       <c r="E114" s="8" t="s">
         <v>666</v>
@@ -48053,7 +48053,7 @@
       </c>
       <c r="B123" s="13" t="n">
         <f aca="false">tp_wA*(8/12*B99+4/12*B100)+tp_wB*(8/12*C99+4/12*C100)+tp_wC*(8/12*D99+4/12*D100)</f>
-        <v>10.0733407138109</v>
+        <v>9.83951402434505</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>687</v>
@@ -48065,7 +48065,7 @@
       </c>
       <c r="B124" s="34" t="n">
         <f aca="false">B122*B123</f>
-        <v>258.83448964137</v>
+        <v>252.826312855546</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>689</v>
@@ -48095,7 +48095,7 @@
       </c>
       <c r="B128" s="34" t="n">
         <f aca="false">tp_w_dcf*B114+(1-tp_w_dcf)*tp_comp_adj</f>
-        <v>195.133733060084</v>
+        <v>190.787682307904</v>
       </c>
       <c r="E128" s="8" t="s">
         <v>692</v>
@@ -48107,7 +48107,7 @@
       </c>
       <c r="B129" s="13" t="n">
         <f aca="false">B124</f>
-        <v>258.83448964137</v>
+        <v>252.826312855546</v>
       </c>
       <c r="E129" s="5" t="s">
         <v>694</v>
@@ -48131,7 +48131,7 @@
       </c>
       <c r="B131" s="10" t="n">
         <f aca="false">B128/px-1</f>
-        <v>-0.151961177487684</v>
+        <v>-0.170848838296812</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>697</v>
@@ -48143,7 +48143,7 @@
       </c>
       <c r="B132" s="10" t="n">
         <f aca="false">B129/px-1</f>
-        <v>0.124878268758672</v>
+        <v>0.0987671136703436</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48152,7 +48152,7 @@
       </c>
       <c r="B133" s="10" t="n">
         <f aca="false">B123/cons_feps-1</f>
-        <v>-0.170918459768652</v>
+        <v>-0.190163454786416</v>
       </c>
       <c r="E133" s="5" t="s">
         <v>700</v>
@@ -48177,7 +48177,7 @@
       </c>
       <c r="B135" s="37" t="str">
         <f aca="false">TEXT(D113,"0.00")&amp;"～"&amp;TEXT(B113,"0.00")</f>
-        <v>85.76～204.71</v>
+        <v>84.27～200.18</v>
       </c>
       <c r="E135" s="8" t="s">
         <v>703</v>
@@ -48189,15 +48189,15 @@
       </c>
       <c r="B136" s="21" t="n">
         <f aca="false">IF(px/B99&lt;MIN(E32:E41),0,IF(px/B99&gt;MAX(E32:E41),1,PERCENTRANK(E32:E41,px/B99)))</f>
-        <v>0.767</v>
+        <v>0.782</v>
       </c>
       <c r="C136" s="21" t="n">
         <f aca="false">IF(px/C99&lt;MIN(E32:E41),0,IF(px/C99&gt;MAX(E32:E41),1,PERCENTRANK(E32:E41,px/C99)))</f>
-        <v>0.802</v>
+        <v>0.814</v>
       </c>
       <c r="D136" s="21" t="n">
         <f aca="false">IF(px/D99&lt;MIN(E32:E41),0,IF(px/D99&gt;MAX(E32:E41),1,PERCENTRANK(E32:E41,px/D99)))</f>
-        <v>0.876</v>
+        <v>0.89</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>705</v>
@@ -48660,7 +48660,7 @@
       </c>
       <c r="B158" s="34" t="n">
         <f aca="false">Val!$B$124*B157</f>
-        <v>243.381970662909</v>
+        <v>237.732484351208</v>
       </c>
       <c r="E158" s="5" t="s">
         <v>751</v>
@@ -48743,27 +48743,27 @@
       </c>
       <c r="C5" s="22" t="n">
         <f aca="false">PL!E5</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">C5/B5-1</f>
-        <v>-0.022257910041583</v>
+        <v>-0.03161980047631</v>
       </c>
       <c r="E5" s="22" t="n">
         <f aca="false">PL!E15</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F5" s="10" t="n">
         <f aca="false">E5/B5-1</f>
-        <v>-0.022257910041583</v>
+        <v>-0.03161980047631</v>
       </c>
       <c r="G5" s="22" t="n">
         <f aca="false">PL!E25</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="H5" s="10" t="n">
         <f aca="false">G5/B5-1</f>
-        <v>-0.022257910041583</v>
+        <v>-0.03161980047631</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>763</v>
@@ -48782,27 +48782,27 @@
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">PL!E12</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D6" s="10" t="n">
         <f aca="false">C6/B6-1</f>
-        <v>-0.02173152963261</v>
+        <v>-0.0337190198010738</v>
       </c>
       <c r="E6" s="22" t="n">
         <f aca="false">PL!E22</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F6" s="10" t="n">
         <f aca="false">E6/B6-1</f>
-        <v>-0.02173152963261</v>
+        <v>-0.0337190198010738</v>
       </c>
       <c r="G6" s="22" t="n">
         <f aca="false">PL!E32</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="H6" s="10" t="n">
         <f aca="false">G6/B6-1</f>
-        <v>-0.02173152963261</v>
+        <v>-0.0337190198010738</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>765</v>
@@ -48821,27 +48821,27 @@
       </c>
       <c r="C7" s="22" t="n">
         <f aca="false">PL!E12</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">C7/B7-1</f>
-        <v>-0.00625259813945511</v>
+        <v>-0.018429763785268</v>
       </c>
       <c r="E7" s="22" t="n">
         <f aca="false">PL!E22</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F7" s="10" t="n">
         <f aca="false">E7/B7-1</f>
-        <v>-0.00625259813945511</v>
+        <v>-0.018429763785268</v>
       </c>
       <c r="G7" s="22" t="n">
         <f aca="false">PL!E32</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="H7" s="10" t="n">
         <f aca="false">G7/B7-1</f>
-        <v>-0.00625259813945511</v>
+        <v>-0.018429763785268</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>768</v>
@@ -48857,27 +48857,27 @@
       </c>
       <c r="C8" s="22" t="n">
         <f aca="false">PL!F5</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">C8/B8-1</f>
-        <v>-0.115486244517581</v>
+        <v>-0.131958937150662</v>
       </c>
       <c r="E8" s="22" t="n">
         <f aca="false">PL!F15</f>
-        <v>35.8954420982568</v>
+        <v>35.2328074932868</v>
       </c>
       <c r="F8" s="10" t="n">
         <f aca="false">E8/B8-1</f>
-        <v>-0.158963399759682</v>
+        <v>-0.174489046549045</v>
       </c>
       <c r="G8" s="22" t="n">
         <f aca="false">PL!F25</f>
-        <v>32.2748375498097</v>
+        <v>31.6964900665919</v>
       </c>
       <c r="H8" s="10" t="n">
         <f aca="false">G8/B8-1</f>
-        <v>-0.243794809048507</v>
+        <v>-0.257345593566263</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>770</v>
@@ -48893,27 +48893,27 @@
       </c>
       <c r="C9" s="22" t="n">
         <f aca="false">PL!F12</f>
-        <v>10.6834549282617</v>
+        <v>10.4327111800435</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">C9/B9-1</f>
-        <v>-0.120703298085458</v>
+        <v>-0.141340643617822</v>
       </c>
       <c r="E9" s="22" t="n">
         <f aca="false">PL!F22</f>
-        <v>10.0226796657799</v>
+        <v>9.7875303113938</v>
       </c>
       <c r="F9" s="10" t="n">
         <f aca="false">E9/B9-1</f>
-        <v>-0.175088093351446</v>
+        <v>-0.194441949679523</v>
       </c>
       <c r="G9" s="22" t="n">
         <f aca="false">PL!F32</f>
-        <v>8.74332917812638</v>
+        <v>8.54025887177551</v>
       </c>
       <c r="H9" s="10" t="n">
         <f aca="false">G9/B9-1</f>
-        <v>-0.280384429783837</v>
+        <v>-0.297098035244814</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>772</v>
@@ -49012,27 +49012,27 @@
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">PL!E8</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="D13" s="10" t="n">
         <f aca="false">C13-B13</f>
-        <v>0.000503854044350605</v>
+        <v>1.1614612239752E-006</v>
       </c>
       <c r="E13" s="10" t="n">
         <f aca="false">PL!E18</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F13" s="10" t="n">
         <f aca="false">E13-B13</f>
-        <v>0.000503854044350605</v>
+        <v>1.1614612239752E-006</v>
       </c>
       <c r="G13" s="10" t="n">
         <f aca="false">PL!E28</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="H13" s="10" t="n">
         <f aca="false">G13-B13</f>
-        <v>0.000503854044350605</v>
+        <v>1.1614612239752E-006</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>780</v>
@@ -49051,27 +49051,27 @@
       </c>
       <c r="C14" s="10" t="n">
         <f aca="false">PL!G8</f>
-        <v>0.534964444590398</v>
+        <v>0.533996833374025</v>
       </c>
       <c r="D14" s="10" t="n">
         <f aca="false">C14-B14</f>
-        <v>-0.0150355554096018</v>
+        <v>-0.0160031666259752</v>
       </c>
       <c r="E14" s="10" t="n">
         <f aca="false">PL!G18</f>
-        <v>0.527515070070121</v>
+        <v>0.526567823481368</v>
       </c>
       <c r="F14" s="10" t="n">
         <f aca="false">E14-B14</f>
-        <v>-0.0224849299298786</v>
+        <v>-0.0234321765186321</v>
       </c>
       <c r="G14" s="10" t="n">
         <f aca="false">PL!G28</f>
-        <v>0.515957452643486</v>
+        <v>0.515054115267156</v>
       </c>
       <c r="H14" s="10" t="n">
         <f aca="false">G14-B14</f>
-        <v>-0.034042547356514</v>
+        <v>-0.0349458847328437</v>
       </c>
       <c r="I14" s="8" t="s">
         <v>783</v>
@@ -49092,27 +49092,27 @@
       </c>
       <c r="C16" s="22" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="D16" s="10" t="n">
         <f aca="false">C16/B16-1</f>
-        <v>0.00746484238791623</v>
+        <v>0.0325484797374194</v>
       </c>
       <c r="E16" s="22" t="n">
         <f aca="false">wfeB_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="F16" s="10" t="n">
         <f aca="false">E16/B16-1</f>
-        <v>0.00746484238791623</v>
+        <v>0.0325484797374194</v>
       </c>
       <c r="G16" s="22" t="n">
         <f aca="false">wfeC_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="H16" s="10" t="n">
         <f aca="false">G16/B16-1</f>
-        <v>0.00746484238791623</v>
+        <v>0.0325484797374194</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>775</v>
@@ -49170,27 +49170,27 @@
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">wfeA_26/wfeA_25-1</f>
-        <v>0.33585357367496</v>
+        <v>0.369113361197351</v>
       </c>
       <c r="D18" s="10" t="n">
         <f aca="false">C18-B18</f>
-        <v>-0.073237335415949</v>
+        <v>-0.0399775478935587</v>
       </c>
       <c r="E18" s="10" t="n">
         <f aca="false">wfeB_26/wfeB_25-1</f>
-        <v>0.33585357367496</v>
+        <v>0.369113361197351</v>
       </c>
       <c r="F18" s="10" t="n">
         <f aca="false">E18-B18</f>
-        <v>-0.073237335415949</v>
+        <v>-0.0399775478935587</v>
       </c>
       <c r="G18" s="10" t="n">
         <f aca="false">wfeC_26/wfeC_25-1</f>
-        <v>0.33585357367496</v>
+        <v>0.369113361197351</v>
       </c>
       <c r="H18" s="10" t="n">
         <f aca="false">G18-B18</f>
-        <v>-0.073237335415949</v>
+        <v>-0.0399775478935587</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>790</v>
@@ -49207,7 +49207,7 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">(q1_rev+g_q2rev)/PL!E5</f>
-        <v>0.486078139738043</v>
+        <v>0.490777337727822</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49216,7 +49216,7 @@
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">(q1_eps+g_q2eps)/PL!E12</f>
-        <v>0.47979320303376</v>
+        <v>0.485745422338624</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49225,7 +49225,7 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">Units!E24</f>
-        <v>0.12696721619429</v>
+        <v>0.123882809341932</v>
       </c>
     </row>
   </sheetData>
@@ -49292,11 +49292,11 @@
       </c>
       <c r="C4" s="22" t="n">
         <f aca="false">PL!E52</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="D4" s="13" t="n">
         <f aca="false">PL!E60</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="E4" s="10" t="n">
         <f aca="false">D4/D$4-1</f>
@@ -49304,11 +49304,11 @@
       </c>
       <c r="F4" s="22" t="n">
         <f aca="false">PL!F52</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G4" s="13" t="n">
         <f aca="false">PL!F60</f>
-        <v>10.6834549282617</v>
+        <v>10.4327111800435</v>
       </c>
       <c r="H4" s="10" t="n">
         <f aca="false">G4/G$4-1</f>
@@ -49324,27 +49324,27 @@
       </c>
       <c r="C5" s="22" t="n">
         <f aca="false">E62</f>
-        <v>34.3565327293558</v>
+        <v>34.0318417729205</v>
       </c>
       <c r="D5" s="13" t="n">
         <f aca="false">E70</f>
-        <v>9.33508563924802</v>
+        <v>9.22203477326255</v>
       </c>
       <c r="E5" s="10" t="n">
         <f aca="false">D5/D$4-1</f>
-        <v>-0.00909056649352635</v>
+        <v>-0.00894664253099753</v>
       </c>
       <c r="F5" s="22" t="n">
         <f aca="false">F62</f>
-        <v>36.958256662074</v>
+        <v>36.2765492804199</v>
       </c>
       <c r="G5" s="13" t="n">
         <f aca="false">F70</f>
-        <v>10.4007407077133</v>
+        <v>10.1581196740457</v>
       </c>
       <c r="H5" s="10" t="n">
         <f aca="false">G5/G$4-1</f>
-        <v>-0.0264628083748908</v>
+        <v>-0.026320244206799</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49356,27 +49356,27 @@
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">E92</f>
-        <v>34.848052397901</v>
+        <v>34.5101087493663</v>
       </c>
       <c r="D6" s="13" t="n">
         <f aca="false">E100</f>
-        <v>9.50642587596971</v>
+        <v>9.38859500441026</v>
       </c>
       <c r="E6" s="10" t="n">
         <f aca="false">D6/D$4-1</f>
-        <v>0.0090970177952483</v>
+        <v>0.00895288619105217</v>
       </c>
       <c r="F6" s="22" t="n">
         <f aca="false">F92</f>
-        <v>38.554888628888</v>
+        <v>37.830189577607</v>
       </c>
       <c r="G6" s="13" t="n">
         <f aca="false">F100</f>
-        <v>10.9707109219934</v>
+        <v>10.7117101698758</v>
       </c>
       <c r="H6" s="10" t="n">
         <f aca="false">G6/G$4-1</f>
-        <v>0.0268879305113052</v>
+        <v>0.0267427119391548</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49388,27 +49388,27 @@
       </c>
       <c r="C7" s="22" t="n">
         <f aca="false">E122</f>
-        <v>33.7667091271017</v>
+        <v>33.4579214011856</v>
       </c>
       <c r="D7" s="13" t="n">
         <f aca="false">E130</f>
-        <v>9.12980086684866</v>
+        <v>9.02247171394206</v>
       </c>
       <c r="E7" s="10" t="n">
         <f aca="false">D7/D$4-1</f>
-        <v>-0.0308813272199749</v>
+        <v>-0.0303928466311787</v>
       </c>
       <c r="F7" s="22" t="n">
         <f aca="false">F122</f>
-        <v>35.9761181939343</v>
+        <v>35.3208713798219</v>
       </c>
       <c r="G7" s="13" t="n">
         <f aca="false">F130</f>
-        <v>10.0513389058663</v>
+        <v>9.81875636680461</v>
       </c>
       <c r="H7" s="10" t="n">
         <f aca="false">G7/G$4-1</f>
-        <v>-0.0591677530012525</v>
+        <v>-0.0588490184999347</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49420,27 +49420,27 @@
       </c>
       <c r="C8" s="22" t="n">
         <f aca="false">E152</f>
-        <v>32.9311256905749</v>
+        <v>32.6448675412279</v>
       </c>
       <c r="D8" s="13" t="n">
         <f aca="false">E160</f>
-        <v>8.83959638702616</v>
+        <v>8.74034559664452</v>
       </c>
       <c r="E8" s="10" t="n">
         <f aca="false">D8/D$4-1</f>
-        <v>-0.0616862247661651</v>
+        <v>-0.0607117559230924</v>
       </c>
       <c r="F8" s="22" t="n">
         <f aca="false">F152</f>
-        <v>34.2011893038791</v>
+        <v>33.593750197234</v>
       </c>
       <c r="G8" s="13" t="n">
         <f aca="false">F160</f>
-        <v>9.4223195811866</v>
+        <v>9.20778805198647</v>
       </c>
       <c r="H8" s="10" t="n">
         <f aca="false">G8/G$4-1</f>
-        <v>-0.118045646800916</v>
+        <v>-0.117411774074617</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49452,27 +49452,27 @@
       </c>
       <c r="C9" s="22" t="n">
         <f aca="false">E182</f>
-        <v>32.8240051072656</v>
+        <v>32.5258195350291</v>
       </c>
       <c r="D9" s="13" t="n">
         <f aca="false">E190</f>
-        <v>8.80244559089416</v>
+        <v>8.6990952242787</v>
       </c>
       <c r="E9" s="10" t="n">
         <f aca="false">D9/D$4-1</f>
-        <v>-0.0656297423483399</v>
+        <v>-0.0651447602475304</v>
       </c>
       <c r="F9" s="22" t="n">
         <f aca="false">F182</f>
-        <v>37.5325172883164</v>
+        <v>36.8335047583975</v>
       </c>
       <c r="G9" s="13" t="n">
         <f aca="false">F190</f>
-        <v>10.6054664975495</v>
+        <v>10.356307781526</v>
       </c>
       <c r="H9" s="10" t="n">
         <f aca="false">G9/G$4-1</f>
-        <v>-0.00729992602916085</v>
+        <v>-0.00732344614922276</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49481,27 +49481,27 @@
       </c>
       <c r="C10" s="22" t="n">
         <f aca="false">E212</f>
-        <v>36.3805800199912</v>
+        <v>36.0161309872577</v>
       </c>
       <c r="D10" s="13" t="n">
         <f aca="false">E220</f>
-        <v>10.0421886237855</v>
+        <v>9.91457202604201</v>
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">D10/D$4-1</f>
-        <v>0.0659676648838963</v>
+        <v>0.0654774283399293</v>
       </c>
       <c r="F10" s="22" t="n">
         <f aca="false">F212</f>
-        <v>37.9695768796629</v>
+        <v>37.262480366422</v>
       </c>
       <c r="G10" s="13" t="n">
         <f aca="false">F220</f>
-        <v>10.761488075661</v>
+        <v>10.5091584738415</v>
       </c>
       <c r="H10" s="10" t="n">
         <f aca="false">G10/G$4-1</f>
-        <v>0.00730411163086586</v>
+        <v>0.00732765361551024</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49513,27 +49513,27 @@
       </c>
       <c r="C11" s="22" t="n">
         <f aca="false">E242</f>
-        <v>34.3633846136284</v>
+        <v>34.0320673111434</v>
       </c>
       <c r="D11" s="13" t="n">
         <f aca="false">E250</f>
-        <v>9.33747248234399</v>
+        <v>9.22211326382232</v>
       </c>
       <c r="E11" s="10" t="n">
         <f aca="false">D11/D$4-1</f>
-        <v>-0.0088372056319882</v>
+        <v>-0.008938207480089</v>
       </c>
       <c r="F11" s="22" t="n">
         <f aca="false">F242</f>
-        <v>37.2445622299896</v>
+        <v>36.5415077084098</v>
       </c>
       <c r="G11" s="13" t="n">
         <f aca="false">F250</f>
-        <v>10.5027704550673</v>
+        <v>10.2523655781138</v>
       </c>
       <c r="H11" s="10" t="n">
         <f aca="false">G11/G$4-1</f>
-        <v>-0.0169125507064567</v>
+        <v>-0.0172865517713754</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49542,27 +49542,27 @@
       </c>
       <c r="C12" s="22" t="n">
         <f aca="false">E272</f>
-        <v>34.8412005136284</v>
+        <v>34.5098832111434</v>
       </c>
       <c r="D12" s="13" t="n">
         <f aca="false">E280</f>
-        <v>9.50403569117335</v>
+        <v>9.38851640430933</v>
       </c>
       <c r="E12" s="10" t="n">
         <f aca="false">D12/D$4-1</f>
-        <v>0.00884330221575969</v>
+        <v>0.00894443936821454</v>
       </c>
       <c r="F12" s="22" t="n">
         <f aca="false">F272</f>
-        <v>38.2575319379896</v>
+        <v>37.5544774164097</v>
       </c>
       <c r="G12" s="13" t="n">
         <f aca="false">F280</f>
-        <v>10.8643796118699</v>
+        <v>10.6133015511075</v>
       </c>
       <c r="H12" s="10" t="n">
         <f aca="false">G12/G$4-1</f>
-        <v>0.0169350350446691</v>
+        <v>0.0173100134708446</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49571,11 +49571,11 @@
       </c>
       <c r="C13" s="22" t="n">
         <f aca="false">E302</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="D13" s="13" t="n">
         <f aca="false">E310</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="E13" s="10" t="n">
         <f aca="false">D13/D$4-1</f>
@@ -49583,15 +49583,15 @@
       </c>
       <c r="F13" s="22" t="n">
         <f aca="false">F302</f>
-        <v>37.5312517699896</v>
+        <v>36.8281972484098</v>
       </c>
       <c r="G13" s="13" t="n">
         <f aca="false">F310</f>
-        <v>10.6050149928985</v>
+        <v>10.3544177348403</v>
       </c>
       <c r="H13" s="10" t="n">
         <f aca="false">G13/G$4-1</f>
-        <v>-0.00734218807397669</v>
+        <v>-0.00750461158677074</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49600,11 +49600,11 @@
       </c>
       <c r="C14" s="22" t="n">
         <f aca="false">E332</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="D14" s="13" t="n">
         <f aca="false">E340</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="E14" s="10" t="n">
         <f aca="false">D14/D$4-1</f>
@@ -49612,15 +49612,15 @@
       </c>
       <c r="F14" s="22" t="n">
         <f aca="false">F332</f>
-        <v>37.9708423979896</v>
+        <v>37.2677878764097</v>
       </c>
       <c r="G14" s="13" t="n">
         <f aca="false">F340</f>
-        <v>10.7619400997283</v>
+        <v>10.5110507197992</v>
       </c>
       <c r="H14" s="10" t="n">
         <f aca="false">G14/G$4-1</f>
-        <v>0.00734642229443527</v>
+        <v>0.00750902985846991</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49632,27 +49632,27 @@
       </c>
       <c r="C15" s="22" t="n">
         <f aca="false">E362</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="D15" s="13" t="n">
         <f aca="false">E370</f>
-        <v>9.6623614529879</v>
+        <v>9.53988049664648</v>
       </c>
       <c r="E15" s="10" t="n">
         <f aca="false">D15/D$4-1</f>
-        <v>0.025649413805088</v>
+        <v>0.025210902854766</v>
       </c>
       <c r="F15" s="22" t="n">
         <f aca="false">F362</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G15" s="13" t="n">
         <f aca="false">F370</f>
-        <v>10.9967097375445</v>
+        <v>10.7307965587359</v>
       </c>
       <c r="H15" s="10" t="n">
         <f aca="false">G15/G$4-1</f>
-        <v>0.0293214892922131</v>
+        <v>0.0285721873775835</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49664,27 +49664,27 @@
       </c>
       <c r="C16" s="22" t="n">
         <f aca="false">E392</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="D16" s="13" t="n">
         <f aca="false">E400</f>
-        <v>9.25994886694476</v>
+        <v>9.14919446408203</v>
       </c>
       <c r="E16" s="10" t="n">
         <f aca="false">D16/D$4-1</f>
-        <v>-0.0170662551326853</v>
+        <v>-0.0167744847314771</v>
       </c>
       <c r="F16" s="22" t="n">
         <f aca="false">F392</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G16" s="13" t="n">
         <f aca="false">F400</f>
-        <v>10.4750257400788</v>
+        <v>10.2343752195125</v>
       </c>
       <c r="H16" s="10" t="n">
         <f aca="false">G16/G$4-1</f>
-        <v>-0.0195095303516039</v>
+        <v>-0.0190109701215866</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49693,23 +49693,23 @@
       </c>
       <c r="C17" s="22" t="n">
         <f aca="false">E422</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="D17" s="13" t="n">
         <f aca="false">E430</f>
-        <v>9.81560607375453</v>
+        <v>9.6953277607241</v>
       </c>
       <c r="E17" s="10" t="n">
         <f aca="false">D17/D$4-1</f>
-        <v>0.0419161676646709</v>
+        <v>0.0419161676646707</v>
       </c>
       <c r="F17" s="22" t="n">
         <f aca="false">F422</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G17" s="13" t="n">
         <f aca="false">F430</f>
-        <v>11.1312644162727</v>
+        <v>10.8700104510633</v>
       </c>
       <c r="H17" s="10" t="n">
         <f aca="false">G17/G$4-1</f>
@@ -49722,27 +49722,27 @@
       </c>
       <c r="C18" s="22" t="n">
         <f aca="false">E452</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="D18" s="13" t="n">
         <f aca="false">E460</f>
-        <v>9.13866772384042</v>
+        <v>9.02668446688106</v>
       </c>
       <c r="E18" s="10" t="n">
         <f aca="false">D18/D$4-1</f>
-        <v>-0.0299401197604788</v>
+        <v>-0.0299401197604791</v>
       </c>
       <c r="F18" s="22" t="n">
         <f aca="false">F452</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G18" s="13" t="n">
         <f aca="false">F460</f>
-        <v>10.3635910082538</v>
+        <v>10.1203545578865</v>
       </c>
       <c r="H18" s="10" t="n">
         <f aca="false">G18/G$4-1</f>
-        <v>-0.0299401197604789</v>
+        <v>-0.0299401197604791</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49751,11 +49751,11 @@
       </c>
       <c r="C19" s="22" t="n">
         <f aca="false">E482</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="D19" s="13" t="n">
         <f aca="false">E490</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="E19" s="10" t="n">
         <f aca="false">D19/D$4-1</f>
@@ -49763,15 +49763,15 @@
       </c>
       <c r="F19" s="22" t="n">
         <f aca="false">F482</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G19" s="13" t="n">
         <f aca="false">F490</f>
-        <v>10.5232031043378</v>
+        <v>10.2762205123428</v>
       </c>
       <c r="H19" s="10" t="n">
         <f aca="false">G19/G$4-1</f>
-        <v>-0.015</v>
+        <v>-0.0150000000000001</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49780,11 +49780,11 @@
       </c>
       <c r="C20" s="22" t="n">
         <f aca="false">E512</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="D20" s="13" t="n">
         <f aca="false">E520</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="E20" s="10" t="n">
         <f aca="false">D20/D$4-1</f>
@@ -49792,11 +49792,11 @@
       </c>
       <c r="F20" s="22" t="n">
         <f aca="false">F512</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G20" s="13" t="n">
         <f aca="false">F520</f>
-        <v>10.8486629941626</v>
+        <v>10.5940417653019</v>
       </c>
       <c r="H20" s="10" t="n">
         <f aca="false">G20/G$4-1</f>
@@ -49809,27 +49809,27 @@
       </c>
       <c r="C21" s="22" t="n">
         <f aca="false">E542</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="D21" s="13" t="n">
         <f aca="false">E550</f>
-        <v>9.3540853057912</v>
+        <v>9.23864577546889</v>
       </c>
       <c r="E21" s="10" t="n">
         <f aca="false">D21/D$4-1</f>
-        <v>-0.00707377205385262</v>
+        <v>-0.00716152786679669</v>
       </c>
       <c r="F21" s="22" t="n">
         <f aca="false">F542</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G21" s="13" t="n">
         <f aca="false">F550</f>
-        <v>10.6158000411076</v>
+        <v>10.3650562928894</v>
       </c>
       <c r="H21" s="10" t="n">
         <f aca="false">G21/G$4-1</f>
-        <v>-0.00633267867074583</v>
+        <v>-0.00648488067833175</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49838,27 +49838,27 @@
       </c>
       <c r="C22" s="22" t="n">
         <f aca="false">E572</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="D22" s="13" t="n">
         <f aca="false">E580</f>
-        <v>9.48736543348474</v>
+        <v>9.37192590316243</v>
       </c>
       <c r="E22" s="10" t="n">
         <f aca="false">D22/D$4-1</f>
-        <v>0.00707377205385296</v>
+        <v>0.00716152786679691</v>
       </c>
       <c r="F22" s="22" t="n">
         <f aca="false">F572</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G22" s="13" t="n">
         <f aca="false">F580</f>
-        <v>10.7511098154158</v>
+        <v>10.5003660671975</v>
       </c>
       <c r="H22" s="10" t="n">
         <f aca="false">G22/G$4-1</f>
-        <v>0.00633267867074605</v>
+        <v>0.00648488067833153</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49870,11 +49870,11 @@
       </c>
       <c r="C23" s="22" t="n">
         <f aca="false">PL!E76</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="D23" s="13" t="n">
         <f aca="false">PL!E84</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="E23" s="10" t="n">
         <f aca="false">D23/D$4-1</f>
@@ -49882,15 +49882,15 @@
       </c>
       <c r="F23" s="22" t="n">
         <f aca="false">PL!F76</f>
-        <v>35.8954420982568</v>
+        <v>35.2328074932868</v>
       </c>
       <c r="G23" s="13" t="n">
         <f aca="false">PL!F84</f>
-        <v>10.0226796657799</v>
+        <v>9.7875303113938</v>
       </c>
       <c r="H23" s="10" t="n">
         <f aca="false">G23/G$4-1</f>
-        <v>-0.0618503346453733</v>
+        <v>-0.0618421096410514</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49902,11 +49902,11 @@
       </c>
       <c r="C24" s="22" t="n">
         <f aca="false">PL!E100</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="D24" s="13" t="n">
         <f aca="false">PL!E108</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="E24" s="10" t="n">
         <f aca="false">D24/D$4-1</f>
@@ -49914,15 +49914,15 @@
       </c>
       <c r="F24" s="22" t="n">
         <f aca="false">PL!F100</f>
-        <v>32.2748375498097</v>
+        <v>31.6964900665919</v>
       </c>
       <c r="G24" s="13" t="n">
         <f aca="false">PL!F108</f>
-        <v>8.74332917812638</v>
+        <v>8.54025887177551</v>
       </c>
       <c r="H24" s="10" t="n">
         <f aca="false">G24/G$4-1</f>
-        <v>-0.18160096739894</v>
+        <v>-0.181396022146956</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50006,15 +50006,15 @@
       </c>
       <c r="E54" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift_lo)^1</f>
-        <v>5.77277679608639</v>
+        <v>5.42697805420094</v>
       </c>
       <c r="F54" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift_lo)^2</f>
-        <v>6.32675858233546</v>
+        <v>5.94777542825478</v>
       </c>
       <c r="G54" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift_lo)^3</f>
-        <v>6.43656882258251</v>
+        <v>6.05100785607899</v>
       </c>
       <c r="H54" s="8" t="s">
         <v>506</v>
@@ -50033,15 +50033,15 @@
       </c>
       <c r="E55" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift_lo)^1</f>
-        <v>5.86396121950692</v>
+        <v>5.56037804852178</v>
       </c>
       <c r="F55" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift_lo)^2</f>
-        <v>6.47176330515376</v>
+        <v>6.13671360879696</v>
       </c>
       <c r="G55" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift_lo)^3</f>
-        <v>6.70399960468704</v>
+        <v>6.35692680149323</v>
       </c>
       <c r="H55" s="8" t="s">
         <v>506</v>
@@ -50083,15 +50083,15 @@
       </c>
       <c r="E57" s="17" t="n">
         <f aca="false">SUM(E53:E56)</f>
-        <v>24.0844637587116</v>
+        <v>23.435081845841</v>
       </c>
       <c r="F57" s="17" t="n">
         <f aca="false">SUM(F53:F56)</f>
-        <v>26.5337462814363</v>
+        <v>25.8197134309988</v>
       </c>
       <c r="G57" s="17" t="n">
         <f aca="false">SUM(G53:G56)</f>
-        <v>27.501241480826</v>
+        <v>26.7686077111287</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50143,15 +50143,15 @@
       </c>
       <c r="E60" s="17" t="n">
         <f aca="false">h2s26+h1s*E57</f>
-        <v>23.8886278793558</v>
+        <v>23.5639369229205</v>
       </c>
       <c r="F60" s="17" t="n">
         <f aca="false">(1-h1s)*E57+h1s*F57</f>
-        <v>25.309105020074</v>
+        <v>24.6273976384199</v>
       </c>
       <c r="G60" s="17" t="n">
         <f aca="false">(1-h1s)*F57+h1s*G57</f>
-        <v>27.0174938811311</v>
+        <v>26.2941605710637</v>
       </c>
       <c r="H60" s="8" t="s">
         <v>515</v>
@@ -50202,15 +50202,15 @@
       </c>
       <c r="E62" s="17" t="n">
         <f aca="false">E60+E61</f>
-        <v>34.3565327293558</v>
+        <v>34.0318417729205</v>
       </c>
       <c r="F62" s="17" t="n">
         <f aca="false">F60+F61</f>
-        <v>36.958256662074</v>
+        <v>36.2765492804199</v>
       </c>
       <c r="G62" s="17" t="n">
         <f aca="false">G60+G61</f>
-        <v>40.0645437201711</v>
+        <v>39.3412104101037</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50230,15 +50230,15 @@
       </c>
       <c r="E63" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E62)</f>
-        <v>0.525131437822751</v>
+        <v>0.524635306239678</v>
       </c>
       <c r="F63" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F62)</f>
-        <v>0.528945432606449</v>
+        <v>0.527972688281455</v>
       </c>
       <c r="G63" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G62)</f>
-        <v>0.533162044250997</v>
+        <v>0.532210116026795</v>
       </c>
       <c r="H63" s="5" t="s">
         <v>516</v>
@@ -50261,15 +50261,15 @@
       </c>
       <c r="E64" s="17" t="n">
         <f aca="false">E62*E63</f>
-        <v>18.041695430771</v>
+        <v>17.8543057304364</v>
       </c>
       <c r="F64" s="17" t="n">
         <f aca="false">F62*F63</f>
-        <v>19.5489010585009</v>
+        <v>19.153027245158</v>
       </c>
       <c r="G64" s="17" t="n">
         <f aca="false">G62*G63</f>
-        <v>21.3608940318299</v>
+        <v>20.9377901569959</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50289,15 +50289,15 @@
       </c>
       <c r="E65" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E62</f>
-        <v>4.13347710025874</v>
+        <v>4.11573139403167</v>
       </c>
       <c r="F65" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F62</f>
-        <v>4.27567209423347</v>
+        <v>4.23841396095968</v>
       </c>
       <c r="G65" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G62</f>
-        <v>4.44544355382429</v>
+        <v>4.40591039107274</v>
       </c>
       <c r="H65" s="5" t="s">
         <v>517</v>
@@ -50320,15 +50320,15 @@
       </c>
       <c r="E66" s="17" t="n">
         <f aca="false">E64-E65</f>
-        <v>13.9082183305123</v>
+        <v>13.7385743364048</v>
       </c>
       <c r="F66" s="17" t="n">
         <f aca="false">F64-F65</f>
-        <v>15.2732289642674</v>
+        <v>14.9146132841983</v>
       </c>
       <c r="G66" s="17" t="n">
         <f aca="false">G64-G65</f>
-        <v>16.9154504780056</v>
+        <v>16.5318797659231</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50348,15 +50348,15 @@
       </c>
       <c r="E67" s="10" t="n">
         <f aca="false">E66/E62</f>
-        <v>0.404820196498713</v>
+        <v>0.403697643755992</v>
       </c>
       <c r="F67" s="10" t="n">
         <f aca="false">F66/F62</f>
-        <v>0.413256206966618</v>
+        <v>0.411136493962186</v>
       </c>
       <c r="G67" s="10" t="n">
         <f aca="false">G66/G62</f>
-        <v>0.422204994923959</v>
+        <v>0.420217873156169</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50376,15 +50376,15 @@
       </c>
       <c r="E68" s="17" t="n">
         <f aca="false">(E66+oth_inc)*(1-tax)</f>
-        <v>11.6968623059778</v>
+        <v>11.555209570898</v>
       </c>
       <c r="F68" s="17" t="n">
         <f aca="false">(F66+oth_inc)*(1-tax)</f>
-        <v>12.8366461851633</v>
+        <v>12.5372020923056</v>
       </c>
       <c r="G68" s="17" t="n">
         <f aca="false">(G66+oth_inc)*(1-tax)</f>
-        <v>14.2079011491347</v>
+        <v>13.8876196045458</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50432,15 +50432,15 @@
       </c>
       <c r="E70" s="13" t="n">
         <f aca="false">E68/E69</f>
-        <v>9.33508563924802</v>
+        <v>9.22203477326255</v>
       </c>
       <c r="F70" s="13" t="n">
         <f aca="false">F68/F69</f>
-        <v>10.4007407077133</v>
+        <v>10.1581196740457</v>
       </c>
       <c r="G70" s="13" t="n">
         <f aca="false">G68/G69</f>
-        <v>11.6870901722364</v>
+        <v>11.4236339971953</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50460,15 +50460,15 @@
       </c>
       <c r="E71" s="10" t="n">
         <f aca="false">E60/E62</f>
-        <v>0.695315446047449</v>
+        <v>0.692408512009203</v>
       </c>
       <c r="F71" s="10" t="n">
         <f aca="false">F60/F62</f>
-        <v>0.684802458392087</v>
+        <v>0.678879279505023</v>
       </c>
       <c r="G71" s="10" t="n">
         <f aca="false">G60/G62</f>
-        <v>0.674349221841474</v>
+        <v>0.668361758496144</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50547,15 +50547,15 @@
       </c>
       <c r="E84" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift_hi)^1</f>
-        <v>6.00840033878379</v>
+        <v>5.64848736253567</v>
       </c>
       <c r="F84" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift_hi)^2</f>
-        <v>6.85376887657415</v>
+        <v>6.44321694664335</v>
       </c>
       <c r="G84" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift_hi)^3</f>
-        <v>7.25732722661809</v>
+        <v>6.8226014935676</v>
       </c>
       <c r="H84" s="8" t="s">
         <v>506</v>
@@ -50574,15 +50574,15 @@
       </c>
       <c r="E85" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift_hi)^1</f>
-        <v>6.10330657540517</v>
+        <v>5.7873322545839</v>
       </c>
       <c r="F85" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift_hi)^2</f>
-        <v>7.01085229350476</v>
+        <v>6.64789341794289</v>
       </c>
       <c r="G85" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift_hi)^3</f>
-        <v>7.55885941709101</v>
+        <v>7.16752966149206</v>
       </c>
       <c r="H85" s="8" t="s">
         <v>506</v>
@@ -50624,15 +50624,15 @@
       </c>
       <c r="E87" s="17" t="n">
         <f aca="false">SUM(E83:E86)</f>
-        <v>25.0675030958019</v>
+        <v>24.3916157987325</v>
       </c>
       <c r="F87" s="17" t="n">
         <f aca="false">SUM(F83:F86)</f>
-        <v>28.7439708779741</v>
+        <v>27.9704600724814</v>
       </c>
       <c r="G87" s="17" t="n">
         <f aca="false">SUM(G83:G86)</f>
-        <v>31.0080594282403</v>
+        <v>30.1820039395909</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50684,15 +50684,15 @@
       </c>
       <c r="E90" s="17" t="n">
         <f aca="false">h2s26+h1s*E87</f>
-        <v>24.380147547901</v>
+        <v>24.0422038993663</v>
       </c>
       <c r="F90" s="17" t="n">
         <f aca="false">(1-h1s)*E87+h1s*F87</f>
-        <v>26.905736986888</v>
+        <v>26.181037935607</v>
       </c>
       <c r="G90" s="17" t="n">
         <f aca="false">(1-h1s)*F87+h1s*G87</f>
-        <v>29.8760151531072</v>
+        <v>29.0762320060362</v>
       </c>
       <c r="H90" s="8" t="s">
         <v>515</v>
@@ -50743,15 +50743,15 @@
       </c>
       <c r="E92" s="17" t="n">
         <f aca="false">E90+E91</f>
-        <v>34.848052397901</v>
+        <v>34.5101087493663</v>
       </c>
       <c r="F92" s="17" t="n">
         <f aca="false">F90+F91</f>
-        <v>38.554888628888</v>
+        <v>37.830189577607</v>
       </c>
       <c r="G92" s="17" t="n">
         <f aca="false">G90+G91</f>
-        <v>42.9230649921472</v>
+        <v>42.1232818450762</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50771,15 +50771,15 @@
       </c>
       <c r="E93" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E92)</f>
-        <v>0.525873634549288</v>
+        <v>0.525364472700102</v>
       </c>
       <c r="F93" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F92)</f>
-        <v>0.531155231192122</v>
+        <v>0.530163787859966</v>
       </c>
       <c r="G93" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G92)</f>
-        <v>0.536762900012546</v>
+        <v>0.535780168034</v>
       </c>
       <c r="H93" s="5" t="s">
         <v>516</v>
@@ -50802,15 +50802,15 @@
       </c>
       <c r="E94" s="17" t="n">
         <f aca="false">E92*E93</f>
-        <v>18.3256719714482</v>
+        <v>18.130385085934</v>
       </c>
       <c r="F94" s="17" t="n">
         <f aca="false">F92*F93</f>
-        <v>20.4786307832635</v>
+        <v>20.0561966019247</v>
       </c>
       <c r="G94" s="17" t="n">
         <f aca="false">G92*G93</f>
-        <v>23.0395088426119</v>
+        <v>22.5688190250985</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50830,15 +50830,15 @@
       </c>
       <c r="E95" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E92</f>
-        <v>4.16034068690924</v>
+        <v>4.14187066614228</v>
       </c>
       <c r="F95" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F92</f>
-        <v>4.36293464736062</v>
+        <v>4.32332684119237</v>
       </c>
       <c r="G95" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G92</f>
-        <v>4.60167358650905</v>
+        <v>4.55796212337159</v>
       </c>
       <c r="H95" s="5" t="s">
         <v>517</v>
@@ -50861,15 +50861,15 @@
       </c>
       <c r="E96" s="17" t="n">
         <f aca="false">E94-E95</f>
-        <v>14.165331284539</v>
+        <v>13.9885144197917</v>
       </c>
       <c r="F96" s="17" t="n">
         <f aca="false">F94-F95</f>
-        <v>16.1156961359029</v>
+        <v>15.7328697607324</v>
       </c>
       <c r="G96" s="17" t="n">
         <f aca="false">G94-G95</f>
-        <v>18.4378352561029</v>
+        <v>18.0108569017269</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50889,15 +50889,15 @@
       </c>
       <c r="E97" s="10" t="n">
         <f aca="false">E96/E92</f>
-        <v>0.406488463768271</v>
+        <v>0.405345416943914</v>
       </c>
       <c r="F97" s="10" t="n">
         <f aca="false">F96/F92</f>
-        <v>0.417993585483421</v>
+        <v>0.415881335420143</v>
       </c>
       <c r="G97" s="10" t="n">
         <f aca="false">G96/G92</f>
-        <v>0.429555421065017</v>
+        <v>0.427574873391119</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50917,15 +50917,15 @@
       </c>
       <c r="E98" s="17" t="n">
         <f aca="false">(E96+oth_inc)*(1-tax)</f>
-        <v>11.91155162259</v>
+        <v>11.7639095405261</v>
       </c>
       <c r="F98" s="17" t="n">
         <f aca="false">(F96+oth_inc)*(1-tax)</f>
-        <v>13.5401062734789</v>
+        <v>13.2204462502115</v>
       </c>
       <c r="G98" s="17" t="n">
         <f aca="false">(G96+oth_inc)*(1-tax)</f>
-        <v>15.4790924388459</v>
+        <v>15.1225655129419</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50973,15 +50973,15 @@
       </c>
       <c r="E100" s="13" t="n">
         <f aca="false">E98/E99</f>
-        <v>9.50642587596971</v>
+        <v>9.38859500441026</v>
       </c>
       <c r="F100" s="13" t="n">
         <f aca="false">F98/F99</f>
-        <v>10.9707109219934</v>
+        <v>10.7117101698758</v>
       </c>
       <c r="G100" s="13" t="n">
         <f aca="false">G98/G99</f>
-        <v>12.7327426632746</v>
+        <v>12.439471877665</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51001,15 +51001,15 @@
       </c>
       <c r="E101" s="10" t="n">
         <f aca="false">E90/E92</f>
-        <v>0.699612915795819</v>
+        <v>0.696671345604142</v>
       </c>
       <c r="F101" s="10" t="n">
         <f aca="false">F90/F92</f>
-        <v>0.697855393796375</v>
+        <v>0.692067320516534</v>
       </c>
       <c r="G101" s="10" t="n">
         <f aca="false">G90/G92</f>
-        <v>0.696036388794068</v>
+        <v>0.690265115452654</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51088,15 +51088,15 @@
       </c>
       <c r="E114" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F114" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G114" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H114" s="8" t="s">
         <v>506</v>
@@ -51115,15 +51115,15 @@
       </c>
       <c r="E115" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F115" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G115" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H115" s="8" t="s">
         <v>506</v>
@@ -51138,15 +51138,15 @@
       </c>
       <c r="E116" s="17" t="n">
         <f aca="false">-cn_sh*cut_sens_lo*(E113+E114+E115)</f>
-        <v>-1.67116687305346</v>
+        <v>-1.6261077199155</v>
       </c>
       <c r="F116" s="17" t="n">
         <f aca="false">-cn_sh*cut_sens_lo*(F113+F114+F115)</f>
-        <v>-1.87869090705713</v>
+        <v>-1.82813464526022</v>
       </c>
       <c r="G116" s="17" t="n">
         <f aca="false">-cn_sh*cut_sens_lo*(G113+G114+G115)</f>
-        <v>-1.98693191261312</v>
+        <v>-1.93399999612911</v>
       </c>
       <c r="H116" s="5" t="s">
         <v>510</v>
@@ -51165,15 +51165,15 @@
       </c>
       <c r="E117" s="17" t="n">
         <f aca="false">SUM(E113:E116)</f>
-        <v>22.9048165542033</v>
+        <v>22.2872411023713</v>
       </c>
       <c r="F117" s="17" t="n">
         <f aca="false">SUM(F113:F116)</f>
-        <v>25.7491165496654</v>
+        <v>25.0561983732725</v>
       </c>
       <c r="G117" s="17" t="n">
         <f aca="false">SUM(G113:G116)</f>
-        <v>27.2326550375798</v>
+        <v>26.5071764175343</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51225,15 +51225,15 @@
       </c>
       <c r="E120" s="17" t="n">
         <f aca="false">h2s26+h1s*E117</f>
-        <v>23.2988042771017</v>
+        <v>22.9900165511856</v>
       </c>
       <c r="F120" s="17" t="n">
         <f aca="false">(1-h1s)*E117+h1s*F117</f>
-        <v>24.3269665519343</v>
+        <v>23.6717197378219</v>
       </c>
       <c r="G120" s="17" t="n">
         <f aca="false">(1-h1s)*F117+h1s*G117</f>
-        <v>26.4908857936226</v>
+        <v>25.7816873954034</v>
       </c>
       <c r="H120" s="8" t="s">
         <v>515</v>
@@ -51284,15 +51284,15 @@
       </c>
       <c r="E122" s="17" t="n">
         <f aca="false">E120+E121</f>
-        <v>33.7667091271017</v>
+        <v>33.4579214011856</v>
       </c>
       <c r="F122" s="17" t="n">
         <f aca="false">F120+F121</f>
-        <v>35.9761181939343</v>
+        <v>35.3208713798219</v>
       </c>
       <c r="G122" s="17" t="n">
         <f aca="false">G120+G121</f>
-        <v>39.5379356326626</v>
+        <v>38.8287372344434</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51312,15 +51312,15 @@
       </c>
       <c r="E123" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E122)</f>
-        <v>0.524226656987743</v>
+        <v>0.523746657957779</v>
       </c>
       <c r="F123" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F122)</f>
-        <v>0.527538178871552</v>
+        <v>0.526577779973196</v>
       </c>
       <c r="G123" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G122)</f>
-        <v>0.532470734049608</v>
+        <v>0.53152503295053</v>
       </c>
       <c r="H123" s="5" t="s">
         <v>516</v>
@@ -51343,15 +51343,15 @@
       </c>
       <c r="E124" s="17" t="n">
         <f aca="false">E122*E123</f>
-        <v>17.701409043178</v>
+        <v>17.523474516085</v>
       </c>
       <c r="F124" s="17" t="n">
         <f aca="false">F122*F123</f>
-        <v>18.9787758748958</v>
+        <v>18.5991860379054</v>
       </c>
       <c r="G124" s="17" t="n">
         <f aca="false">G122*G123</f>
-        <v>21.05279360913</v>
+        <v>20.638445837965</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51371,15 +51371,15 @@
       </c>
       <c r="E125" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E122</f>
-        <v>4.10124079627815</v>
+        <v>4.08436426749893</v>
       </c>
       <c r="F125" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F122</f>
-        <v>4.22199415715367</v>
+        <v>4.18618220354361</v>
       </c>
       <c r="G125" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G122</f>
-        <v>4.41666223967768</v>
+        <v>4.37790160843103</v>
       </c>
       <c r="H125" s="5" t="s">
         <v>517</v>
@@ -51402,15 +51402,15 @@
       </c>
       <c r="E126" s="17" t="n">
         <f aca="false">E124-E125</f>
-        <v>13.6001682468998</v>
+        <v>13.4391102485861</v>
       </c>
       <c r="F126" s="17" t="n">
         <f aca="false">F124-F125</f>
-        <v>14.7567817177421</v>
+        <v>14.4130038343618</v>
       </c>
       <c r="G126" s="17" t="n">
         <f aca="false">G124-G125</f>
-        <v>16.6361313694523</v>
+        <v>16.260544229534</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51430,15 +51430,15 @@
       </c>
       <c r="E127" s="10" t="n">
         <f aca="false">E126/E122</f>
-        <v>0.402768543292368</v>
+        <v>0.40167200130101</v>
       </c>
       <c r="F127" s="10" t="n">
         <f aca="false">F126/F122</f>
-        <v>0.4101827117143</v>
+        <v>0.408059124005521</v>
       </c>
       <c r="G127" s="10" t="n">
         <f aca="false">G126/G122</f>
-        <v>0.420763783016256</v>
+        <v>0.418776024864128</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51458,15 +51458,15 @@
       </c>
       <c r="E128" s="17" t="n">
         <f aca="false">(E126+oth_inc)*(1-tax)</f>
-        <v>11.4396404861614</v>
+        <v>11.3051570575694</v>
       </c>
       <c r="F128" s="17" t="n">
         <f aca="false">(F126+oth_inc)*(1-tax)</f>
-        <v>12.4054127343147</v>
+        <v>12.1183582016921</v>
       </c>
       <c r="G128" s="17" t="n">
         <f aca="false">(G126+oth_inc)*(1-tax)</f>
-        <v>13.9746696934927</v>
+        <v>13.6610544316609</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51514,15 +51514,15 @@
       </c>
       <c r="E130" s="13" t="n">
         <f aca="false">E128/E129</f>
-        <v>9.12980086684866</v>
+        <v>9.02247171394206</v>
       </c>
       <c r="F130" s="13" t="n">
         <f aca="false">F128/F129</f>
-        <v>10.0513389058663</v>
+        <v>9.81875636680461</v>
       </c>
       <c r="G130" s="13" t="n">
         <f aca="false">G128/G129</f>
-        <v>11.4952393827019</v>
+        <v>11.2372667373446</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51542,15 +51542,15 @@
       </c>
       <c r="E131" s="10" t="n">
         <f aca="false">E120/E122</f>
-        <v>0.689993336022245</v>
+        <v>0.68713224218319</v>
       </c>
       <c r="F131" s="10" t="n">
         <f aca="false">F120/F122</f>
-        <v>0.676197649251551</v>
+        <v>0.670190706318335</v>
       </c>
       <c r="G131" s="10" t="n">
         <f aca="false">G120/G122</f>
-        <v>0.670011859995499</v>
+        <v>0.663984698748676</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51629,15 +51629,15 @@
       </c>
       <c r="E144" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F144" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G144" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H144" s="8" t="s">
         <v>506</v>
@@ -51656,15 +51656,15 @@
       </c>
       <c r="E145" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F145" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G145" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H145" s="8" t="s">
         <v>506</v>
@@ -51679,15 +51679,15 @@
       </c>
       <c r="E146" s="17" t="n">
         <f aca="false">-cn_sh*cut_sens_hi*(E143+E144+E145)</f>
-        <v>-3.34233374610692</v>
+        <v>-3.252215439831</v>
       </c>
       <c r="F146" s="17" t="n">
         <f aca="false">-cn_sh*cut_sens_hi*(F143+F144+F145)</f>
-        <v>-3.75738181411426</v>
+        <v>-3.65626929052045</v>
       </c>
       <c r="G146" s="17" t="n">
         <f aca="false">-cn_sh*cut_sens_hi*(G143+G144+G145)</f>
-        <v>-3.97386382522624</v>
+        <v>-3.86799999225822</v>
       </c>
       <c r="H146" s="5" t="s">
         <v>510</v>
@@ -51706,15 +51706,15 @@
       </c>
       <c r="E147" s="17" t="n">
         <f aca="false">SUM(E143:E146)</f>
-        <v>21.2336496811498</v>
+        <v>20.6611333824558</v>
       </c>
       <c r="F147" s="17" t="n">
         <f aca="false">SUM(F143:F146)</f>
-        <v>23.8704256426082</v>
+        <v>23.2280637280123</v>
       </c>
       <c r="G147" s="17" t="n">
         <f aca="false">SUM(G143:G146)</f>
-        <v>25.2457231249667</v>
+        <v>24.5731764214052</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51766,15 +51766,15 @@
       </c>
       <c r="E150" s="17" t="n">
         <f aca="false">h2s26+h1s*E147</f>
-        <v>22.4632208405749</v>
+        <v>22.1769626912279</v>
       </c>
       <c r="F150" s="17" t="n">
         <f aca="false">(1-h1s)*E147+h1s*F147</f>
-        <v>22.552037661879</v>
+        <v>21.944598555234</v>
       </c>
       <c r="G150" s="17" t="n">
         <f aca="false">(1-h1s)*F147+h1s*G147</f>
-        <v>24.5580743837875</v>
+        <v>23.9006200747087</v>
       </c>
       <c r="H150" s="8" t="s">
         <v>515</v>
@@ -51825,15 +51825,15 @@
       </c>
       <c r="E152" s="17" t="n">
         <f aca="false">E150+E151</f>
-        <v>32.9311256905749</v>
+        <v>32.6448675412279</v>
       </c>
       <c r="F152" s="17" t="n">
         <f aca="false">F150+F151</f>
-        <v>34.2011893038791</v>
+        <v>33.593750197234</v>
       </c>
       <c r="G152" s="17" t="n">
         <f aca="false">G150+G151</f>
-        <v>37.6051242228275</v>
+        <v>36.9476699137487</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51853,15 +51853,15 @@
       </c>
       <c r="E153" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E152)</f>
-        <v>0.522917455443357</v>
+        <v>0.522461290989033</v>
       </c>
       <c r="F153" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F152)</f>
-        <v>0.524894658953583</v>
+        <v>0.523958342202833</v>
       </c>
       <c r="G153" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G152)</f>
-        <v>0.529852013113354</v>
+        <v>0.528930463736136</v>
       </c>
       <c r="H153" s="5" t="s">
         <v>516</v>
@@ -51884,15 +51884,15 @@
       </c>
       <c r="E154" s="17" t="n">
         <f aca="false">E152*E153</f>
-        <v>17.2202604510008</v>
+        <v>17.0556796397559</v>
       </c>
       <c r="F154" s="17" t="n">
         <f aca="false">F152*F153</f>
-        <v>17.9520215954665</v>
+        <v>17.6017256617188</v>
       </c>
       <c r="G154" s="17" t="n">
         <f aca="false">G152*G153</f>
-        <v>19.9251507728429</v>
+        <v>19.5427481814488</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51912,15 +51912,15 @@
       </c>
       <c r="E155" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E152</f>
-        <v>4.05557269897231</v>
+        <v>4.03992750491089</v>
       </c>
       <c r="F155" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F152</f>
-        <v>4.12498693834267</v>
+        <v>4.0917878740518</v>
       </c>
       <c r="G155" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G152</f>
-        <v>4.31102608692543</v>
+        <v>4.27509348456802</v>
       </c>
       <c r="H155" s="5" t="s">
         <v>517</v>
@@ -51943,15 +51943,15 @@
       </c>
       <c r="E156" s="17" t="n">
         <f aca="false">E154-E155</f>
-        <v>13.1646877520285</v>
+        <v>13.015752134845</v>
       </c>
       <c r="F156" s="17" t="n">
         <f aca="false">F154-F155</f>
-        <v>13.8270346571238</v>
+        <v>13.509937787667</v>
       </c>
       <c r="G156" s="17" t="n">
         <f aca="false">G154-G155</f>
-        <v>15.6141246859175</v>
+        <v>15.2676546968808</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51971,15 +51971,15 @@
       </c>
       <c r="E157" s="10" t="n">
         <f aca="false">E156/E152</f>
-        <v>0.399764280022662</v>
+        <v>0.398707457409871</v>
       </c>
       <c r="F157" s="10" t="n">
         <f aca="false">F156/F152</f>
-        <v>0.404285199975651</v>
+        <v>0.402156285271758</v>
       </c>
       <c r="G157" s="10" t="n">
         <f aca="false">G156/G152</f>
-        <v>0.415212687329436</v>
+        <v>0.413223749495485</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51999,15 +51999,15 @@
       </c>
       <c r="E158" s="17" t="n">
         <f aca="false">(E156+oth_inc)*(1-tax)</f>
-        <v>11.0760142729438</v>
+        <v>10.9516530325956</v>
       </c>
       <c r="F158" s="17" t="n">
         <f aca="false">(F156+oth_inc)*(1-tax)</f>
-        <v>11.6290739386984</v>
+        <v>11.364298052702</v>
       </c>
       <c r="G158" s="17" t="n">
         <f aca="false">(G156+oth_inc)*(1-tax)</f>
-        <v>13.1212941127411</v>
+        <v>12.8319916718954</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52055,15 +52055,15 @@
       </c>
       <c r="E160" s="13" t="n">
         <f aca="false">E158/E159</f>
-        <v>8.83959638702616</v>
+        <v>8.74034559664452</v>
       </c>
       <c r="F160" s="13" t="n">
         <f aca="false">F158/F159</f>
-        <v>9.4223195811866</v>
+        <v>9.20778805198647</v>
       </c>
       <c r="G160" s="13" t="n">
         <f aca="false">G158/G159</f>
-        <v>10.7932724096535</v>
+        <v>10.5552989273129</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52083,15 +52083,15 @@
       </c>
       <c r="E161" s="10" t="n">
         <f aca="false">E150/E152</f>
-        <v>0.682127329980828</v>
+        <v>0.679339950245475</v>
       </c>
       <c r="F161" s="10" t="n">
         <f aca="false">F150/F152</f>
-        <v>0.659393375519875</v>
+        <v>0.653234557808936</v>
       </c>
       <c r="G161" s="10" t="n">
         <f aca="false">G150/G152</f>
-        <v>0.653051276689573</v>
+        <v>0.646877600955696</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52170,15 +52170,15 @@
       </c>
       <c r="E174" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F174" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G174" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H174" s="8" t="s">
         <v>506</v>
@@ -52197,15 +52197,15 @@
       </c>
       <c r="E175" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F175" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G175" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H175" s="8" t="s">
         <v>506</v>
@@ -52247,15 +52247,15 @@
       </c>
       <c r="E177" s="17" t="n">
         <f aca="false">SUM(E173:E176)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F177" s="17" t="n">
         <f aca="false">SUM(F173:F176)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G177" s="17" t="n">
         <f aca="false">SUM(G173:G176)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52307,15 +52307,15 @@
       </c>
       <c r="E180" s="17" t="n">
         <f aca="false">h2s26+h1s_lo*E177</f>
-        <v>22.9055885422655</v>
+        <v>22.6074029700291</v>
       </c>
       <c r="F180" s="17" t="n">
         <f aca="false">(1-h1s_lo)*E177+h1s_lo*F177</f>
-        <v>25.9493042405164</v>
+        <v>25.2502917105975</v>
       </c>
       <c r="G180" s="17" t="n">
         <f aca="false">(1-h1s_lo)*F177+h1s_lo*G177</f>
-        <v>28.3441082287842</v>
+        <v>27.5849125463415</v>
       </c>
       <c r="H180" s="8" t="s">
         <v>515</v>
@@ -52366,15 +52366,15 @@
       </c>
       <c r="E182" s="17" t="n">
         <f aca="false">E180+E181</f>
-        <v>32.8240051072656</v>
+        <v>32.5258195350291</v>
       </c>
       <c r="F182" s="17" t="n">
         <f aca="false">F180+F181</f>
-        <v>37.5325172883164</v>
+        <v>36.8335047583975</v>
       </c>
       <c r="G182" s="17" t="n">
         <f aca="false">G180+G181</f>
-        <v>41.3173068423202</v>
+        <v>40.5581111598775</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52394,15 +52394,15 @@
       </c>
       <c r="E183" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E182)</f>
-        <v>0.522747220242595</v>
+        <v>0.522270404139689</v>
       </c>
       <c r="F183" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F182)</f>
-        <v>0.529751035203379</v>
+        <v>0.528768769680821</v>
       </c>
       <c r="G183" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G182)</f>
-        <v>0.534770767755058</v>
+        <v>0.533801779870705</v>
       </c>
       <c r="H183" s="5" t="s">
         <v>516</v>
@@ -52425,15 +52425,15 @@
       </c>
       <c r="E184" s="17" t="n">
         <f aca="false">E182*E183</f>
-        <v>17.1586574270518</v>
+        <v>16.9872729135342</v>
       </c>
       <c r="F184" s="17" t="n">
         <f aca="false">F182*F183</f>
-        <v>19.8828898872743</v>
+        <v>19.4764069941305</v>
       </c>
       <c r="G184" s="17" t="n">
         <f aca="false">G182*G183</f>
-        <v>22.0952879016389</v>
+        <v>21.6499919253365</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52453,15 +52453,15 @@
       </c>
       <c r="E185" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E182</f>
-        <v>4.04971811520702</v>
+        <v>4.03342103805971</v>
       </c>
       <c r="F185" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F182</f>
-        <v>4.307057817085</v>
+        <v>4.26885388574927</v>
       </c>
       <c r="G185" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G182</f>
-        <v>4.51391224966307</v>
+        <v>4.47241905965432</v>
       </c>
       <c r="H185" s="5" t="s">
         <v>517</v>
@@ -52484,15 +52484,15 @@
       </c>
       <c r="E186" s="17" t="n">
         <f aca="false">E184-E185</f>
-        <v>13.1089393118448</v>
+        <v>12.9538518754745</v>
       </c>
       <c r="F186" s="17" t="n">
         <f aca="false">F184-F185</f>
-        <v>15.5758320701893</v>
+        <v>15.2075531083812</v>
       </c>
       <c r="G186" s="17" t="n">
         <f aca="false">G184-G185</f>
-        <v>17.5813756519758</v>
+        <v>17.1775728656822</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52512,15 +52512,15 @@
       </c>
       <c r="E187" s="10" t="n">
         <f aca="false">E186/E182</f>
-        <v>0.399370499395368</v>
+        <v>0.398263658246142</v>
       </c>
       <c r="F187" s="10" t="n">
         <f aca="false">F186/F182</f>
-        <v>0.414995667637725</v>
+        <v>0.412872823483194</v>
       </c>
       <c r="G187" s="10" t="n">
         <f aca="false">G186/G182</f>
-        <v>0.425520853018612</v>
+        <v>0.423529902513687</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52540,15 +52540,15 @@
       </c>
       <c r="E188" s="17" t="n">
         <f aca="false">(E186+oth_inc)*(1-tax)</f>
-        <v>11.0294643253904</v>
+        <v>10.8999663160212</v>
       </c>
       <c r="F188" s="17" t="n">
         <f aca="false">(F186+oth_inc)*(1-tax)</f>
-        <v>13.0893197786081</v>
+        <v>12.7818068454983</v>
       </c>
       <c r="G188" s="17" t="n">
         <f aca="false">(G186+oth_inc)*(1-tax)</f>
-        <v>14.7639486693998</v>
+        <v>14.4267733428446</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52596,15 +52596,15 @@
       </c>
       <c r="E190" s="13" t="n">
         <f aca="false">E188/E189</f>
-        <v>8.80244559089416</v>
+        <v>8.6990952242787</v>
       </c>
       <c r="F190" s="13" t="n">
         <f aca="false">F188/F189</f>
-        <v>10.6054664975495</v>
+        <v>10.356307781526</v>
       </c>
       <c r="G190" s="13" t="n">
         <f aca="false">G188/G189</f>
-        <v>12.1444819742467</v>
+        <v>11.867129365727</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52624,15 +52624,15 @@
       </c>
       <c r="E191" s="10" t="n">
         <f aca="false">E180/E182</f>
-        <v>0.697830397826602</v>
+        <v>0.695060210417811</v>
       </c>
       <c r="F191" s="10" t="n">
         <f aca="false">F180/F182</f>
-        <v>0.691381929998983</v>
+        <v>0.685525091251079</v>
       </c>
       <c r="G191" s="10" t="n">
         <f aca="false">G180/G182</f>
-        <v>0.686010546063765</v>
+        <v>0.680133067282239</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52711,15 +52711,15 @@
       </c>
       <c r="E204" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F204" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G204" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H204" s="8" t="s">
         <v>506</v>
@@ -52738,15 +52738,15 @@
       </c>
       <c r="E205" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F205" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G205" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H205" s="8" t="s">
         <v>506</v>
@@ -52788,15 +52788,15 @@
       </c>
       <c r="E207" s="17" t="n">
         <f aca="false">SUM(E203:E206)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F207" s="17" t="n">
         <f aca="false">SUM(F203:F206)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G207" s="17" t="n">
         <f aca="false">SUM(G203:G206)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52848,15 +52848,15 @@
       </c>
       <c r="E210" s="17" t="n">
         <f aca="false">h2s26+h1s_hi*E207</f>
-        <v>25.3631868849912</v>
+        <v>24.9987378522577</v>
       </c>
       <c r="F210" s="17" t="n">
         <f aca="false">(1-h1s_hi)*E207+h1s_hi*F207</f>
-        <v>26.2544866434629</v>
+        <v>25.547390130222</v>
       </c>
       <c r="G210" s="17" t="n">
         <f aca="false">(1-h1s_hi)*F207+h1s_hi*G207</f>
-        <v>28.5032861781312</v>
+        <v>27.7405968858546</v>
       </c>
       <c r="H210" s="8" t="s">
         <v>515</v>
@@ -52907,15 +52907,15 @@
       </c>
       <c r="E212" s="17" t="n">
         <f aca="false">E210+E211</f>
-        <v>36.3805800199912</v>
+        <v>36.0161309872577</v>
       </c>
       <c r="F212" s="17" t="n">
         <f aca="false">F210+F211</f>
-        <v>37.9695768796629</v>
+        <v>37.262480366422</v>
       </c>
       <c r="G212" s="17" t="n">
         <f aca="false">G210+G211</f>
-        <v>41.6241872426752</v>
+        <v>40.8614979503986</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52935,15 +52935,15 @@
       </c>
       <c r="E213" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E212)</f>
-        <v>0.528122308211755</v>
+        <v>0.527596257837265</v>
       </c>
       <c r="F213" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F212)</f>
-        <v>0.530355947215798</v>
+        <v>0.529373760068437</v>
       </c>
       <c r="G213" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G212)</f>
-        <v>0.535157406150365</v>
+        <v>0.534191161416414</v>
       </c>
       <c r="H213" s="5" t="s">
         <v>516</v>
@@ -52966,15 +52966,15 @@
       </c>
       <c r="E214" s="17" t="n">
         <f aca="false">E212*E213</f>
-        <v>19.2133958942402</v>
+        <v>19.0019759306539</v>
       </c>
       <c r="F214" s="17" t="n">
         <f aca="false">F212*F213</f>
-        <v>20.1373909113967</v>
+        <v>19.7257793410491</v>
       </c>
       <c r="G214" s="17" t="n">
         <f aca="false">G212*G213</f>
-        <v>22.2754920779072</v>
+        <v>21.8278510473378</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52994,15 +52994,15 @@
       </c>
       <c r="E215" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E212</f>
-        <v>4.24409967196095</v>
+        <v>4.22418102211424</v>
       </c>
       <c r="F215" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F212</f>
-        <v>4.33094493484433</v>
+        <v>4.29229918032156</v>
       </c>
       <c r="G215" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G212</f>
-        <v>4.53068453519678</v>
+        <v>4.48900040493375</v>
       </c>
       <c r="H215" s="5" t="s">
         <v>517</v>
@@ -53025,15 +53025,15 @@
       </c>
       <c r="E216" s="17" t="n">
         <f aca="false">E214-E215</f>
-        <v>14.9692962222793</v>
+        <v>14.7777949085397</v>
       </c>
       <c r="F216" s="17" t="n">
         <f aca="false">F214-F215</f>
-        <v>15.8064459765524</v>
+        <v>15.4334801607276</v>
       </c>
       <c r="G216" s="17" t="n">
         <f aca="false">G214-G215</f>
-        <v>17.7448075427104</v>
+        <v>17.3388506424041</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53053,15 +53053,15 @@
       </c>
       <c r="E217" s="10" t="n">
         <f aca="false">E216/E212</f>
-        <v>0.41146392427096</v>
+        <v>0.410310449886135</v>
       </c>
       <c r="F217" s="10" t="n">
         <f aca="false">F216/F212</f>
-        <v>0.416292391844338</v>
+        <v>0.414182845826737</v>
       </c>
       <c r="G217" s="10" t="n">
         <f aca="false">G216/G212</f>
-        <v>0.426310006709694</v>
+        <v>0.424332232348691</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53081,15 +53081,15 @@
       </c>
       <c r="E218" s="17" t="n">
         <f aca="false">(E216+oth_inc)*(1-tax)</f>
-        <v>12.5828623456032</v>
+        <v>12.4229587486306</v>
       </c>
       <c r="F218" s="17" t="n">
         <f aca="false">(F216+oth_inc)*(1-tax)</f>
-        <v>13.2818823904212</v>
+        <v>12.9704559342075</v>
       </c>
       <c r="G218" s="17" t="n">
         <f aca="false">(G216+oth_inc)*(1-tax)</f>
-        <v>14.9004142981632</v>
+        <v>14.5614402864074</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53137,15 +53137,15 @@
       </c>
       <c r="E220" s="13" t="n">
         <f aca="false">E218/E219</f>
-        <v>10.0421886237855</v>
+        <v>9.91457202604201</v>
       </c>
       <c r="F220" s="13" t="n">
         <f aca="false">F218/F219</f>
-        <v>10.761488075661</v>
+        <v>10.5091584738415</v>
       </c>
       <c r="G220" s="13" t="n">
         <f aca="false">G218/G219</f>
-        <v>12.256735437445</v>
+        <v>11.9779032721694</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53165,15 +53165,15 @@
       </c>
       <c r="E221" s="10" t="n">
         <f aca="false">E210/E212</f>
-        <v>0.697162795949215</v>
+        <v>0.694098371118822</v>
       </c>
       <c r="F221" s="10" t="n">
         <f aca="false">F210/F212</f>
-        <v>0.691461132860957</v>
+        <v>0.685606268799092</v>
       </c>
       <c r="G221" s="10" t="n">
         <f aca="false">G210/G212</f>
-        <v>0.684777002658402</v>
+        <v>0.678893292642591</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53252,15 +53252,15 @@
       </c>
       <c r="E234" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F234" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G234" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H234" s="8" t="s">
         <v>506</v>
@@ -53279,15 +53279,15 @@
       </c>
       <c r="E235" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F235" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G235" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H235" s="8" t="s">
         <v>506</v>
@@ -53329,15 +53329,15 @@
       </c>
       <c r="E237" s="17" t="n">
         <f aca="false">SUM(E233:E236)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F237" s="17" t="n">
         <f aca="false">SUM(F233:F236)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G237" s="17" t="n">
         <f aca="false">SUM(G233:G236)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53389,15 +53389,15 @@
       </c>
       <c r="E240" s="17" t="n">
         <f aca="false">h2s26+h1s*E237</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F240" s="17" t="n">
         <f aca="false">(1-h1s)*E237+h1s*F237</f>
-        <v>26.1018954419896</v>
+        <v>25.3988409204097</v>
       </c>
       <c r="G240" s="17" t="n">
         <f aca="false">(1-h1s)*F237+h1s*G237</f>
-        <v>28.4236972034577</v>
+        <v>27.662754716098</v>
       </c>
       <c r="H240" s="8" t="s">
         <v>515</v>
@@ -53448,15 +53448,15 @@
       </c>
       <c r="E242" s="17" t="n">
         <f aca="false">E240+E241</f>
-        <v>34.3633846136284</v>
+        <v>34.0320673111434</v>
       </c>
       <c r="F242" s="17" t="n">
         <f aca="false">F240+F241</f>
-        <v>37.2445622299896</v>
+        <v>36.5415077084098</v>
       </c>
       <c r="G242" s="17" t="n">
         <f aca="false">G240+G241</f>
-        <v>40.9034840060177</v>
+        <v>40.1425415186581</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53476,15 +53476,15 @@
       </c>
       <c r="E243" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E242)</f>
-        <v>0.525141856991989</v>
+        <v>0.524635652504973</v>
       </c>
       <c r="F243" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F242)</f>
-        <v>0.529348629563067</v>
+        <v>0.528352918184478</v>
       </c>
       <c r="G243" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G242)</f>
-        <v>0.534244820526996</v>
+        <v>0.533263663375194</v>
       </c>
       <c r="H243" s="5" t="s">
         <v>516</v>
@@ -53507,15 +53507,15 @@
       </c>
       <c r="E244" s="17" t="n">
         <f aca="false">E242*E243</f>
-        <v>18.0456516085308</v>
+        <v>17.8544358398749</v>
       </c>
       <c r="F244" s="17" t="n">
         <f aca="false">F242*F243</f>
-        <v>19.7153579751214</v>
+        <v>19.3068122325989</v>
       </c>
       <c r="G244" s="17" t="n">
         <f aca="false">G242*G243</f>
-        <v>21.8524744717238</v>
+        <v>21.4065587474304</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53535,15 +53535,15 @@
       </c>
       <c r="E245" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E242</f>
-        <v>4.13385158412715</v>
+        <v>4.11574372063013</v>
       </c>
       <c r="F245" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F242</f>
-        <v>4.29131987991616</v>
+        <v>4.25289503698692</v>
       </c>
       <c r="G245" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G242</f>
-        <v>4.49129511685561</v>
+        <v>4.44970645671972</v>
       </c>
       <c r="H245" s="5" t="s">
         <v>517</v>
@@ -53566,15 +53566,15 @@
       </c>
       <c r="E246" s="17" t="n">
         <f aca="false">E244-E245</f>
-        <v>13.9118000244036</v>
+        <v>13.7386921192448</v>
       </c>
       <c r="F246" s="17" t="n">
         <f aca="false">F244-F245</f>
-        <v>15.4240380952052</v>
+        <v>15.053917195612</v>
       </c>
       <c r="G246" s="17" t="n">
         <f aca="false">G244-G245</f>
-        <v>17.3611793548682</v>
+        <v>16.9568522907107</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53594,15 +53594,15 @@
       </c>
       <c r="E247" s="10" t="n">
         <f aca="false">E246/E242</f>
-        <v>0.404843707359555</v>
+        <v>0.403698429297188</v>
       </c>
       <c r="F247" s="10" t="n">
         <f aca="false">F246/F242</f>
-        <v>0.41412859144269</v>
+        <v>0.411967599031154</v>
       </c>
       <c r="G247" s="10" t="n">
         <f aca="false">G246/G242</f>
-        <v>0.424442557321376</v>
+        <v>0.42241601177218</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53622,15 +53622,15 @@
       </c>
       <c r="E248" s="17" t="n">
         <f aca="false">(E246+oth_inc)*(1-tax)</f>
-        <v>11.699853020377</v>
+        <v>11.5553079195694</v>
       </c>
       <c r="F248" s="17" t="n">
         <f aca="false">(F246+oth_inc)*(1-tax)</f>
-        <v>12.9625718094963</v>
+        <v>12.653520858336</v>
       </c>
       <c r="G248" s="17" t="n">
         <f aca="false">(G246+oth_inc)*(1-tax)</f>
-        <v>14.5800847613149</v>
+        <v>14.2424716627434</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53678,15 +53678,15 @@
       </c>
       <c r="E250" s="13" t="n">
         <f aca="false">E248/E249</f>
-        <v>9.33747248234399</v>
+        <v>9.22211326382232</v>
       </c>
       <c r="F250" s="13" t="n">
         <f aca="false">F248/F249</f>
-        <v>10.5027704550673</v>
+        <v>10.2523655781138</v>
       </c>
       <c r="G250" s="13" t="n">
         <f aca="false">G248/G249</f>
-        <v>11.9932397850837</v>
+        <v>11.71552707545</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53706,15 +53706,15 @@
       </c>
       <c r="E251" s="10" t="n">
         <f aca="false">E240/E242</f>
-        <v>0.702328597284238</v>
+        <v>0.699430633864237</v>
       </c>
       <c r="F251" s="10" t="n">
         <f aca="false">F240/F242</f>
-        <v>0.70082433190669</v>
+        <v>0.69506822551179</v>
       </c>
       <c r="G251" s="10" t="n">
         <f aca="false">G240/G242</f>
-        <v>0.694896728094752</v>
+        <v>0.689113186897759</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53793,15 +53793,15 @@
       </c>
       <c r="E264" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F264" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G264" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H264" s="8" t="s">
         <v>506</v>
@@ -53820,15 +53820,15 @@
       </c>
       <c r="E265" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F265" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G265" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H265" s="8" t="s">
         <v>506</v>
@@ -53870,15 +53870,15 @@
       </c>
       <c r="E267" s="17" t="n">
         <f aca="false">SUM(E263:E266)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F267" s="17" t="n">
         <f aca="false">SUM(F263:F266)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G267" s="17" t="n">
         <f aca="false">SUM(G263:G266)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53930,15 +53930,15 @@
       </c>
       <c r="E270" s="17" t="n">
         <f aca="false">h2s26+h1s*E267</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F270" s="17" t="n">
         <f aca="false">(1-h1s)*E267+h1s*F267</f>
-        <v>26.1018954419896</v>
+        <v>25.3988409204097</v>
       </c>
       <c r="G270" s="17" t="n">
         <f aca="false">(1-h1s)*F267+h1s*G267</f>
-        <v>28.4236972034577</v>
+        <v>27.662754716098</v>
       </c>
       <c r="H270" s="8" t="s">
         <v>515</v>
@@ -53989,15 +53989,15 @@
       </c>
       <c r="E272" s="17" t="n">
         <f aca="false">E270+E271</f>
-        <v>34.8412005136284</v>
+        <v>34.5098832111434</v>
       </c>
       <c r="F272" s="17" t="n">
         <f aca="false">F270+F271</f>
-        <v>38.2575319379896</v>
+        <v>37.5544774164097</v>
       </c>
       <c r="G272" s="17" t="n">
         <f aca="false">G270+G271</f>
-        <v>42.0380100789777</v>
+        <v>41.2770675916181</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54017,15 +54017,15 @@
       </c>
       <c r="E273" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E272)</f>
-        <v>0.525863360304425</v>
+        <v>0.525364131231364</v>
       </c>
       <c r="F273" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F272)</f>
-        <v>0.530750698025923</v>
+        <v>0.529781596787328</v>
       </c>
       <c r="G273" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G272)</f>
-        <v>0.53567429174441</v>
+        <v>0.534719857514236</v>
       </c>
       <c r="H273" s="5" t="s">
         <v>516</v>
@@ -54048,15 +54048,15 @@
       </c>
       <c r="E274" s="17" t="n">
         <f aca="false">E272*E273</f>
-        <v>18.3217107791369</v>
+        <v>18.1302548121182</v>
       </c>
       <c r="F274" s="17" t="n">
         <f aca="false">F272*F273</f>
-        <v>20.305211780837</v>
+        <v>19.8956710121792</v>
       </c>
       <c r="G274" s="17" t="n">
         <f aca="false">G272*G273</f>
-        <v>22.5186812754008</v>
+        <v>22.0716677011955</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54076,15 +54076,15 @@
       </c>
       <c r="E275" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E272</f>
-        <v>4.15996620304083</v>
+        <v>4.14185833954381</v>
       </c>
       <c r="F275" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F272</f>
-        <v>4.34668287201316</v>
+        <v>4.30825802908391</v>
       </c>
       <c r="G275" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G272</f>
-        <v>4.55330166800425</v>
+        <v>4.51171300786836</v>
       </c>
       <c r="H275" s="5" t="s">
         <v>517</v>
@@ -54107,15 +54107,15 @@
       </c>
       <c r="E276" s="17" t="n">
         <f aca="false">E274-E275</f>
-        <v>14.1617445760961</v>
+        <v>13.9883964725744</v>
       </c>
       <c r="F276" s="17" t="n">
         <f aca="false">F274-F275</f>
-        <v>15.9585289088239</v>
+        <v>15.5874129830953</v>
       </c>
       <c r="G276" s="17" t="n">
         <f aca="false">G274-G275</f>
-        <v>17.9653796073965</v>
+        <v>17.5599546933271</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54135,15 +54135,15 @@
       </c>
       <c r="E277" s="10" t="n">
         <f aca="false">E276/E272</f>
-        <v>0.406465459494043</v>
+        <v>0.405344648284913</v>
       </c>
       <c r="F277" s="10" t="n">
         <f aca="false">F276/F272</f>
-        <v>0.417134302722155</v>
+        <v>0.415061373648199</v>
       </c>
       <c r="G277" s="10" t="n">
         <f aca="false">G276/G272</f>
-        <v>0.427360371569553</v>
+        <v>0.425416719691904</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54163,15 +54163,15 @@
       </c>
       <c r="E278" s="17" t="n">
         <f aca="false">(E276+oth_inc)*(1-tax)</f>
-        <v>11.9085567210402</v>
+        <v>11.7638110545996</v>
       </c>
       <c r="F278" s="17" t="n">
         <f aca="false">(F276+oth_inc)*(1-tax)</f>
-        <v>13.4088716388679</v>
+        <v>13.0989898408846</v>
       </c>
       <c r="G278" s="17" t="n">
         <f aca="false">(G276+oth_inc)*(1-tax)</f>
-        <v>15.0845919721761</v>
+        <v>14.7460621689282</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54219,15 +54219,15 @@
       </c>
       <c r="E280" s="13" t="n">
         <f aca="false">E278/E279</f>
-        <v>9.50403569117335</v>
+        <v>9.38851640430933</v>
       </c>
       <c r="F280" s="13" t="n">
         <f aca="false">F278/F279</f>
-        <v>10.8643796118699</v>
+        <v>10.6133015511075</v>
       </c>
       <c r="G280" s="13" t="n">
         <f aca="false">G278/G279</f>
-        <v>12.4082357231879</v>
+        <v>12.129768953535</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54247,15 +54247,15 @@
       </c>
       <c r="E281" s="10" t="n">
         <f aca="false">E270/E272</f>
-        <v>0.692696788797161</v>
+        <v>0.689746478291682</v>
       </c>
       <c r="F281" s="10" t="n">
         <f aca="false">F270/F272</f>
-        <v>0.682268147466944</v>
+        <v>0.676319913569387</v>
       </c>
       <c r="G281" s="10" t="n">
         <f aca="false">G270/G272</f>
-        <v>0.676142784828718</v>
+        <v>0.670172479057485</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54334,15 +54334,15 @@
       </c>
       <c r="E294" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F294" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G294" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H294" s="8" t="s">
         <v>506</v>
@@ -54361,15 +54361,15 @@
       </c>
       <c r="E295" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F295" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G295" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H295" s="8" t="s">
         <v>506</v>
@@ -54411,15 +54411,15 @@
       </c>
       <c r="E297" s="17" t="n">
         <f aca="false">SUM(E293:E296)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F297" s="17" t="n">
         <f aca="false">SUM(F293:F296)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G297" s="17" t="n">
         <f aca="false">SUM(G293:G296)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54471,15 +54471,15 @@
       </c>
       <c r="E300" s="17" t="n">
         <f aca="false">h2s26+h1s*E297</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F300" s="17" t="n">
         <f aca="false">(1-h1s)*E297+h1s*F297</f>
-        <v>26.1018954419896</v>
+        <v>25.3988409204097</v>
       </c>
       <c r="G300" s="17" t="n">
         <f aca="false">(1-h1s)*F297+h1s*G297</f>
-        <v>28.4236972034577</v>
+        <v>27.662754716098</v>
       </c>
       <c r="H300" s="8" t="s">
         <v>515</v>
@@ -54530,15 +54530,15 @@
       </c>
       <c r="E302" s="17" t="n">
         <f aca="false">E300+E301</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F302" s="17" t="n">
         <f aca="false">F300+F301</f>
-        <v>37.5312517699896</v>
+        <v>36.8281972484098</v>
       </c>
       <c r="G302" s="17" t="n">
         <f aca="false">G300+G301</f>
-        <v>40.7674020376977</v>
+        <v>40.006459550338</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54558,15 +54558,15 @@
       </c>
       <c r="E303" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E302)</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F303" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F302)</f>
-        <v>0.529749273455441</v>
+        <v>0.528761240377874</v>
       </c>
       <c r="G303" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G302)</f>
-        <v>0.534070704232038</v>
+        <v>0.533086240919534</v>
       </c>
       <c r="H303" s="5" t="s">
         <v>516</v>
@@ -54589,15 +54589,15 @@
       </c>
       <c r="E304" s="17" t="n">
         <f aca="false">E302*E303</f>
-        <v>18.1836381009569</v>
+        <v>17.9923018165092</v>
       </c>
       <c r="F304" s="17" t="n">
         <f aca="false">F302*F303</f>
-        <v>19.8821533570252</v>
+        <v>19.4733232579502</v>
       </c>
       <c r="G304" s="17" t="n">
         <f aca="false">G302*G303</f>
-        <v>21.7726751159839</v>
+        <v>21.3268931341891</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54617,15 +54617,15 @@
       </c>
       <c r="E305" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E302</f>
-        <v>4.14690889358399</v>
+        <v>4.12880103008697</v>
       </c>
       <c r="F305" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F302</f>
-        <v>4.30698865126437</v>
+        <v>4.26856380833512</v>
       </c>
       <c r="G305" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G302</f>
-        <v>4.48385767338899</v>
+        <v>4.4422690132531</v>
       </c>
       <c r="H305" s="5" t="s">
         <v>517</v>
@@ -54648,15 +54648,15 @@
       </c>
       <c r="E306" s="17" t="n">
         <f aca="false">E304-E305</f>
-        <v>14.0367292073729</v>
+        <v>13.8635007864222</v>
       </c>
       <c r="F306" s="17" t="n">
         <f aca="false">F304-F305</f>
-        <v>15.5751647057609</v>
+        <v>15.204759449615</v>
       </c>
       <c r="G306" s="17" t="n">
         <f aca="false">G304-G305</f>
-        <v>17.2888174425949</v>
+        <v>16.884624120936</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54676,15 +54676,15 @@
       </c>
       <c r="E307" s="10" t="n">
         <f aca="false">E306/E302</f>
-        <v>0.405658936660381</v>
+        <v>0.404526007234486</v>
       </c>
       <c r="F307" s="10" t="n">
         <f aca="false">F306/F302</f>
-        <v>0.414991879333343</v>
+        <v>0.412856468294048</v>
       </c>
       <c r="G307" s="10" t="n">
         <f aca="false">G306/G302</f>
-        <v>0.424084356089403</v>
+        <v>0.422047447105159</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54704,15 +54704,15 @@
       </c>
       <c r="E308" s="17" t="n">
         <f aca="false">(E306+oth_inc)*(1-tax)</f>
-        <v>11.8041688881564</v>
+        <v>11.6595231566625</v>
       </c>
       <c r="F308" s="17" t="n">
         <f aca="false">(F306+oth_inc)*(1-tax)</f>
-        <v>13.0887625293103</v>
+        <v>12.7794741404285</v>
       </c>
       <c r="G308" s="17" t="n">
         <f aca="false">(G306+oth_inc)*(1-tax)</f>
-        <v>14.5196625645667</v>
+        <v>14.1821611409815</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54760,15 +54760,15 @@
       </c>
       <c r="E310" s="13" t="n">
         <f aca="false">E308/E309</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F310" s="13" t="n">
         <f aca="false">F308/F309</f>
-        <v>10.6050149928985</v>
+        <v>10.3544177348403</v>
       </c>
       <c r="G310" s="13" t="n">
         <f aca="false">G308/G309</f>
-        <v>11.9435378865141</v>
+        <v>11.6659170381357</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54788,15 +54788,15 @@
       </c>
       <c r="E311" s="10" t="n">
         <f aca="false">E300/E302</f>
-        <v>0.697479442127972</v>
+        <v>0.694554801249891</v>
       </c>
       <c r="F311" s="10" t="n">
         <f aca="false">F300/F302</f>
-        <v>0.695470953166049</v>
+        <v>0.689657458633995</v>
       </c>
       <c r="G311" s="10" t="n">
         <f aca="false">G300/G302</f>
-        <v>0.697216299855808</v>
+        <v>0.691457205336839</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54875,15 +54875,15 @@
       </c>
       <c r="E324" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F324" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G324" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H324" s="8" t="s">
         <v>506</v>
@@ -54902,15 +54902,15 @@
       </c>
       <c r="E325" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F325" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G325" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H325" s="8" t="s">
         <v>506</v>
@@ -54952,15 +54952,15 @@
       </c>
       <c r="E327" s="17" t="n">
         <f aca="false">SUM(E323:E326)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F327" s="17" t="n">
         <f aca="false">SUM(F323:F326)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G327" s="17" t="n">
         <f aca="false">SUM(G323:G326)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55012,15 +55012,15 @@
       </c>
       <c r="E330" s="17" t="n">
         <f aca="false">h2s26+h1s*E327</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F330" s="17" t="n">
         <f aca="false">(1-h1s)*E327+h1s*F327</f>
-        <v>26.1018954419896</v>
+        <v>25.3988409204097</v>
       </c>
       <c r="G330" s="17" t="n">
         <f aca="false">(1-h1s)*F327+h1s*G327</f>
-        <v>28.4236972034577</v>
+        <v>27.662754716098</v>
       </c>
       <c r="H330" s="8" t="s">
         <v>515</v>
@@ -55071,15 +55071,15 @@
       </c>
       <c r="E332" s="17" t="n">
         <f aca="false">E330+E331</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F332" s="17" t="n">
         <f aca="false">F330+F331</f>
-        <v>37.9708423979896</v>
+        <v>37.2677878764097</v>
       </c>
       <c r="G332" s="17" t="n">
         <f aca="false">G330+G331</f>
-        <v>42.1916756724177</v>
+        <v>41.430733185058</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55099,15 +55099,15 @@
       </c>
       <c r="E333" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E332)</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F333" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F332)</f>
-        <v>0.530357688626256</v>
+        <v>0.529381201625848</v>
       </c>
       <c r="G333" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G332)</f>
-        <v>0.535864933328953</v>
+        <v>0.534914007053554</v>
       </c>
       <c r="H333" s="5" t="s">
         <v>516</v>
@@ -55130,15 +55130,15 @@
       </c>
       <c r="E334" s="17" t="n">
         <f aca="false">E332*E333</f>
-        <v>18.1836381009569</v>
+        <v>17.9923018165092</v>
       </c>
       <c r="F334" s="17" t="n">
         <f aca="false">F332*F333</f>
-        <v>20.1381282093896</v>
+        <v>19.728866327951</v>
       </c>
       <c r="G334" s="17" t="n">
         <f aca="false">G332*G333</f>
-        <v>22.6090394712369</v>
+        <v>22.1618795031861</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55158,15 +55158,15 @@
       </c>
       <c r="E335" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E332</f>
-        <v>4.14690889358399</v>
+        <v>4.12880103008697</v>
       </c>
       <c r="F335" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F332</f>
-        <v>4.33101410066496</v>
+        <v>4.29258925773571</v>
       </c>
       <c r="G335" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G332</f>
-        <v>4.56170012944689</v>
+        <v>4.52011146931099</v>
       </c>
       <c r="H335" s="5" t="s">
         <v>517</v>
@@ -55189,15 +55189,15 @@
       </c>
       <c r="E336" s="17" t="n">
         <f aca="false">E334-E335</f>
-        <v>14.0367292073729</v>
+        <v>13.8635007864222</v>
       </c>
       <c r="F336" s="17" t="n">
         <f aca="false">F334-F335</f>
-        <v>15.8071141087247</v>
+        <v>15.4362770702153</v>
       </c>
       <c r="G336" s="17" t="n">
         <f aca="false">G334-G335</f>
-        <v>18.04733934179</v>
+        <v>17.6417680338751</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55217,15 +55217,15 @@
       </c>
       <c r="E337" s="10" t="n">
         <f aca="false">E336/E332</f>
-        <v>0.405658936660381</v>
+        <v>0.404526007234486</v>
       </c>
       <c r="F337" s="10" t="n">
         <f aca="false">F336/F332</f>
-        <v>0.416296113292488</v>
+        <v>0.414198908757511</v>
       </c>
       <c r="G337" s="10" t="n">
         <f aca="false">G336/G332</f>
-        <v>0.42774644652448</v>
+        <v>0.425813561036316</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55245,15 +55245,15 @@
       </c>
       <c r="E338" s="17" t="n">
         <f aca="false">(E336+oth_inc)*(1-tax)</f>
-        <v>11.8041688881564</v>
+        <v>11.6595231566625</v>
       </c>
       <c r="F338" s="17" t="n">
         <f aca="false">(F336+oth_inc)*(1-tax)</f>
-        <v>13.2824402807851</v>
+        <v>12.9727913536298</v>
       </c>
       <c r="G338" s="17" t="n">
         <f aca="false">(G336+oth_inc)*(1-tax)</f>
-        <v>15.1530283503947</v>
+        <v>14.8143763082857</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55301,15 +55301,15 @@
       </c>
       <c r="E340" s="13" t="n">
         <f aca="false">E338/E339</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F340" s="13" t="n">
         <f aca="false">F338/F339</f>
-        <v>10.7619400997283</v>
+        <v>10.5110507197992</v>
       </c>
       <c r="G340" s="13" t="n">
         <f aca="false">G338/G339</f>
-        <v>12.464529901681</v>
+        <v>12.1859625811742</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55329,15 +55329,15 @@
       </c>
       <c r="E341" s="10" t="n">
         <f aca="false">E330/E332</f>
-        <v>0.697479442127972</v>
+        <v>0.694554801249891</v>
       </c>
       <c r="F341" s="10" t="n">
         <f aca="false">F330/F332</f>
-        <v>0.687419445910729</v>
+        <v>0.681522633021292</v>
       </c>
       <c r="G341" s="10" t="n">
         <f aca="false">G330/G332</f>
-        <v>0.673680216546587</v>
+        <v>0.667686825442775</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55416,15 +55416,15 @@
       </c>
       <c r="E354" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F354" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G354" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H354" s="8" t="s">
         <v>506</v>
@@ -55443,15 +55443,15 @@
       </c>
       <c r="E355" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F355" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G355" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H355" s="8" t="s">
         <v>506</v>
@@ -55493,15 +55493,15 @@
       </c>
       <c r="E357" s="17" t="n">
         <f aca="false">SUM(E353:E356)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F357" s="17" t="n">
         <f aca="false">SUM(F353:F356)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G357" s="17" t="n">
         <f aca="false">SUM(G353:G356)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55553,15 +55553,15 @@
       </c>
       <c r="E360" s="17" t="n">
         <f aca="false">h2s26+h1s*E357</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F360" s="17" t="n">
         <f aca="false">(1-h1s)*E357+h1s*F357</f>
-        <v>26.1018954419896</v>
+        <v>25.3988409204097</v>
       </c>
       <c r="G360" s="17" t="n">
         <f aca="false">(1-h1s)*F357+h1s*G357</f>
-        <v>28.4236972034577</v>
+        <v>27.662754716098</v>
       </c>
       <c r="H360" s="8" t="s">
         <v>515</v>
@@ -55612,15 +55612,15 @@
       </c>
       <c r="E362" s="17" t="n">
         <f aca="false">E360+E361</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F362" s="17" t="n">
         <f aca="false">F360+F361</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G362" s="17" t="n">
         <f aca="false">G360+G361</f>
-        <v>41.4707470424977</v>
+        <v>40.709804555138</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55640,15 +55640,15 @@
       </c>
       <c r="E363" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E362)</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F363" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F362)</f>
-        <v>0.530054366629259</v>
+        <v>0.52907214052116</v>
       </c>
       <c r="G363" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G362)</f>
-        <v>0.534964444590398</v>
+        <v>0.533996833374025</v>
       </c>
       <c r="H363" s="5" t="s">
         <v>516</v>
@@ -55671,15 +55671,15 @@
       </c>
       <c r="E364" s="17" t="n">
         <f aca="false">E362*E363</f>
-        <v>18.1836381009569</v>
+        <v>17.9923018165092</v>
       </c>
       <c r="F364" s="17" t="n">
         <f aca="false">F362*F363</f>
-        <v>20.0101073516955</v>
+        <v>19.6010607270061</v>
       </c>
       <c r="G364" s="17" t="n">
         <f aca="false">G362*G363</f>
-        <v>22.1853751583387</v>
+        <v>21.7389067197192</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55699,15 +55699,15 @@
       </c>
       <c r="E365" s="17" t="n">
         <f aca="false">(1-phi_lo)*a26_opx+phi_lo*a26_opx/a26_rev*E362</f>
-        <v>3.78431007629361</v>
+        <v>3.77676856824803</v>
       </c>
       <c r="F365" s="17" t="n">
         <f aca="false">(1-phi_lo)*a26_opx+phi_lo*a26_opx/a26_rev*F362</f>
-        <v>3.85598263118507</v>
+        <v>3.83997956919222</v>
       </c>
       <c r="G365" s="17" t="n">
         <f aca="false">(1-phi_lo)*a26_opx+phi_lo*a26_opx/a26_rev*G362</f>
-        <v>3.94065115574994</v>
+        <v>3.92333043676665</v>
       </c>
       <c r="H365" s="5" t="s">
         <v>517</v>
@@ -55730,15 +55730,15 @@
       </c>
       <c r="E366" s="17" t="n">
         <f aca="false">E364-E365</f>
-        <v>14.3993280246633</v>
+        <v>14.2155332482611</v>
       </c>
       <c r="F366" s="17" t="n">
         <f aca="false">F364-F365</f>
-        <v>16.1541247205104</v>
+        <v>15.7610811578139</v>
       </c>
       <c r="G366" s="17" t="n">
         <f aca="false">G364-G365</f>
-        <v>18.2447240025888</v>
+        <v>17.8155762829525</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55758,15 +55758,15 @@
       </c>
       <c r="E367" s="10" t="n">
         <f aca="false">E366/E362</f>
-        <v>0.416137976932745</v>
+        <v>0.414798036529143</v>
       </c>
       <c r="F367" s="10" t="n">
         <f aca="false">F366/F362</f>
-        <v>0.427911964523003</v>
+        <v>0.425423351380331</v>
       </c>
       <c r="G367" s="10" t="n">
         <f aca="false">G366/G362</f>
-        <v>0.439942014642085</v>
+        <v>0.437623724251066</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55786,15 +55786,15 @@
       </c>
       <c r="E368" s="17" t="n">
         <f aca="false">(E366+oth_inc)*(1-tax)</f>
-        <v>12.1069389005938</v>
+        <v>11.953470262298</v>
       </c>
       <c r="F368" s="17" t="n">
         <f aca="false">(F366+oth_inc)*(1-tax)</f>
-        <v>13.5721941416262</v>
+        <v>13.2440027667746</v>
       </c>
       <c r="G368" s="17" t="n">
         <f aca="false">(G366+oth_inc)*(1-tax)</f>
-        <v>15.3178445421616</v>
+        <v>14.9595061962653</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55842,15 +55842,15 @@
       </c>
       <c r="E370" s="13" t="n">
         <f aca="false">E368/E369</f>
-        <v>9.6623614529879</v>
+        <v>9.53988049664648</v>
       </c>
       <c r="F370" s="13" t="n">
         <f aca="false">F368/F369</f>
-        <v>10.9967097375445</v>
+        <v>10.7307965587359</v>
       </c>
       <c r="G370" s="13" t="n">
         <f aca="false">G368/G369</f>
-        <v>12.600103880892</v>
+        <v>12.3053430631822</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55870,15 +55870,15 @@
       </c>
       <c r="E371" s="10" t="n">
         <f aca="false">E360/E362</f>
-        <v>0.697479442127972</v>
+        <v>0.694554801249891</v>
       </c>
       <c r="F371" s="10" t="n">
         <f aca="false">F360/F362</f>
-        <v>0.691421760671098</v>
+        <v>0.685565915012096</v>
       </c>
       <c r="G371" s="10" t="n">
         <f aca="false">G360/G362</f>
-        <v>0.685391492329042</v>
+        <v>0.679510870130343</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55957,15 +55957,15 @@
       </c>
       <c r="E384" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F384" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G384" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H384" s="8" t="s">
         <v>506</v>
@@ -55984,15 +55984,15 @@
       </c>
       <c r="E385" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F385" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G385" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H385" s="8" t="s">
         <v>506</v>
@@ -56034,15 +56034,15 @@
       </c>
       <c r="E387" s="17" t="n">
         <f aca="false">SUM(E383:E386)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F387" s="17" t="n">
         <f aca="false">SUM(F383:F386)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G387" s="17" t="n">
         <f aca="false">SUM(G383:G386)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56094,15 +56094,15 @@
       </c>
       <c r="E390" s="17" t="n">
         <f aca="false">h2s26+h1s*E387</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F390" s="17" t="n">
         <f aca="false">(1-h1s)*E387+h1s*F387</f>
-        <v>26.1018954419896</v>
+        <v>25.3988409204097</v>
       </c>
       <c r="G390" s="17" t="n">
         <f aca="false">(1-h1s)*F387+h1s*G387</f>
-        <v>28.4236972034577</v>
+        <v>27.662754716098</v>
       </c>
       <c r="H390" s="8" t="s">
         <v>515</v>
@@ -56153,15 +56153,15 @@
       </c>
       <c r="E392" s="17" t="n">
         <f aca="false">E390+E391</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F392" s="17" t="n">
         <f aca="false">F390+F391</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G392" s="17" t="n">
         <f aca="false">G390+G391</f>
-        <v>41.4707470424977</v>
+        <v>40.709804555138</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56181,15 +56181,15 @@
       </c>
       <c r="E393" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E392)</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F393" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F392)</f>
-        <v>0.530054366629259</v>
+        <v>0.52907214052116</v>
       </c>
       <c r="G393" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G392)</f>
-        <v>0.534964444590398</v>
+        <v>0.533996833374025</v>
       </c>
       <c r="H393" s="5" t="s">
         <v>516</v>
@@ -56212,15 +56212,15 @@
       </c>
       <c r="E394" s="17" t="n">
         <f aca="false">E392*E393</f>
-        <v>18.1836381009569</v>
+        <v>17.9923018165092</v>
       </c>
       <c r="F394" s="17" t="n">
         <f aca="false">F392*F393</f>
-        <v>20.0101073516955</v>
+        <v>19.6010607270061</v>
       </c>
       <c r="G394" s="17" t="n">
         <f aca="false">G392*G393</f>
-        <v>22.1853751583387</v>
+        <v>21.7389067197192</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56240,15 +56240,15 @@
       </c>
       <c r="E395" s="17" t="n">
         <f aca="false">(1-phi_hi)*a26_opx+phi_hi*a26_opx/a26_rev*E392</f>
-        <v>4.3881699209787</v>
+        <v>4.36303156082678</v>
       </c>
       <c r="F395" s="17" t="n">
         <f aca="false">(1-phi_hi)*a26_opx+phi_hi*a26_opx/a26_rev*F392</f>
-        <v>4.62707843728358</v>
+        <v>4.57373489730739</v>
       </c>
       <c r="G395" s="17" t="n">
         <f aca="false">(1-phi_hi)*a26_opx+phi_hi*a26_opx/a26_rev*G392</f>
-        <v>4.9093068524998</v>
+        <v>4.85157112255551</v>
       </c>
       <c r="H395" s="5" t="s">
         <v>517</v>
@@ -56271,15 +56271,15 @@
       </c>
       <c r="E396" s="17" t="n">
         <f aca="false">E394-E395</f>
-        <v>13.7954681799782</v>
+        <v>13.6292702556824</v>
       </c>
       <c r="F396" s="17" t="n">
         <f aca="false">F394-F395</f>
-        <v>15.3830289144119</v>
+        <v>15.0273258296987</v>
       </c>
       <c r="G396" s="17" t="n">
         <f aca="false">G394-G395</f>
-        <v>17.2760683058389</v>
+        <v>16.8873355971637</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56299,15 +56299,15 @@
       </c>
       <c r="E397" s="10" t="n">
         <f aca="false">E396/E392</f>
-        <v>0.398686536581656</v>
+        <v>0.397691345280603</v>
       </c>
       <c r="F397" s="10" t="n">
         <f aca="false">F396/F392</f>
-        <v>0.407486152110887</v>
+        <v>0.405617815982451</v>
       </c>
       <c r="G397" s="10" t="n">
         <f aca="false">G396/G392</f>
-        <v>0.416584448988464</v>
+        <v>0.414822320610534</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56327,15 +56327,15 @@
       </c>
       <c r="E398" s="17" t="n">
         <f aca="false">(E396+oth_inc)*(1-tax)</f>
-        <v>11.6027159302818</v>
+        <v>11.4639406634948</v>
       </c>
       <c r="F398" s="17" t="n">
         <f aca="false">(F396+oth_inc)*(1-tax)</f>
-        <v>12.9283291435339</v>
+        <v>12.6313170677984</v>
       </c>
       <c r="G398" s="17" t="n">
         <f aca="false">(G396+oth_inc)*(1-tax)</f>
-        <v>14.5090170353755</v>
+        <v>14.1844252236317</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56383,15 +56383,15 @@
       </c>
       <c r="E400" s="13" t="n">
         <f aca="false">E398/E399</f>
-        <v>9.25994886694476</v>
+        <v>9.14919446408203</v>
       </c>
       <c r="F400" s="13" t="n">
         <f aca="false">F398/F399</f>
-        <v>10.4750257400788</v>
+        <v>10.2343752195125</v>
       </c>
       <c r="G400" s="13" t="n">
         <f aca="false">G398/G399</f>
-        <v>11.9347811209452</v>
+        <v>11.6677794200465</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56411,15 +56411,15 @@
       </c>
       <c r="E401" s="10" t="n">
         <f aca="false">E390/E392</f>
-        <v>0.697479442127972</v>
+        <v>0.694554801249891</v>
       </c>
       <c r="F401" s="10" t="n">
         <f aca="false">F390/F392</f>
-        <v>0.691421760671098</v>
+        <v>0.685565915012096</v>
       </c>
       <c r="G401" s="10" t="n">
         <f aca="false">G390/G392</f>
-        <v>0.685391492329042</v>
+        <v>0.679510870130343</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56498,15 +56498,15 @@
       </c>
       <c r="E414" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F414" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G414" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H414" s="8" t="s">
         <v>506</v>
@@ -56525,15 +56525,15 @@
       </c>
       <c r="E415" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F415" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G415" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H415" s="8" t="s">
         <v>506</v>
@@ -56575,15 +56575,15 @@
       </c>
       <c r="E417" s="17" t="n">
         <f aca="false">SUM(E413:E416)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F417" s="17" t="n">
         <f aca="false">SUM(F413:F416)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G417" s="17" t="n">
         <f aca="false">SUM(G413:G416)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56635,15 +56635,15 @@
       </c>
       <c r="E420" s="17" t="n">
         <f aca="false">h2s26+h1s*E417</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F420" s="17" t="n">
         <f aca="false">(1-h1s)*E417+h1s*F417</f>
-        <v>26.1018954419896</v>
+        <v>25.3988409204097</v>
       </c>
       <c r="G420" s="17" t="n">
         <f aca="false">(1-h1s)*F417+h1s*G417</f>
-        <v>28.4236972034577</v>
+        <v>27.662754716098</v>
       </c>
       <c r="H420" s="8" t="s">
         <v>515</v>
@@ -56694,15 +56694,15 @@
       </c>
       <c r="E422" s="17" t="n">
         <f aca="false">E420+E421</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F422" s="17" t="n">
         <f aca="false">F420+F421</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G422" s="17" t="n">
         <f aca="false">G420+G421</f>
-        <v>41.4707470424977</v>
+        <v>40.709804555138</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56722,15 +56722,15 @@
       </c>
       <c r="E423" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E422)</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F423" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F422)</f>
-        <v>0.530054366629259</v>
+        <v>0.52907214052116</v>
       </c>
       <c r="G423" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G422)</f>
-        <v>0.534964444590398</v>
+        <v>0.533996833374025</v>
       </c>
       <c r="H423" s="5" t="s">
         <v>516</v>
@@ -56753,15 +56753,15 @@
       </c>
       <c r="E424" s="17" t="n">
         <f aca="false">E422*E423</f>
-        <v>18.1836381009569</v>
+        <v>17.9923018165092</v>
       </c>
       <c r="F424" s="17" t="n">
         <f aca="false">F422*F423</f>
-        <v>20.0101073516955</v>
+        <v>19.6010607270061</v>
       </c>
       <c r="G424" s="17" t="n">
         <f aca="false">G422*G423</f>
-        <v>22.1853751583387</v>
+        <v>21.7389067197192</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56781,15 +56781,15 @@
       </c>
       <c r="E425" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E422</f>
-        <v>4.14690889358399</v>
+        <v>4.12880103008697</v>
       </c>
       <c r="F425" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F422</f>
-        <v>4.31900137596466</v>
+        <v>4.28057653303542</v>
       </c>
       <c r="G425" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G422</f>
-        <v>4.52229839242993</v>
+        <v>4.48070973229404</v>
       </c>
       <c r="H425" s="5" t="s">
         <v>517</v>
@@ -56812,15 +56812,15 @@
       </c>
       <c r="E426" s="17" t="n">
         <f aca="false">E424-E425</f>
-        <v>14.0367292073729</v>
+        <v>13.8635007864222</v>
       </c>
       <c r="F426" s="17" t="n">
         <f aca="false">F424-F425</f>
-        <v>15.6911059757308</v>
+        <v>15.3204841939707</v>
       </c>
       <c r="G426" s="17" t="n">
         <f aca="false">G424-G425</f>
-        <v>17.6630767659088</v>
+        <v>17.2581969874251</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56840,15 +56840,15 @@
       </c>
       <c r="E427" s="10" t="n">
         <f aca="false">E426/E422</f>
-        <v>0.405658936660381</v>
+        <v>0.404526007234486</v>
       </c>
       <c r="F427" s="10" t="n">
         <f aca="false">F426/F422</f>
-        <v>0.415646907510161</v>
+        <v>0.413530751178012</v>
       </c>
       <c r="G427" s="10" t="n">
         <f aca="false">G426/G422</f>
-        <v>0.425916532147547</v>
+        <v>0.423932199528257</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56868,15 +56868,15 @@
       </c>
       <c r="E428" s="17" t="n">
         <f aca="false">(E426+oth_inc)*(1-tax_lo)</f>
-        <v>12.2989544104144</v>
+        <v>12.1482456841873</v>
       </c>
       <c r="F428" s="17" t="n">
         <f aca="false">(F426+oth_inc)*(1-tax_lo)</f>
-        <v>13.7382621988858</v>
+        <v>13.4158212487545</v>
       </c>
       <c r="G428" s="17" t="n">
         <f aca="false">(G426+oth_inc)*(1-tax_lo)</f>
-        <v>15.4538767863406</v>
+        <v>15.1016313790599</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56924,15 +56924,15 @@
       </c>
       <c r="E430" s="13" t="n">
         <f aca="false">E428/E429</f>
-        <v>9.81560607375453</v>
+        <v>9.6953277607241</v>
       </c>
       <c r="F430" s="13" t="n">
         <f aca="false">F428/F429</f>
-        <v>11.1312644162727</v>
+        <v>10.8700104510633</v>
       </c>
       <c r="G430" s="13" t="n">
         <f aca="false">G428/G429</f>
-        <v>12.7120008519762</v>
+        <v>12.4222519443484</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56952,15 +56952,15 @@
       </c>
       <c r="E431" s="10" t="n">
         <f aca="false">E420/E422</f>
-        <v>0.697479442127972</v>
+        <v>0.694554801249891</v>
       </c>
       <c r="F431" s="10" t="n">
         <f aca="false">F420/F422</f>
-        <v>0.691421760671098</v>
+        <v>0.685565915012096</v>
       </c>
       <c r="G431" s="10" t="n">
         <f aca="false">G420/G422</f>
-        <v>0.685391492329042</v>
+        <v>0.679510870130343</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57039,15 +57039,15 @@
       </c>
       <c r="E444" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F444" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G444" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H444" s="8" t="s">
         <v>506</v>
@@ -57066,15 +57066,15 @@
       </c>
       <c r="E445" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F445" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G445" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H445" s="8" t="s">
         <v>506</v>
@@ -57116,15 +57116,15 @@
       </c>
       <c r="E447" s="17" t="n">
         <f aca="false">SUM(E443:E446)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F447" s="17" t="n">
         <f aca="false">SUM(F443:F446)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G447" s="17" t="n">
         <f aca="false">SUM(G443:G446)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="448" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57176,15 +57176,15 @@
       </c>
       <c r="E450" s="17" t="n">
         <f aca="false">h2s26+h1s*E447</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F450" s="17" t="n">
         <f aca="false">(1-h1s)*E447+h1s*F447</f>
-        <v>26.1018954419896</v>
+        <v>25.3988409204097</v>
       </c>
       <c r="G450" s="17" t="n">
         <f aca="false">(1-h1s)*F447+h1s*G447</f>
-        <v>28.4236972034577</v>
+        <v>27.662754716098</v>
       </c>
       <c r="H450" s="8" t="s">
         <v>515</v>
@@ -57235,15 +57235,15 @@
       </c>
       <c r="E452" s="17" t="n">
         <f aca="false">E450+E451</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F452" s="17" t="n">
         <f aca="false">F450+F451</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G452" s="17" t="n">
         <f aca="false">G450+G451</f>
-        <v>41.4707470424977</v>
+        <v>40.709804555138</v>
       </c>
     </row>
     <row r="453" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57263,15 +57263,15 @@
       </c>
       <c r="E453" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E452)</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F453" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F452)</f>
-        <v>0.530054366629259</v>
+        <v>0.52907214052116</v>
       </c>
       <c r="G453" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G452)</f>
-        <v>0.534964444590398</v>
+        <v>0.533996833374025</v>
       </c>
       <c r="H453" s="5" t="s">
         <v>516</v>
@@ -57294,15 +57294,15 @@
       </c>
       <c r="E454" s="17" t="n">
         <f aca="false">E452*E453</f>
-        <v>18.1836381009569</v>
+        <v>17.9923018165092</v>
       </c>
       <c r="F454" s="17" t="n">
         <f aca="false">F452*F453</f>
-        <v>20.0101073516955</v>
+        <v>19.6010607270061</v>
       </c>
       <c r="G454" s="17" t="n">
         <f aca="false">G452*G453</f>
-        <v>22.1853751583387</v>
+        <v>21.7389067197192</v>
       </c>
     </row>
     <row r="455" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57322,15 +57322,15 @@
       </c>
       <c r="E455" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E452</f>
-        <v>4.14690889358399</v>
+        <v>4.12880103008697</v>
       </c>
       <c r="F455" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F452</f>
-        <v>4.31900137596466</v>
+        <v>4.28057653303542</v>
       </c>
       <c r="G455" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G452</f>
-        <v>4.52229839242993</v>
+        <v>4.48070973229404</v>
       </c>
       <c r="H455" s="5" t="s">
         <v>517</v>
@@ -57353,15 +57353,15 @@
       </c>
       <c r="E456" s="17" t="n">
         <f aca="false">E454-E455</f>
-        <v>14.0367292073729</v>
+        <v>13.8635007864222</v>
       </c>
       <c r="F456" s="17" t="n">
         <f aca="false">F454-F455</f>
-        <v>15.6911059757308</v>
+        <v>15.3204841939707</v>
       </c>
       <c r="G456" s="17" t="n">
         <f aca="false">G454-G455</f>
-        <v>17.6630767659088</v>
+        <v>17.2581969874251</v>
       </c>
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57381,15 +57381,15 @@
       </c>
       <c r="E457" s="10" t="n">
         <f aca="false">E456/E452</f>
-        <v>0.405658936660381</v>
+        <v>0.404526007234486</v>
       </c>
       <c r="F457" s="10" t="n">
         <f aca="false">F456/F452</f>
-        <v>0.415646907510161</v>
+        <v>0.413530751178012</v>
       </c>
       <c r="G457" s="10" t="n">
         <f aca="false">G456/G452</f>
-        <v>0.425916532147547</v>
+        <v>0.423932199528257</v>
       </c>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57409,15 +57409,15 @@
       </c>
       <c r="E458" s="17" t="n">
         <f aca="false">(E456+oth_inc)*(1-tax_hi)</f>
-        <v>11.4507506579721</v>
+        <v>11.310435637002</v>
       </c>
       <c r="F458" s="17" t="n">
         <f aca="false">(F456+oth_inc)*(1-tax_hi)</f>
-        <v>12.7907958403419</v>
+        <v>12.4905921971163</v>
       </c>
       <c r="G458" s="17" t="n">
         <f aca="false">(G456+oth_inc)*(1-tax_hi)</f>
-        <v>14.3880921803861</v>
+        <v>14.0601395598144</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57465,15 +57465,15 @@
       </c>
       <c r="E460" s="13" t="n">
         <f aca="false">E458/E459</f>
-        <v>9.13866772384042</v>
+        <v>9.02668446688106</v>
       </c>
       <c r="F460" s="13" t="n">
         <f aca="false">F458/F459</f>
-        <v>10.3635910082538</v>
+        <v>10.1203545578865</v>
       </c>
       <c r="G460" s="13" t="n">
         <f aca="false">G458/G459</f>
-        <v>11.8353111380468</v>
+        <v>11.5655449137037</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57493,15 +57493,15 @@
       </c>
       <c r="E461" s="10" t="n">
         <f aca="false">E450/E452</f>
-        <v>0.697479442127972</v>
+        <v>0.694554801249891</v>
       </c>
       <c r="F461" s="10" t="n">
         <f aca="false">F450/F452</f>
-        <v>0.691421760671098</v>
+        <v>0.685565915012096</v>
       </c>
       <c r="G461" s="10" t="n">
         <f aca="false">G450/G452</f>
-        <v>0.685391492329042</v>
+        <v>0.679510870130343</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57580,15 +57580,15 @@
       </c>
       <c r="E474" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F474" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G474" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H474" s="8" t="s">
         <v>506</v>
@@ -57607,15 +57607,15 @@
       </c>
       <c r="E475" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F475" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G475" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H475" s="8" t="s">
         <v>506</v>
@@ -57657,15 +57657,15 @@
       </c>
       <c r="E477" s="17" t="n">
         <f aca="false">SUM(E473:E476)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F477" s="17" t="n">
         <f aca="false">SUM(F473:F476)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G477" s="17" t="n">
         <f aca="false">SUM(G473:G476)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="478" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57717,15 +57717,15 @@
       </c>
       <c r="E480" s="17" t="n">
         <f aca="false">h2s26+h1s*E477</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F480" s="17" t="n">
         <f aca="false">(1-h1s)*E477+h1s*F477</f>
-        <v>26.1018954419896</v>
+        <v>25.3988409204097</v>
       </c>
       <c r="G480" s="17" t="n">
         <f aca="false">(1-h1s)*F477+h1s*G477</f>
-        <v>28.4236972034577</v>
+        <v>27.662754716098</v>
       </c>
       <c r="H480" s="8" t="s">
         <v>515</v>
@@ -57776,15 +57776,15 @@
       </c>
       <c r="E482" s="17" t="n">
         <f aca="false">E480+E481</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F482" s="17" t="n">
         <f aca="false">F480+F481</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G482" s="17" t="n">
         <f aca="false">G480+G481</f>
-        <v>41.4707470424977</v>
+        <v>40.709804555138</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57804,15 +57804,15 @@
       </c>
       <c r="E483" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E482)</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F483" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F482)</f>
-        <v>0.530054366629259</v>
+        <v>0.52907214052116</v>
       </c>
       <c r="G483" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G482)</f>
-        <v>0.534964444590398</v>
+        <v>0.533996833374025</v>
       </c>
       <c r="H483" s="5" t="s">
         <v>516</v>
@@ -57835,15 +57835,15 @@
       </c>
       <c r="E484" s="17" t="n">
         <f aca="false">E482*E483</f>
-        <v>18.1836381009569</v>
+        <v>17.9923018165092</v>
       </c>
       <c r="F484" s="17" t="n">
         <f aca="false">F482*F483</f>
-        <v>20.0101073516955</v>
+        <v>19.6010607270061</v>
       </c>
       <c r="G484" s="17" t="n">
         <f aca="false">G482*G483</f>
-        <v>22.1853751583387</v>
+        <v>21.7389067197192</v>
       </c>
     </row>
     <row r="485" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57863,15 +57863,15 @@
       </c>
       <c r="E485" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E482</f>
-        <v>4.14690889358399</v>
+        <v>4.12880103008697</v>
       </c>
       <c r="F485" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F482</f>
-        <v>4.31900137596466</v>
+        <v>4.28057653303542</v>
       </c>
       <c r="G485" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G482</f>
-        <v>4.52229839242993</v>
+        <v>4.48070973229404</v>
       </c>
       <c r="H485" s="5" t="s">
         <v>517</v>
@@ -57894,15 +57894,15 @@
       </c>
       <c r="E486" s="17" t="n">
         <f aca="false">E484-E485</f>
-        <v>14.0367292073729</v>
+        <v>13.8635007864222</v>
       </c>
       <c r="F486" s="17" t="n">
         <f aca="false">F484-F485</f>
-        <v>15.6911059757308</v>
+        <v>15.3204841939707</v>
       </c>
       <c r="G486" s="17" t="n">
         <f aca="false">G484-G485</f>
-        <v>17.6630767659088</v>
+        <v>17.2581969874251</v>
       </c>
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57922,15 +57922,15 @@
       </c>
       <c r="E487" s="10" t="n">
         <f aca="false">E486/E482</f>
-        <v>0.405658936660381</v>
+        <v>0.404526007234486</v>
       </c>
       <c r="F487" s="10" t="n">
         <f aca="false">F486/F482</f>
-        <v>0.415646907510161</v>
+        <v>0.413530751178012</v>
       </c>
       <c r="G487" s="10" t="n">
         <f aca="false">G486/G482</f>
-        <v>0.425916532147547</v>
+        <v>0.423932199528257</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57950,15 +57950,15 @@
       </c>
       <c r="E488" s="17" t="n">
         <f aca="false">(E486+oth_inc)*(1-tax)</f>
-        <v>11.8041688881564</v>
+        <v>11.6595231566625</v>
       </c>
       <c r="F488" s="17" t="n">
         <f aca="false">(F486+oth_inc)*(1-tax)</f>
-        <v>13.1855734897352</v>
+        <v>12.8761043019655</v>
       </c>
       <c r="G488" s="17" t="n">
         <f aca="false">(G486+oth_inc)*(1-tax)</f>
-        <v>14.8321690995338</v>
+        <v>14.4940944845</v>
       </c>
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58006,15 +58006,15 @@
       </c>
       <c r="E490" s="13" t="n">
         <f aca="false">E488/E489</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F490" s="13" t="n">
         <f aca="false">F488/F489</f>
-        <v>10.5232031043378</v>
+        <v>10.2762205123428</v>
       </c>
       <c r="G490" s="13" t="n">
         <f aca="false">G488/G489</f>
-        <v>11.837325697952</v>
+        <v>11.5675135550678</v>
       </c>
     </row>
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58034,15 +58034,15 @@
       </c>
       <c r="E491" s="10" t="n">
         <f aca="false">E480/E482</f>
-        <v>0.697479442127972</v>
+        <v>0.694554801249891</v>
       </c>
       <c r="F491" s="10" t="n">
         <f aca="false">F480/F482</f>
-        <v>0.691421760671098</v>
+        <v>0.685565915012096</v>
       </c>
       <c r="G491" s="10" t="n">
         <f aca="false">G480/G482</f>
-        <v>0.685391492329042</v>
+        <v>0.679510870130343</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58121,15 +58121,15 @@
       </c>
       <c r="E504" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F504" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G504" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H504" s="8" t="s">
         <v>506</v>
@@ -58148,15 +58148,15 @@
       </c>
       <c r="E505" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F505" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G505" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H505" s="8" t="s">
         <v>506</v>
@@ -58198,15 +58198,15 @@
       </c>
       <c r="E507" s="17" t="n">
         <f aca="false">SUM(E503:E506)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F507" s="17" t="n">
         <f aca="false">SUM(F503:F506)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G507" s="17" t="n">
         <f aca="false">SUM(G503:G506)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58258,15 +58258,15 @@
       </c>
       <c r="E510" s="17" t="n">
         <f aca="false">h2s26+h1s*E507</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F510" s="17" t="n">
         <f aca="false">(1-h1s)*E507+h1s*F507</f>
-        <v>26.1018954419896</v>
+        <v>25.3988409204097</v>
       </c>
       <c r="G510" s="17" t="n">
         <f aca="false">(1-h1s)*F507+h1s*G507</f>
-        <v>28.4236972034577</v>
+        <v>27.662754716098</v>
       </c>
       <c r="H510" s="8" t="s">
         <v>515</v>
@@ -58317,15 +58317,15 @@
       </c>
       <c r="E512" s="17" t="n">
         <f aca="false">E510+E511</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F512" s="17" t="n">
         <f aca="false">F510+F511</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G512" s="17" t="n">
         <f aca="false">G510+G511</f>
-        <v>41.4707470424977</v>
+        <v>40.709804555138</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58345,15 +58345,15 @@
       </c>
       <c r="E513" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E512)</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F513" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F512)</f>
-        <v>0.530054366629259</v>
+        <v>0.52907214052116</v>
       </c>
       <c r="G513" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G512)</f>
-        <v>0.534964444590398</v>
+        <v>0.533996833374025</v>
       </c>
       <c r="H513" s="5" t="s">
         <v>516</v>
@@ -58376,15 +58376,15 @@
       </c>
       <c r="E514" s="17" t="n">
         <f aca="false">E512*E513</f>
-        <v>18.1836381009569</v>
+        <v>17.9923018165092</v>
       </c>
       <c r="F514" s="17" t="n">
         <f aca="false">F512*F513</f>
-        <v>20.0101073516955</v>
+        <v>19.6010607270061</v>
       </c>
       <c r="G514" s="17" t="n">
         <f aca="false">G512*G513</f>
-        <v>22.1853751583387</v>
+        <v>21.7389067197192</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58404,15 +58404,15 @@
       </c>
       <c r="E515" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E512</f>
-        <v>4.14690889358399</v>
+        <v>4.12880103008697</v>
       </c>
       <c r="F515" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F512</f>
-        <v>4.31900137596466</v>
+        <v>4.28057653303542</v>
       </c>
       <c r="G515" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G512</f>
-        <v>4.52229839242993</v>
+        <v>4.48070973229404</v>
       </c>
       <c r="H515" s="5" t="s">
         <v>517</v>
@@ -58435,15 +58435,15 @@
       </c>
       <c r="E516" s="17" t="n">
         <f aca="false">E514-E515</f>
-        <v>14.0367292073729</v>
+        <v>13.8635007864222</v>
       </c>
       <c r="F516" s="17" t="n">
         <f aca="false">F514-F515</f>
-        <v>15.6911059757308</v>
+        <v>15.3204841939707</v>
       </c>
       <c r="G516" s="17" t="n">
         <f aca="false">G514-G515</f>
-        <v>17.6630767659088</v>
+        <v>17.2581969874251</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58463,15 +58463,15 @@
       </c>
       <c r="E517" s="10" t="n">
         <f aca="false">E516/E512</f>
-        <v>0.405658936660381</v>
+        <v>0.404526007234486</v>
       </c>
       <c r="F517" s="10" t="n">
         <f aca="false">F516/F512</f>
-        <v>0.415646907510161</v>
+        <v>0.413530751178012</v>
       </c>
       <c r="G517" s="10" t="n">
         <f aca="false">G516/G512</f>
-        <v>0.425916532147547</v>
+        <v>0.423932199528257</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58491,15 +58491,15 @@
       </c>
       <c r="E518" s="17" t="n">
         <f aca="false">(E516+oth_inc)*(1-tax)</f>
-        <v>11.8041688881564</v>
+        <v>11.6595231566625</v>
       </c>
       <c r="F518" s="17" t="n">
         <f aca="false">(F516+oth_inc)*(1-tax)</f>
-        <v>13.1855734897352</v>
+        <v>12.8761043019655</v>
       </c>
       <c r="G518" s="17" t="n">
         <f aca="false">(G516+oth_inc)*(1-tax)</f>
-        <v>14.8321690995338</v>
+        <v>14.4940944845</v>
       </c>
     </row>
     <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58547,15 +58547,15 @@
       </c>
       <c r="E520" s="13" t="n">
         <f aca="false">E518/E519</f>
-        <v>9.42072536963797</v>
+        <v>9.30528583931566</v>
       </c>
       <c r="F520" s="13" t="n">
         <f aca="false">F518/F519</f>
-        <v>10.8486629941626</v>
+        <v>10.5940417653019</v>
       </c>
       <c r="G520" s="13" t="n">
         <f aca="false">G518/G519</f>
-        <v>12.5808541799893</v>
+        <v>12.2940945425314</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58575,15 +58575,15 @@
       </c>
       <c r="E521" s="10" t="n">
         <f aca="false">E510/E512</f>
-        <v>0.697479442127972</v>
+        <v>0.694554801249891</v>
       </c>
       <c r="F521" s="10" t="n">
         <f aca="false">F510/F512</f>
-        <v>0.691421760671098</v>
+        <v>0.685565915012096</v>
       </c>
       <c r="G521" s="10" t="n">
         <f aca="false">G510/G512</f>
-        <v>0.685391492329042</v>
+        <v>0.679510870130343</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58662,15 +58662,15 @@
       </c>
       <c r="E534" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F534" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G534" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H534" s="8" t="s">
         <v>506</v>
@@ -58689,15 +58689,15 @@
       </c>
       <c r="E535" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F535" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G535" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H535" s="8" t="s">
         <v>506</v>
@@ -58739,15 +58739,15 @@
       </c>
       <c r="E537" s="17" t="n">
         <f aca="false">SUM(E533:E536)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F537" s="17" t="n">
         <f aca="false">SUM(F533:F536)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G537" s="17" t="n">
         <f aca="false">SUM(G533:G536)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58799,15 +58799,15 @@
       </c>
       <c r="E540" s="17" t="n">
         <f aca="false">h2s26+h1s*E537</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F540" s="17" t="n">
         <f aca="false">(1-h1s)*E537+h1s*F537</f>
-        <v>26.1018954419896</v>
+        <v>25.3988409204097</v>
       </c>
       <c r="G540" s="17" t="n">
         <f aca="false">(1-h1s)*F537+h1s*G537</f>
-        <v>28.4236972034577</v>
+        <v>27.662754716098</v>
       </c>
       <c r="H540" s="8" t="s">
         <v>515</v>
@@ -58858,15 +58858,15 @@
       </c>
       <c r="E542" s="17" t="n">
         <f aca="false">E540+E541</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F542" s="17" t="n">
         <f aca="false">F540+F541</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G542" s="17" t="n">
         <f aca="false">G540+G541</f>
-        <v>41.4707470424977</v>
+        <v>40.709804555138</v>
       </c>
     </row>
     <row r="543" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58886,15 +58886,15 @@
       </c>
       <c r="E543" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E542)</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F543" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F542)</f>
-        <v>0.530054366629259</v>
+        <v>0.52907214052116</v>
       </c>
       <c r="G543" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G542)</f>
-        <v>0.534964444590398</v>
+        <v>0.533996833374025</v>
       </c>
       <c r="H543" s="5" t="s">
         <v>516</v>
@@ -58917,15 +58917,15 @@
       </c>
       <c r="E544" s="17" t="n">
         <f aca="false">E542*E543</f>
-        <v>18.1836381009569</v>
+        <v>17.9923018165092</v>
       </c>
       <c r="F544" s="17" t="n">
         <f aca="false">F542*F543</f>
-        <v>20.0101073516955</v>
+        <v>19.6010607270061</v>
       </c>
       <c r="G544" s="17" t="n">
         <f aca="false">G542*G543</f>
-        <v>22.1853751583387</v>
+        <v>21.7389067197192</v>
       </c>
     </row>
     <row r="545" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58945,15 +58945,15 @@
       </c>
       <c r="E545" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E542</f>
-        <v>4.14690889358399</v>
+        <v>4.12880103008697</v>
       </c>
       <c r="F545" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F542</f>
-        <v>4.31900137596466</v>
+        <v>4.28057653303542</v>
       </c>
       <c r="G545" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G542</f>
-        <v>4.52229839242993</v>
+        <v>4.48070973229404</v>
       </c>
       <c r="H545" s="5" t="s">
         <v>517</v>
@@ -58976,15 +58976,15 @@
       </c>
       <c r="E546" s="17" t="n">
         <f aca="false">E544-E545</f>
-        <v>14.0367292073729</v>
+        <v>13.8635007864222</v>
       </c>
       <c r="F546" s="17" t="n">
         <f aca="false">F544-F545</f>
-        <v>15.6911059757308</v>
+        <v>15.3204841939707</v>
       </c>
       <c r="G546" s="17" t="n">
         <f aca="false">G544-G545</f>
-        <v>17.6630767659088</v>
+        <v>17.2581969874251</v>
       </c>
     </row>
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59004,15 +59004,15 @@
       </c>
       <c r="E547" s="10" t="n">
         <f aca="false">E546/E542</f>
-        <v>0.405658936660381</v>
+        <v>0.404526007234486</v>
       </c>
       <c r="F547" s="10" t="n">
         <f aca="false">F546/F542</f>
-        <v>0.415646907510161</v>
+        <v>0.413530751178012</v>
       </c>
       <c r="G547" s="10" t="n">
         <f aca="false">G546/G542</f>
-        <v>0.425916532147547</v>
+        <v>0.423932199528257</v>
       </c>
     </row>
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59032,15 +59032,15 @@
       </c>
       <c r="E548" s="17" t="n">
         <f aca="false">(E546+oth_inc_lo)*(1-tax)</f>
-        <v>11.7206688881564</v>
+        <v>11.5760231566625</v>
       </c>
       <c r="F548" s="17" t="n">
         <f aca="false">(F546+oth_inc_lo)*(1-tax)</f>
-        <v>13.1020734897352</v>
+        <v>12.7926043019655</v>
       </c>
       <c r="G548" s="17" t="n">
         <f aca="false">(G546+oth_inc_lo)*(1-tax)</f>
-        <v>14.7486690995338</v>
+        <v>14.4105944845</v>
       </c>
     </row>
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59088,15 +59088,15 @@
       </c>
       <c r="E550" s="13" t="n">
         <f aca="false">E548/E549</f>
-        <v>9.3540853057912</v>
+        <v>9.23864577546889</v>
       </c>
       <c r="F550" s="13" t="n">
         <f aca="false">F548/F549</f>
-        <v>10.6158000411076</v>
+        <v>10.3650562928894</v>
       </c>
       <c r="G550" s="13" t="n">
         <f aca="false">G548/G549</f>
-        <v>12.1319133542273</v>
+        <v>11.8538210118489</v>
       </c>
     </row>
     <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59116,15 +59116,15 @@
       </c>
       <c r="E551" s="10" t="n">
         <f aca="false">E540/E542</f>
-        <v>0.697479442127972</v>
+        <v>0.694554801249891</v>
       </c>
       <c r="F551" s="10" t="n">
         <f aca="false">F540/F542</f>
-        <v>0.691421760671098</v>
+        <v>0.685565915012096</v>
       </c>
       <c r="G551" s="10" t="n">
         <f aca="false">G540/G542</f>
-        <v>0.685391492329042</v>
+        <v>0.679510870130343</v>
       </c>
     </row>
     <row r="560" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59203,15 +59203,15 @@
       </c>
       <c r="E564" s="17" t="n">
         <f aca="false">k_dram*dramA_27*(1+drift)^1</f>
-        <v>5.89058856743509</v>
+        <v>5.53773270836831</v>
       </c>
       <c r="F564" s="17" t="n">
         <f aca="false">k_dram*dramA_28*(1+drift)^2</f>
-        <v>6.58762867798361</v>
+        <v>6.19301897985713</v>
       </c>
       <c r="G564" s="17" t="n">
         <f aca="false">k_dram*dramA_29*(1+drift)^3</f>
-        <v>6.83874153475859</v>
+        <v>6.42908976710277</v>
       </c>
       <c r="H564" s="8" t="s">
         <v>506</v>
@@ -59230,15 +59230,15 @@
       </c>
       <c r="E565" s="17" t="n">
         <f aca="false">k_nand*nandA_27*(1+drift)^1</f>
-        <v>5.98363389745604</v>
+        <v>5.67385515155284</v>
       </c>
       <c r="F565" s="17" t="n">
         <f aca="false">k_nand*nandA_28*(1+drift)^2</f>
-        <v>6.7386123543875</v>
+        <v>6.38974761432419</v>
       </c>
       <c r="G565" s="17" t="n">
         <f aca="false">k_nand*nandA_29*(1+drift)^3</f>
-        <v>7.12288205242611</v>
+        <v>6.75412328355238</v>
       </c>
       <c r="H565" s="8" t="s">
         <v>506</v>
@@ -59280,15 +59280,15 @@
       </c>
       <c r="E567" s="17" t="n">
         <f aca="false">SUM(E563:E566)</f>
-        <v>24.5759834272568</v>
+        <v>23.9133488222868</v>
       </c>
       <c r="F567" s="17" t="n">
         <f aca="false">SUM(F563:F566)</f>
-        <v>27.6278074567225</v>
+        <v>26.8843330185327</v>
       </c>
       <c r="G567" s="17" t="n">
         <f aca="false">SUM(G563:G566)</f>
-        <v>29.2195869501929</v>
+        <v>28.4411764136634</v>
       </c>
     </row>
     <row r="568" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59340,15 +59340,15 @@
       </c>
       <c r="E570" s="17" t="n">
         <f aca="false">h2s26+h1s*E567</f>
-        <v>24.1343877136284</v>
+        <v>23.8030704111434</v>
       </c>
       <c r="F570" s="17" t="n">
         <f aca="false">(1-h1s)*E567+h1s*F567</f>
-        <v>26.1018954419896</v>
+        <v>25.3988409204097</v>
       </c>
       <c r="G570" s="17" t="n">
         <f aca="false">(1-h1s)*F567+h1s*G567</f>
-        <v>28.4236972034577</v>
+        <v>27.662754716098</v>
       </c>
       <c r="H570" s="8" t="s">
         <v>515</v>
@@ -59399,15 +59399,15 @@
       </c>
       <c r="E572" s="17" t="n">
         <f aca="false">E570+E571</f>
-        <v>34.6022925636284</v>
+        <v>34.2709752611434</v>
       </c>
       <c r="F572" s="17" t="n">
         <f aca="false">F570+F571</f>
-        <v>37.7510470839896</v>
+        <v>37.0479925624097</v>
       </c>
       <c r="G572" s="17" t="n">
         <f aca="false">G570+G571</f>
-        <v>41.4707470424977</v>
+        <v>40.709804555138</v>
       </c>
     </row>
     <row r="573" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59427,15 +59427,15 @@
       </c>
       <c r="E573" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(E572)</f>
-        <v>0.525503854044351</v>
+        <v>0.525001161461224</v>
       </c>
       <c r="F573" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(F572)</f>
-        <v>0.530054366629259</v>
+        <v>0.52907214052116</v>
       </c>
       <c r="G573" s="10" t="n">
         <f aca="false">gm_a+gm_b*LN(G572)</f>
-        <v>0.534964444590398</v>
+        <v>0.533996833374025</v>
       </c>
       <c r="H573" s="5" t="s">
         <v>516</v>
@@ -59458,15 +59458,15 @@
       </c>
       <c r="E574" s="17" t="n">
         <f aca="false">E572*E573</f>
-        <v>18.1836381009569</v>
+        <v>17.9923018165092</v>
       </c>
       <c r="F574" s="17" t="n">
         <f aca="false">F572*F573</f>
-        <v>20.0101073516955</v>
+        <v>19.6010607270061</v>
       </c>
       <c r="G574" s="17" t="n">
         <f aca="false">G572*G573</f>
-        <v>22.1853751583387</v>
+        <v>21.7389067197192</v>
       </c>
     </row>
     <row r="575" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59486,15 +59486,15 @@
       </c>
       <c r="E575" s="17" t="n">
         <f aca="false">opex_fix+opex_var*E572</f>
-        <v>4.14690889358399</v>
+        <v>4.12880103008697</v>
       </c>
       <c r="F575" s="17" t="n">
         <f aca="false">opex_fix+opex_var*F572</f>
-        <v>4.31900137596466</v>
+        <v>4.28057653303542</v>
       </c>
       <c r="G575" s="17" t="n">
         <f aca="false">opex_fix+opex_var*G572</f>
-        <v>4.52229839242993</v>
+        <v>4.48070973229404</v>
       </c>
       <c r="H575" s="5" t="s">
         <v>517</v>
@@ -59517,15 +59517,15 @@
       </c>
       <c r="E576" s="17" t="n">
         <f aca="false">E574-E575</f>
-        <v>14.0367292073729</v>
+        <v>13.8635007864222</v>
       </c>
       <c r="F576" s="17" t="n">
         <f aca="false">F574-F575</f>
-        <v>15.6911059757308</v>
+        <v>15.3204841939707</v>
       </c>
       <c r="G576" s="17" t="n">
         <f aca="false">G574-G575</f>
-        <v>17.6630767659088</v>
+        <v>17.2581969874251</v>
       </c>
     </row>
     <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59545,15 +59545,15 @@
       </c>
       <c r="E577" s="10" t="n">
         <f aca="false">E576/E572</f>
-        <v>0.405658936660381</v>
+        <v>0.404526007234486</v>
       </c>
       <c r="F577" s="10" t="n">
         <f aca="false">F576/F572</f>
-        <v>0.415646907510161</v>
+        <v>0.413530751178012</v>
       </c>
       <c r="G577" s="10" t="n">
         <f aca="false">G576/G572</f>
-        <v>0.425916532147547</v>
+        <v>0.423932199528257</v>
       </c>
     </row>
     <row r="578" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59573,15 +59573,15 @@
       </c>
       <c r="E578" s="17" t="n">
         <f aca="false">(E576+oth_inc_hi)*(1-tax)</f>
-        <v>11.8876688881564</v>
+        <v>11.7430231566625</v>
       </c>
       <c r="F578" s="17" t="n">
         <f aca="false">(F576+oth_inc_hi)*(1-tax)</f>
-        <v>13.2690734897352</v>
+        <v>12.9596043019655</v>
       </c>
       <c r="G578" s="17" t="n">
         <f aca="false">(G576+oth_inc_hi)*(1-tax)</f>
-        <v>14.9156690995338</v>
+        <v>14.5775944845</v>
       </c>
     </row>
     <row r="579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59629,15 +59629,15 @@
       </c>
       <c r="E580" s="13" t="n">
         <f aca="false">E578/E579</f>
-        <v>9.48736543348474</v>
+        <v>9.37192590316243</v>
       </c>
       <c r="F580" s="13" t="n">
         <f aca="false">F578/F579</f>
-        <v>10.7511098154158</v>
+        <v>10.5003660671975</v>
       </c>
       <c r="G580" s="13" t="n">
         <f aca="false">G578/G579</f>
-        <v>12.2692836834742</v>
+        <v>11.9911913410957</v>
       </c>
     </row>
     <row r="581" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59657,15 +59657,15 @@
       </c>
       <c r="E581" s="10" t="n">
         <f aca="false">E570/E572</f>
-        <v>0.697479442127972</v>
+        <v>0.694554801249891</v>
       </c>
       <c r="F581" s="10" t="n">
         <f aca="false">F570/F572</f>
-        <v>0.691421760671098</v>
+        <v>0.685565915012096</v>
       </c>
       <c r="G581" s="10" t="n">
         <f aca="false">G570/G572</f>
-        <v>0.685391492329042</v>
+        <v>0.679510870130343</v>
       </c>
     </row>
     <row r="584" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59702,15 +59702,15 @@
       </c>
       <c r="C586" s="13" t="n">
         <f aca="false">(tp_wA*(Val!B98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B101*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B102*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B103*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C101*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C102*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C103*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D101*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D102*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D103*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>146.885495457259</v>
+        <v>143.842880264599</v>
       </c>
       <c r="D586" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>243.381970662909</v>
+        <v>237.732484351208</v>
       </c>
       <c r="E586" s="13" t="n">
         <f aca="false">tp_w_dcf*C586+(1-tp_w_dcf)*D586</f>
-        <v>195.133733060084</v>
+        <v>190.787682307904</v>
       </c>
       <c r="F586" s="10" t="n">
         <f aca="false">E586/E$586-1</f>
@@ -59726,19 +59726,19 @@
       </c>
       <c r="C587" s="13" t="n">
         <f aca="false">(tp_wA*(Val!B98*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!B99*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!B100*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!B101*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B102*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B103*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C98*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!C99*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!C100*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!C101*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C102*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C103*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D98*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!D99*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!D100*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!D101*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D102*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D103*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
-        <v>127.484936624092</v>
+        <v>124.848706627946</v>
       </c>
       <c r="D587" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>243.381970662909</v>
+        <v>237.732484351208</v>
       </c>
       <c r="E587" s="13" t="n">
         <f aca="false">tp_w_dcf*C587+(1-tp_w_dcf)*D587</f>
-        <v>185.4334536435</v>
+        <v>181.290595489577</v>
       </c>
       <c r="F587" s="10" t="n">
         <f aca="false">E587/E$586-1</f>
-        <v>-0.0497109303679266</v>
+        <v>-0.0497783017406731</v>
       </c>
     </row>
     <row r="588" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59750,19 +59750,19 @@
       </c>
       <c r="C588" s="13" t="n">
         <f aca="false">(tp_wA*(Val!B98*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!B99*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!B100*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!B101*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B102*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B103*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C98*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!C99*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!C100*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!C101*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C102*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C103*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D98*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!D99*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!D100*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!D101*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D102*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D103*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
-        <v>174.029071561665</v>
+        <v>170.418169442082</v>
       </c>
       <c r="D588" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>243.381970662909</v>
+        <v>237.732484351208</v>
       </c>
       <c r="E588" s="13" t="n">
         <f aca="false">tp_w_dcf*C588+(1-tp_w_dcf)*D588</f>
-        <v>208.705521112287</v>
+        <v>204.075326896645</v>
       </c>
       <c r="F588" s="10" t="n">
         <f aca="false">E588/E$586-1</f>
-        <v>0.0695512141307935</v>
+        <v>0.0696462393588762</v>
       </c>
     </row>
     <row r="589" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59774,19 +59774,19 @@
       </c>
       <c r="C589" s="13" t="n">
         <f aca="false">(tp_wA*(Val!B98*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B99*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B100*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B101*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B102*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B103*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B103*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C98*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C99*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C100*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C101*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C102*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C103*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C103*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D98*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D99*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D100*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D101*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D102*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D103*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D103*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>165.315494338033</v>
+        <v>161.88703827706</v>
       </c>
       <c r="D589" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>243.381970662909</v>
+        <v>237.732484351208</v>
       </c>
       <c r="E589" s="13" t="n">
         <f aca="false">tp_w_dcf*C589+(1-tp_w_dcf)*D589</f>
-        <v>204.348732500471</v>
+        <v>199.809761314134</v>
       </c>
       <c r="F589" s="10" t="n">
         <f aca="false">E589/E$586-1</f>
-        <v>0.047224020654336</v>
+        <v>0.0472885822454192</v>
       </c>
     </row>
     <row r="590" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59798,19 +59798,19 @@
       </c>
       <c r="C590" s="13" t="n">
         <f aca="false">(tp_wA*(Val!B98*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B99*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B100*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B101*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B102*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B103*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B103*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*(Val!C98*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C99*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C100*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C101*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C102*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C103*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C103*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*(Val!D98*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D99*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D100*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D101*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D102*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D103*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D103*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>133.932114158512</v>
+        <v>131.16084436642</v>
       </c>
       <c r="D590" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>243.381970662909</v>
+        <v>237.732484351208</v>
       </c>
       <c r="E590" s="13" t="n">
         <f aca="false">tp_w_dcf*C590+(1-tp_w_dcf)*D590</f>
-        <v>188.65704241071</v>
+        <v>184.446664358814</v>
       </c>
       <c r="F590" s="10" t="n">
         <f aca="false">E590/E$586-1</f>
-        <v>-0.0331910354391636</v>
+        <v>-0.0332359923470131</v>
       </c>
     </row>
     <row r="591" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59822,19 +59822,19 @@
       </c>
       <c r="C591" s="13" t="n">
         <f aca="false">(tp_wA*(Val!B98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B101*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B102*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B103*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C101*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C102*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C103*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D101*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D102*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D103*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>146.885495457259</v>
+        <v>143.842880264599</v>
       </c>
       <c r="D591" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>243.381970662909</v>
+        <v>237.732484351208</v>
       </c>
       <c r="E591" s="13" t="n">
         <f aca="false">0.4*C591+(1-0.4)*D591</f>
-        <v>204.783380580649</v>
+        <v>200.176642716564</v>
       </c>
       <c r="F591" s="10" t="n">
         <f aca="false">E591/E$586-1</f>
-        <v>0.0494514575683014</v>
+        <v>0.0492115648928972</v>
       </c>
     </row>
     <row r="592" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59846,19 +59846,19 @@
       </c>
       <c r="C592" s="13" t="n">
         <f aca="false">(tp_wA*(Val!B98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B101*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B102*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B103*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C101*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C102*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C103*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D101*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D102*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D103*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D103*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>146.885495457259</v>
+        <v>143.842880264599</v>
       </c>
       <c r="D592" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>243.381970662909</v>
+        <v>237.732484351208</v>
       </c>
       <c r="E592" s="13" t="n">
         <f aca="false">0.8*C592+(1-0.8)*D592</f>
-        <v>166.184790498389</v>
+        <v>162.620801081921</v>
       </c>
       <c r="F592" s="10" t="n">
         <f aca="false">E592/E$586-1</f>
-        <v>-0.148354372704904</v>
+        <v>-0.147634694678691</v>
       </c>
     </row>
   </sheetData>
